--- a/Results/Phase 2/Carbon dioxide/carbon dioxide ecotoxicity freshwater results.xlsx
+++ b/Results/Phase 2/Carbon dioxide/carbon dioxide ecotoxicity freshwater results.xlsx
@@ -3257,7 +3257,7 @@
         <v>66.95144180229023</v>
       </c>
       <c r="S15" t="n">
-        <v>66.66413081238655</v>
+        <v>66.66413081238656</v>
       </c>
       <c r="T15" t="n">
         <v>66.18914940795155</v>
@@ -5014,85 +5014,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>14.82728848146627</v>
+        <v>14.8272884814661</v>
       </c>
       <c r="C2" t="n">
-        <v>10.56773154003308</v>
+        <v>10.56773154003309</v>
       </c>
       <c r="D2" t="n">
-        <v>16.59710956329379</v>
+        <v>16.59710956329362</v>
       </c>
       <c r="E2" t="n">
         <v>10.8203336217722</v>
       </c>
       <c r="F2" t="n">
-        <v>16.12402908264007</v>
+        <v>16.12402908264008</v>
       </c>
       <c r="G2" t="n">
-        <v>30.14227935199282</v>
+        <v>30.14227935199259</v>
       </c>
       <c r="H2" t="n">
-        <v>10.93634225643032</v>
+        <v>10.93634225643018</v>
       </c>
       <c r="I2" t="n">
-        <v>14.41237789946634</v>
+        <v>14.41237789946618</v>
       </c>
       <c r="J2" t="n">
-        <v>22.0777437456777</v>
+        <v>22.07774374567736</v>
       </c>
       <c r="K2" t="n">
-        <v>14.85159838616546</v>
+        <v>14.85159838616529</v>
       </c>
       <c r="L2" t="n">
-        <v>12.49251723389269</v>
+        <v>12.49251723389245</v>
       </c>
       <c r="M2" t="n">
-        <v>36.30378577156746</v>
+        <v>36.30378577156741</v>
       </c>
       <c r="N2" t="n">
-        <v>12.59207881809535</v>
+        <v>12.5920788180952</v>
       </c>
       <c r="O2" t="n">
-        <v>15.57093842739487</v>
+        <v>15.57093842739472</v>
       </c>
       <c r="P2" t="n">
-        <v>20.62688517930878</v>
+        <v>20.62688517930865</v>
       </c>
       <c r="Q2" t="n">
-        <v>13.16733112656433</v>
+        <v>13.16733112656416</v>
       </c>
       <c r="R2" t="n">
-        <v>11.05425234267917</v>
+        <v>11.05425234267901</v>
       </c>
       <c r="S2" t="n">
-        <v>16.71498757627944</v>
+        <v>16.71498757627926</v>
       </c>
       <c r="T2" t="n">
-        <v>12.44124972394357</v>
+        <v>12.44124972394336</v>
       </c>
       <c r="U2" t="n">
-        <v>14.28035502974777</v>
+        <v>14.28035502974748</v>
       </c>
       <c r="V2" t="n">
-        <v>14.03814588170138</v>
+        <v>14.03814588170139</v>
       </c>
       <c r="W2" t="n">
-        <v>15.9539845314879</v>
+        <v>15.95398453148774</v>
       </c>
       <c r="X2" t="n">
-        <v>16.51602570036792</v>
+        <v>16.51602570036773</v>
       </c>
       <c r="Y2" t="n">
-        <v>22.39982918835592</v>
+        <v>22.39982918835576</v>
       </c>
       <c r="Z2" t="n">
-        <v>15.93502411903036</v>
+        <v>15.93502411903019</v>
       </c>
       <c r="AA2" t="n">
-        <v>13.53151047811815</v>
+        <v>13.53151047811795</v>
       </c>
       <c r="AB2" t="n">
-        <v>38.90559816779643</v>
+        <v>38.90559816779638</v>
       </c>
     </row>
     <row r="3">
@@ -5102,85 +5102,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>11.22269781079597</v>
+        <v>11.22269781079578</v>
       </c>
       <c r="C3" t="n">
-        <v>12.45498804954637</v>
+        <v>12.45498804954638</v>
       </c>
       <c r="D3" t="n">
-        <v>12.45296694184641</v>
+        <v>12.45296694184642</v>
       </c>
       <c r="E3" t="n">
-        <v>11.74220983961228</v>
+        <v>11.74220983961229</v>
       </c>
       <c r="F3" t="n">
-        <v>11.39874051853362</v>
+        <v>11.39874051853363</v>
       </c>
       <c r="G3" t="n">
-        <v>12.70807126063395</v>
+        <v>12.708071260634</v>
       </c>
       <c r="H3" t="n">
-        <v>12.45296694184641</v>
+        <v>12.45296694184642</v>
       </c>
       <c r="I3" t="n">
-        <v>12.45296694184641</v>
+        <v>12.45296694184642</v>
       </c>
       <c r="J3" t="n">
-        <v>12.432155345925</v>
+        <v>12.43215534592493</v>
       </c>
       <c r="K3" t="n">
-        <v>12.45296694184641</v>
+        <v>12.45296694184642</v>
       </c>
       <c r="L3" t="n">
-        <v>12.45296694184641</v>
+        <v>12.45296694184642</v>
       </c>
       <c r="M3" t="n">
-        <v>12.49221357672782</v>
+        <v>12.49221357672783</v>
       </c>
       <c r="N3" t="n">
-        <v>11.49930254576037</v>
+        <v>11.49930254576031</v>
       </c>
       <c r="O3" t="n">
-        <v>11.76137780237625</v>
+        <v>11.76137780237622</v>
       </c>
       <c r="P3" t="n">
-        <v>11.69713682434906</v>
+        <v>11.69713682434909</v>
       </c>
       <c r="Q3" t="n">
-        <v>10.98092184700156</v>
+        <v>10.98092184700135</v>
       </c>
       <c r="R3" t="n">
-        <v>12.45296694184641</v>
+        <v>12.45296694184642</v>
       </c>
       <c r="S3" t="n">
-        <v>12.45296694184641</v>
+        <v>12.45296694184642</v>
       </c>
       <c r="T3" t="n">
-        <v>12.45296694184641</v>
+        <v>12.45296694184642</v>
       </c>
       <c r="U3" t="n">
-        <v>11.85218419944863</v>
+        <v>11.85218419944855</v>
       </c>
       <c r="V3" t="n">
         <v>12.06095482532595</v>
       </c>
       <c r="W3" t="n">
-        <v>12.45320872506089</v>
+        <v>12.45320872506075</v>
       </c>
       <c r="X3" t="n">
-        <v>11.09367845749247</v>
+        <v>11.09367845749233</v>
       </c>
       <c r="Y3" t="n">
-        <v>13.67567411236269</v>
+        <v>13.67567411236266</v>
       </c>
       <c r="Z3" t="n">
-        <v>11.19984493005893</v>
+        <v>11.19984493005886</v>
       </c>
       <c r="AA3" t="n">
-        <v>12.45296694184641</v>
+        <v>12.45296694184642</v>
       </c>
       <c r="AB3" t="n">
-        <v>13.79092406175507</v>
+        <v>13.79092406175508</v>
       </c>
     </row>
     <row r="4">
@@ -5190,85 +5190,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>23.80567667775824</v>
+        <v>23.80567667775804</v>
       </c>
       <c r="C4" t="n">
-        <v>22.25440262852513</v>
+        <v>22.25440262852506</v>
       </c>
       <c r="D4" t="n">
-        <v>24.45075567979599</v>
+        <v>24.45075567979572</v>
       </c>
       <c r="E4" t="n">
-        <v>22.30980651594614</v>
+        <v>22.30980651594611</v>
       </c>
       <c r="F4" t="n">
-        <v>24.26839744074815</v>
+        <v>24.26839744074801</v>
       </c>
       <c r="G4" t="n">
-        <v>29.38781101236275</v>
+        <v>29.38781101236249</v>
       </c>
       <c r="H4" t="n">
-        <v>22.38747246852997</v>
+        <v>22.38747246852977</v>
       </c>
       <c r="I4" t="n">
-        <v>23.65444664274531</v>
+        <v>23.65444664274508</v>
       </c>
       <c r="J4" t="n">
-        <v>25.46402272726189</v>
+        <v>25.46402272726161</v>
       </c>
       <c r="K4" t="n">
-        <v>23.81453735255978</v>
+        <v>23.81453735255958</v>
       </c>
       <c r="L4" t="n">
-        <v>22.9546799742859</v>
+        <v>22.95467997428558</v>
       </c>
       <c r="M4" t="n">
-        <v>31.65854944756074</v>
+        <v>31.65854944756052</v>
       </c>
       <c r="N4" t="n">
-        <v>22.99096900261657</v>
+        <v>22.99096900261634</v>
       </c>
       <c r="O4" t="n">
-        <v>24.07672835067067</v>
+        <v>24.07672835067046</v>
       </c>
       <c r="P4" t="n">
-        <v>25.91956157181908</v>
+        <v>25.91956157181881</v>
       </c>
       <c r="Q4" t="n">
-        <v>23.20064171409989</v>
+        <v>23.20064171409962</v>
       </c>
       <c r="R4" t="n">
-        <v>22.43044931039756</v>
+        <v>22.43044931039731</v>
       </c>
       <c r="S4" t="n">
-        <v>24.49372083133573</v>
+        <v>24.49372083133544</v>
       </c>
       <c r="T4" t="n">
-        <v>22.93599356892292</v>
+        <v>22.93599356892265</v>
       </c>
       <c r="U4" t="n">
-        <v>23.6063258570238</v>
+        <v>23.60632585702354</v>
       </c>
       <c r="V4" t="n">
-        <v>17.00366262639201</v>
+        <v>17.00366262639211</v>
       </c>
       <c r="W4" t="n">
-        <v>24.21634415765812</v>
+        <v>24.21634415765789</v>
       </c>
       <c r="X4" t="n">
-        <v>24.42120156389429</v>
+        <v>24.42120156389411</v>
       </c>
       <c r="Y4" t="n">
-        <v>26.56577884415709</v>
+        <v>26.56577884415686</v>
       </c>
       <c r="Z4" t="n">
-        <v>24.20943330996178</v>
+        <v>24.20943330996151</v>
       </c>
       <c r="AA4" t="n">
-        <v>23.33338081133139</v>
+        <v>23.33338081133115</v>
       </c>
       <c r="AB4" t="n">
-        <v>32.61551707444305</v>
+        <v>32.61551707444279</v>
       </c>
     </row>
     <row r="5">
@@ -5278,85 +5278,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>22.49184570553952</v>
+        <v>22.49184570553931</v>
       </c>
       <c r="C5" t="n">
-        <v>22.94228546495793</v>
+        <v>22.94228546495783</v>
       </c>
       <c r="D5" t="n">
-        <v>22.94026435725795</v>
+        <v>22.94026435725779</v>
       </c>
       <c r="E5" t="n">
-        <v>22.64581957213176</v>
+        <v>22.64581957213175</v>
       </c>
       <c r="F5" t="n">
-        <v>22.54608524627118</v>
+        <v>22.54608524627095</v>
       </c>
       <c r="G5" t="n">
-        <v>23.03324688586983</v>
+        <v>23.03324688586976</v>
       </c>
       <c r="H5" t="n">
-        <v>22.94026435725795</v>
+        <v>22.94026435725779</v>
       </c>
       <c r="I5" t="n">
-        <v>22.94026435725795</v>
+        <v>22.94026435725779</v>
       </c>
       <c r="J5" t="n">
-        <v>21.94831901976929</v>
+        <v>21.94831901976926</v>
       </c>
       <c r="K5" t="n">
-        <v>22.94026435725795</v>
+        <v>22.9402643572578</v>
       </c>
       <c r="L5" t="n">
-        <v>22.94026435725795</v>
+        <v>22.94026435725779</v>
       </c>
       <c r="M5" t="n">
-        <v>22.97951099213929</v>
+        <v>22.97951099213914</v>
       </c>
       <c r="N5" t="n">
-        <v>22.59266488337741</v>
+        <v>22.59266488337715</v>
       </c>
       <c r="O5" t="n">
-        <v>22.68818823697085</v>
+        <v>22.68818823697062</v>
       </c>
       <c r="P5" t="n">
-        <v>22.66477315483566</v>
+        <v>22.66477315483534</v>
       </c>
       <c r="Q5" t="n">
-        <v>22.40372120581309</v>
+        <v>22.40372120581294</v>
       </c>
       <c r="R5" t="n">
-        <v>22.94026435725795</v>
+        <v>22.94026435725779</v>
       </c>
       <c r="S5" t="n">
-        <v>22.94026435725795</v>
+        <v>22.9402643572578</v>
       </c>
       <c r="T5" t="n">
-        <v>22.94026435725795</v>
+        <v>22.9402643572578</v>
       </c>
       <c r="U5" t="n">
-        <v>22.72128610240107</v>
+        <v>22.72128610240102</v>
       </c>
       <c r="V5" t="n">
-        <v>16.28299970369279</v>
+        <v>16.28299970369315</v>
       </c>
       <c r="W5" t="n">
-        <v>22.94035248440048</v>
+        <v>22.94035248440022</v>
       </c>
       <c r="X5" t="n">
-        <v>22.44481966628232</v>
+        <v>22.44481966628198</v>
       </c>
       <c r="Y5" t="n">
-        <v>23.38592676315854</v>
+        <v>23.38592676315844</v>
       </c>
       <c r="Z5" t="n">
-        <v>22.48351609886313</v>
+        <v>22.4835160988628</v>
       </c>
       <c r="AA5" t="n">
-        <v>22.94026435725795</v>
+        <v>22.94026435725779</v>
       </c>
       <c r="AB5" t="n">
-        <v>23.46151327418361</v>
+        <v>23.46151327418359</v>
       </c>
     </row>
     <row r="6">
@@ -5366,85 +5366,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>11.34504602975451</v>
+        <v>11.3450460297544</v>
       </c>
       <c r="C6" t="n">
-        <v>9.793771980521338</v>
+        <v>9.793771980521345</v>
       </c>
       <c r="D6" t="n">
-        <v>11.99012503179226</v>
+        <v>11.99012503179214</v>
       </c>
       <c r="E6" t="n">
-        <v>9.849175867942451</v>
+        <v>9.84917586794246</v>
       </c>
       <c r="F6" t="n">
-        <v>11.80776679274436</v>
+        <v>11.80776679274437</v>
       </c>
       <c r="G6" t="n">
-        <v>16.8881552331634</v>
+        <v>16.88815523316319</v>
       </c>
       <c r="H6" t="n">
-        <v>9.926841820526274</v>
+        <v>9.926841820526162</v>
       </c>
       <c r="I6" t="n">
-        <v>11.19381599474159</v>
+        <v>11.19381599474146</v>
       </c>
       <c r="J6" t="n">
-        <v>13.93692959531517</v>
+        <v>13.9369295953151</v>
       </c>
       <c r="K6" t="n">
-        <v>11.35390670455604</v>
+        <v>11.35390670455595</v>
       </c>
       <c r="L6" t="n">
-        <v>10.49404932628214</v>
+        <v>10.49404932628199</v>
       </c>
       <c r="M6" t="n">
-        <v>19.19791879955693</v>
+        <v>19.19791879955692</v>
       </c>
       <c r="N6" t="n">
-        <v>10.53033835461283</v>
+        <v>10.53033835461273</v>
       </c>
       <c r="O6" t="n">
-        <v>11.57707257147124</v>
+        <v>11.57707257147113</v>
       </c>
       <c r="P6" t="n">
-        <v>13.41990579261964</v>
+        <v>13.41990579261952</v>
       </c>
       <c r="Q6" t="n">
-        <v>10.74001106609614</v>
+        <v>10.74001106609602</v>
       </c>
       <c r="R6" t="n">
-        <v>9.969818662393832</v>
+        <v>9.969818662393719</v>
       </c>
       <c r="S6" t="n">
-        <v>12.03309018333201</v>
+        <v>12.03309018333188</v>
       </c>
       <c r="T6" t="n">
-        <v>10.47536292091915</v>
+        <v>10.47536292091904</v>
       </c>
       <c r="U6" t="n">
-        <v>11.10667007782428</v>
+        <v>11.10667007782418</v>
       </c>
       <c r="V6" t="n">
-        <v>10.98523682215982</v>
+        <v>10.98523682215987</v>
       </c>
       <c r="W6" t="n">
-        <v>11.71668837845871</v>
+        <v>11.7166883784586</v>
       </c>
       <c r="X6" t="n">
-        <v>11.92154578469487</v>
+        <v>11.92154578469474</v>
       </c>
       <c r="Y6" t="n">
-        <v>14.10514819615337</v>
+        <v>14.10514819615324</v>
       </c>
       <c r="Z6" t="n">
-        <v>11.74880266195805</v>
+        <v>11.74880266195791</v>
       </c>
       <c r="AA6" t="n">
-        <v>10.87275016332765</v>
+        <v>10.87275016332754</v>
       </c>
       <c r="AB6" t="n">
-        <v>20.15488642643917</v>
+        <v>20.15488642643918</v>
       </c>
     </row>
     <row r="7">
@@ -5454,7 +5454,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>10.03121505753585</v>
+        <v>10.03121505753573</v>
       </c>
       <c r="C7" t="n">
         <v>10.48165481695413</v>
@@ -5469,7 +5469,7 @@
         <v>10.0854545982673</v>
       </c>
       <c r="G7" t="n">
-        <v>10.53359110667036</v>
+        <v>10.53359110667041</v>
       </c>
       <c r="H7" t="n">
         <v>10.47963370925416</v>
@@ -5478,7 +5478,7 @@
         <v>10.47963370925416</v>
       </c>
       <c r="J7" t="n">
-        <v>10.42122588782287</v>
+        <v>10.42122588782275</v>
       </c>
       <c r="K7" t="n">
         <v>10.47963370925416</v>
@@ -5490,16 +5490,16 @@
         <v>10.51888034413547</v>
       </c>
       <c r="N7" t="n">
-        <v>10.13203423537362</v>
+        <v>10.1320342353735</v>
       </c>
       <c r="O7" t="n">
-        <v>10.18853245777141</v>
+        <v>10.18853245777128</v>
       </c>
       <c r="P7" t="n">
-        <v>10.1651173756362</v>
+        <v>10.16511737563605</v>
       </c>
       <c r="Q7" t="n">
-        <v>9.943090557809333</v>
+        <v>9.943090557809379</v>
       </c>
       <c r="R7" t="n">
         <v>10.47963370925416</v>
@@ -5511,28 +5511,28 @@
         <v>10.47963370925416</v>
       </c>
       <c r="U7" t="n">
-        <v>10.22163032320164</v>
+        <v>10.22163032320161</v>
       </c>
       <c r="V7" t="n">
-        <v>10.26457389946056</v>
+        <v>10.26457389946061</v>
       </c>
       <c r="W7" t="n">
-        <v>10.44069670520098</v>
+        <v>10.44069670520095</v>
       </c>
       <c r="X7" t="n">
-        <v>9.945163887082874</v>
+        <v>9.945163887082677</v>
       </c>
       <c r="Y7" t="n">
-        <v>10.92529611515476</v>
+        <v>10.92529611515485</v>
       </c>
       <c r="Z7" t="n">
-        <v>10.0228854508593</v>
+        <v>10.02288545085918</v>
       </c>
       <c r="AA7" t="n">
         <v>10.47963370925416</v>
       </c>
       <c r="AB7" t="n">
-        <v>11.0008826261799</v>
+        <v>11.00088262617991</v>
       </c>
     </row>
     <row r="8">
@@ -5542,85 +5542,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>82.5672034435258</v>
+        <v>82.56720344352581</v>
       </c>
       <c r="C8" t="n">
-        <v>82.5672034435258</v>
+        <v>82.56720344352581</v>
       </c>
       <c r="D8" t="n">
-        <v>82.5672034435258</v>
+        <v>82.56720344352581</v>
       </c>
       <c r="E8" t="n">
-        <v>82.5672034435258</v>
+        <v>82.56720344352581</v>
       </c>
       <c r="F8" t="n">
-        <v>82.5672034435258</v>
+        <v>82.56720344352581</v>
       </c>
       <c r="G8" t="n">
-        <v>82.5672034435258</v>
+        <v>82.56720344352581</v>
       </c>
       <c r="H8" t="n">
-        <v>82.5672034435258</v>
+        <v>82.56720344352581</v>
       </c>
       <c r="I8" t="n">
-        <v>82.5672034435258</v>
+        <v>82.56720344352581</v>
       </c>
       <c r="J8" t="n">
-        <v>82.5672034435258</v>
+        <v>82.56720344352581</v>
       </c>
       <c r="K8" t="n">
-        <v>82.5672034435258</v>
+        <v>82.56720344352581</v>
       </c>
       <c r="L8" t="n">
-        <v>82.5672034435258</v>
+        <v>82.56720344352581</v>
       </c>
       <c r="M8" t="n">
-        <v>82.5672034435258</v>
+        <v>82.56720344352581</v>
       </c>
       <c r="N8" t="n">
-        <v>82.5672034435258</v>
+        <v>82.56720344352581</v>
       </c>
       <c r="O8" t="n">
-        <v>82.5672034435258</v>
+        <v>82.56720344352581</v>
       </c>
       <c r="P8" t="n">
-        <v>82.5672034435258</v>
+        <v>82.56720344352581</v>
       </c>
       <c r="Q8" t="n">
-        <v>82.5672034435258</v>
+        <v>82.56720344352581</v>
       </c>
       <c r="R8" t="n">
-        <v>82.5672034435258</v>
+        <v>82.56720344352581</v>
       </c>
       <c r="S8" t="n">
         <v>82.30175426985906</v>
       </c>
       <c r="T8" t="n">
-        <v>82.5672034435258</v>
+        <v>82.56720344352581</v>
       </c>
       <c r="U8" t="n">
-        <v>82.5672034435258</v>
+        <v>82.56720344352581</v>
       </c>
       <c r="V8" t="n">
-        <v>82.5672034435258</v>
+        <v>82.56720344352581</v>
       </c>
       <c r="W8" t="n">
-        <v>82.5672034435258</v>
+        <v>82.56720344352581</v>
       </c>
       <c r="X8" t="n">
-        <v>82.5672034435258</v>
+        <v>82.56720344352581</v>
       </c>
       <c r="Y8" t="n">
-        <v>82.5672034435258</v>
+        <v>82.56720344352581</v>
       </c>
       <c r="Z8" t="n">
-        <v>82.5672034435258</v>
+        <v>82.56720344352581</v>
       </c>
       <c r="AA8" t="n">
-        <v>82.5672034435258</v>
+        <v>82.56720344352581</v>
       </c>
       <c r="AB8" t="n">
-        <v>82.5672034435258</v>
+        <v>82.56720344352581</v>
       </c>
     </row>
     <row r="9">
@@ -5630,13 +5630,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>71.44612195095429</v>
+        <v>71.44612195095425</v>
       </c>
       <c r="C9" t="n">
-        <v>66.86619128008779</v>
+        <v>66.8661912800878</v>
       </c>
       <c r="D9" t="n">
-        <v>73.34815395908728</v>
+        <v>73.3481539590873</v>
       </c>
       <c r="E9" t="n">
         <v>67.19966975864618</v>
@@ -5645,7 +5645,7 @@
         <v>72.85651857089789</v>
       </c>
       <c r="G9" t="n">
-        <v>87.90518842897754</v>
+        <v>87.90518842897757</v>
       </c>
       <c r="H9" t="n">
         <v>67.26451040957708</v>
@@ -5654,25 +5654,25 @@
         <v>71.00021630796013</v>
       </c>
       <c r="J9" t="n">
-        <v>79.26057418550918</v>
+        <v>79.26057418550917</v>
       </c>
       <c r="K9" t="n">
-        <v>71.47224787821732</v>
+        <v>71.47224787821733</v>
       </c>
       <c r="L9" t="n">
-        <v>68.93693631057988</v>
+        <v>68.93693631057987</v>
       </c>
       <c r="M9" t="n">
-        <v>94.48479932420337</v>
+        <v>94.48479932420328</v>
       </c>
       <c r="N9" t="n">
-        <v>69.04393544279627</v>
+        <v>69.04393544279624</v>
       </c>
       <c r="O9" t="n">
         <v>72.24532477124282</v>
       </c>
       <c r="P9" t="n">
-        <v>77.67896586202826</v>
+        <v>77.67896586202824</v>
       </c>
       <c r="Q9" t="n">
         <v>69.66216081862387</v>
@@ -5681,19 +5681,19 @@
         <v>67.39122873180176</v>
       </c>
       <c r="S9" t="n">
-        <v>73.47483781208004</v>
+        <v>73.47483781208005</v>
       </c>
       <c r="T9" t="n">
-        <v>68.88183896435557</v>
+        <v>68.88183896435554</v>
       </c>
       <c r="U9" t="n">
-        <v>70.85833093514545</v>
+        <v>70.85833093514555</v>
       </c>
       <c r="V9" t="n">
-        <v>70.65759326748574</v>
+        <v>70.65759326748577</v>
       </c>
       <c r="W9" t="n">
-        <v>72.6569855645605</v>
+        <v>72.65698556456047</v>
       </c>
       <c r="X9" t="n">
         <v>73.26101288917255</v>
@@ -5708,7 +5708,7 @@
         <v>70.05354545657899</v>
       </c>
       <c r="AB9" t="n">
-        <v>97.26636805531392</v>
+        <v>97.26636805531388</v>
       </c>
     </row>
     <row r="10">
@@ -5721,43 +5721,43 @@
         <v>67.57225758001294</v>
       </c>
       <c r="C10" t="n">
-        <v>68.89443149346856</v>
+        <v>68.89443149346859</v>
       </c>
       <c r="D10" t="n">
-        <v>68.89443149346856</v>
+        <v>68.89443149346859</v>
       </c>
       <c r="E10" t="n">
         <v>68.19041288622711</v>
       </c>
       <c r="F10" t="n">
-        <v>67.77823682316627</v>
+        <v>67.77823682316628</v>
       </c>
       <c r="G10" t="n">
         <v>69.16859286759228</v>
       </c>
       <c r="H10" t="n">
-        <v>68.89443149346856</v>
+        <v>68.89443149346859</v>
       </c>
       <c r="I10" t="n">
-        <v>68.89443149346856</v>
+        <v>68.89443149346859</v>
       </c>
       <c r="J10" t="n">
-        <v>68.89443149346856</v>
+        <v>68.89443149346859</v>
       </c>
       <c r="K10" t="n">
-        <v>68.89443149346856</v>
+        <v>68.89443149346859</v>
       </c>
       <c r="L10" t="n">
-        <v>68.89443149346856</v>
+        <v>68.89443149346859</v>
       </c>
       <c r="M10" t="n">
-        <v>68.89443149346874</v>
+        <v>68.89443149346876</v>
       </c>
       <c r="N10" t="n">
         <v>67.86952551568488</v>
       </c>
       <c r="O10" t="n">
-        <v>68.15117857753478</v>
+        <v>68.15117857753476</v>
       </c>
       <c r="P10" t="n">
         <v>68.08213860637834</v>
@@ -5766,13 +5766,13 @@
         <v>67.31242022885006</v>
       </c>
       <c r="R10" t="n">
-        <v>68.89443149346856</v>
+        <v>68.89443149346859</v>
       </c>
       <c r="S10" t="n">
-        <v>68.89443149346856</v>
+        <v>68.89443149346859</v>
       </c>
       <c r="T10" t="n">
-        <v>68.89443149346856</v>
+        <v>68.89443149346859</v>
       </c>
       <c r="U10" t="n">
         <v>68.24876848396558</v>
@@ -5781,7 +5781,7 @@
         <v>68.53270012770176</v>
       </c>
       <c r="W10" t="n">
-        <v>68.89469133861189</v>
+        <v>68.89469133861191</v>
       </c>
       <c r="X10" t="n">
         <v>67.43360009526964</v>
@@ -5793,7 +5793,7 @@
         <v>67.54769752075831</v>
       </c>
       <c r="AA10" t="n">
-        <v>68.89443149346856</v>
+        <v>68.89443149346859</v>
       </c>
       <c r="AB10" t="n">
         <v>70.27555270453649</v>
@@ -5806,85 +5806,85 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>84.63268631796639</v>
+        <v>84.63268631796615</v>
       </c>
       <c r="C11" t="n">
-        <v>84.63268631796639</v>
+        <v>84.63268631796615</v>
       </c>
       <c r="D11" t="n">
-        <v>84.63268631796639</v>
+        <v>84.63268631796615</v>
       </c>
       <c r="E11" t="n">
-        <v>84.63268631796639</v>
+        <v>84.63268631796615</v>
       </c>
       <c r="F11" t="n">
-        <v>84.63268631796639</v>
+        <v>84.63268631796615</v>
       </c>
       <c r="G11" t="n">
-        <v>84.63268631796639</v>
+        <v>84.63268631796615</v>
       </c>
       <c r="H11" t="n">
-        <v>84.63268631796639</v>
+        <v>84.63268631796615</v>
       </c>
       <c r="I11" t="n">
-        <v>84.63268631796639</v>
+        <v>84.63268631796615</v>
       </c>
       <c r="J11" t="n">
-        <v>83.79763474021844</v>
+        <v>83.79763474021823</v>
       </c>
       <c r="K11" t="n">
-        <v>84.63268631796639</v>
+        <v>84.63268631796615</v>
       </c>
       <c r="L11" t="n">
-        <v>84.63268631796639</v>
+        <v>84.63268631796615</v>
       </c>
       <c r="M11" t="n">
-        <v>84.63268631796639</v>
+        <v>84.63268631796615</v>
       </c>
       <c r="N11" t="n">
-        <v>84.63268631796639</v>
+        <v>84.63268631796615</v>
       </c>
       <c r="O11" t="n">
-        <v>84.63268631796639</v>
+        <v>84.63268631796615</v>
       </c>
       <c r="P11" t="n">
-        <v>84.63268631796639</v>
+        <v>84.63268631796615</v>
       </c>
       <c r="Q11" t="n">
-        <v>84.63268631796639</v>
+        <v>84.63268631796615</v>
       </c>
       <c r="R11" t="n">
-        <v>84.63268631796639</v>
+        <v>84.63268631796615</v>
       </c>
       <c r="S11" t="n">
-        <v>84.50221129776506</v>
+        <v>84.50221129776492</v>
       </c>
       <c r="T11" t="n">
-        <v>84.63268631796639</v>
+        <v>84.63268631796615</v>
       </c>
       <c r="U11" t="n">
-        <v>84.63268631796639</v>
+        <v>84.63268631796615</v>
       </c>
       <c r="V11" t="n">
-        <v>79.06143614416098</v>
+        <v>79.06143614416074</v>
       </c>
       <c r="W11" t="n">
-        <v>84.63268631796639</v>
+        <v>84.63268631796615</v>
       </c>
       <c r="X11" t="n">
-        <v>84.63268631796639</v>
+        <v>84.63268631796615</v>
       </c>
       <c r="Y11" t="n">
-        <v>84.63268631796639</v>
+        <v>84.63268631796615</v>
       </c>
       <c r="Z11" t="n">
-        <v>84.63268631796639</v>
+        <v>84.63268631796615</v>
       </c>
       <c r="AA11" t="n">
-        <v>84.63268631796639</v>
+        <v>84.63268631796615</v>
       </c>
       <c r="AB11" t="n">
-        <v>84.63268631796639</v>
+        <v>84.63268631796615</v>
       </c>
     </row>
     <row r="12">
@@ -5894,85 +5894,85 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>79.16639191456116</v>
+        <v>79.16639191456109</v>
       </c>
       <c r="C12" t="n">
-        <v>76.91523950543048</v>
+        <v>76.91523950543035</v>
       </c>
       <c r="D12" t="n">
-        <v>80.10128902219408</v>
+        <v>80.10128902219391</v>
       </c>
       <c r="E12" t="n">
-        <v>77.0791526592202</v>
+        <v>77.07915265922</v>
       </c>
       <c r="F12" t="n">
-        <v>79.85963772481151</v>
+        <v>79.85963772481152</v>
       </c>
       <c r="G12" t="n">
-        <v>87.2564417028114</v>
+        <v>87.2564417028113</v>
       </c>
       <c r="H12" t="n">
-        <v>77.11102348828784</v>
+        <v>77.11102348828763</v>
       </c>
       <c r="I12" t="n">
-        <v>78.94721795001699</v>
+        <v>78.94721795001686</v>
       </c>
       <c r="J12" t="n">
-        <v>82.17234236021866</v>
+        <v>82.17234236021847</v>
       </c>
       <c r="K12" t="n">
-        <v>79.17923347228898</v>
+        <v>79.17923347228887</v>
       </c>
       <c r="L12" t="n">
-        <v>77.9330633545425</v>
+        <v>77.9330633545424</v>
       </c>
       <c r="M12" t="n">
-        <v>90.49048780140176</v>
+        <v>90.49048780140151</v>
       </c>
       <c r="N12" t="n">
-        <v>77.98565614940647</v>
+        <v>77.98565614940635</v>
       </c>
       <c r="O12" t="n">
-        <v>79.55922042738581</v>
+        <v>79.55922042738567</v>
       </c>
       <c r="P12" t="n">
-        <v>82.22999322088728</v>
+        <v>82.22999322088712</v>
       </c>
       <c r="Q12" t="n">
-        <v>78.28952964535966</v>
+        <v>78.28952964535961</v>
       </c>
       <c r="R12" t="n">
-        <v>77.17330876657196</v>
+        <v>77.17330876657185</v>
       </c>
       <c r="S12" t="n">
-        <v>80.16355735797401</v>
+        <v>80.16355735797399</v>
       </c>
       <c r="T12" t="n">
-        <v>77.90598160754611</v>
+        <v>77.90598160754594</v>
       </c>
       <c r="U12" t="n">
-        <v>78.87747768061422</v>
+        <v>78.87747768061419</v>
       </c>
       <c r="V12" t="n">
-        <v>73.20755983766045</v>
+        <v>73.20755983766053</v>
       </c>
       <c r="W12" t="n">
-        <v>79.7615621773422</v>
+        <v>79.76156217734204</v>
       </c>
       <c r="X12" t="n">
-        <v>80.05845697001466</v>
+        <v>80.05845697001452</v>
       </c>
       <c r="Y12" t="n">
-        <v>83.16653999562779</v>
+        <v>83.16653999562764</v>
       </c>
       <c r="Z12" t="n">
-        <v>79.75154645600846</v>
+        <v>79.75154645600834</v>
       </c>
       <c r="AA12" t="n">
-        <v>78.48190514925857</v>
+        <v>78.48190514925842</v>
       </c>
       <c r="AB12" t="n">
-        <v>91.8576995782162</v>
+        <v>91.85769957821604</v>
       </c>
     </row>
     <row r="13">
@@ -5982,85 +5982,85 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>77.2622890496939</v>
+        <v>77.26228904969372</v>
       </c>
       <c r="C13" t="n">
-        <v>77.91217115587926</v>
+        <v>77.91217115587905</v>
       </c>
       <c r="D13" t="n">
-        <v>77.91217115587926</v>
+        <v>77.91217115587905</v>
       </c>
       <c r="E13" t="n">
-        <v>77.56612810465015</v>
+        <v>77.56612810464999</v>
       </c>
       <c r="F13" t="n">
-        <v>77.36353308650982</v>
+        <v>77.36353308650975</v>
       </c>
       <c r="G13" t="n">
-        <v>78.04692844418821</v>
+        <v>78.04692844418808</v>
       </c>
       <c r="H13" t="n">
-        <v>77.91217115587926</v>
+        <v>77.91217115587905</v>
       </c>
       <c r="I13" t="n">
-        <v>77.91217115587926</v>
+        <v>77.91217115587905</v>
       </c>
       <c r="J13" t="n">
-        <v>77.07711957813129</v>
+        <v>77.07711957813119</v>
       </c>
       <c r="K13" t="n">
-        <v>77.91217115587926</v>
+        <v>77.91217115587905</v>
       </c>
       <c r="L13" t="n">
-        <v>77.91217115587926</v>
+        <v>77.91217115587905</v>
       </c>
       <c r="M13" t="n">
-        <v>77.91217115587938</v>
+        <v>77.91217115587916</v>
       </c>
       <c r="N13" t="n">
-        <v>77.40840380068825</v>
+        <v>77.40840380068815</v>
       </c>
       <c r="O13" t="n">
-        <v>77.5468434440558</v>
+        <v>77.5468434440557</v>
       </c>
       <c r="P13" t="n">
-        <v>77.51290854229322</v>
+        <v>77.51290854229305</v>
       </c>
       <c r="Q13" t="n">
-        <v>77.13457238298247</v>
+        <v>77.13457238298241</v>
       </c>
       <c r="R13" t="n">
-        <v>77.91217115587926</v>
+        <v>77.91217115587905</v>
       </c>
       <c r="S13" t="n">
-        <v>77.91217115587926</v>
+        <v>77.91217115587905</v>
       </c>
       <c r="T13" t="n">
-        <v>77.91217115587926</v>
+        <v>77.91217115587905</v>
       </c>
       <c r="U13" t="n">
         <v>77.59481136513494</v>
       </c>
       <c r="V13" t="n">
-        <v>72.16312081564679</v>
+        <v>72.16312081564666</v>
       </c>
       <c r="W13" t="n">
-        <v>77.91229887637601</v>
+        <v>77.91229887637589</v>
       </c>
       <c r="X13" t="n">
-        <v>77.19413536937532</v>
+        <v>77.19413536937519</v>
       </c>
       <c r="Y13" t="n">
-        <v>78.55805870289457</v>
+        <v>78.55805870289451</v>
       </c>
       <c r="Z13" t="n">
-        <v>77.25021715591804</v>
+        <v>77.25021715591794</v>
       </c>
       <c r="AA13" t="n">
-        <v>77.91217115587926</v>
+        <v>77.91217115587905</v>
       </c>
       <c r="AB13" t="n">
-        <v>78.59102735808651</v>
+        <v>78.59102735808645</v>
       </c>
     </row>
     <row r="14">
@@ -6070,43 +6070,43 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>73.9181314709034</v>
+        <v>73.91813147090342</v>
       </c>
       <c r="C14" t="n">
-        <v>73.9181314709034</v>
+        <v>73.91813147090342</v>
       </c>
       <c r="D14" t="n">
-        <v>73.9181314709034</v>
+        <v>73.91813147090342</v>
       </c>
       <c r="E14" t="n">
-        <v>73.9181314709034</v>
+        <v>73.91813147090342</v>
       </c>
       <c r="F14" t="n">
-        <v>73.9181314709034</v>
+        <v>73.91813147090342</v>
       </c>
       <c r="G14" t="n">
         <v>73.88457482995778</v>
       </c>
       <c r="H14" t="n">
-        <v>73.9181314709034</v>
+        <v>73.91813147090342</v>
       </c>
       <c r="I14" t="n">
-        <v>73.9181314709034</v>
+        <v>73.91813147090342</v>
       </c>
       <c r="J14" t="n">
-        <v>73.88580350680087</v>
+        <v>73.88580350680088</v>
       </c>
       <c r="K14" t="n">
-        <v>73.9181314709034</v>
+        <v>73.91813147090342</v>
       </c>
       <c r="L14" t="n">
-        <v>73.9181314709034</v>
+        <v>73.91813147090342</v>
       </c>
       <c r="M14" t="n">
-        <v>73.9181314709034</v>
+        <v>73.91813147090342</v>
       </c>
       <c r="N14" t="n">
-        <v>73.9181314709034</v>
+        <v>73.91813147090342</v>
       </c>
       <c r="O14" t="n">
         <v>73.88457482995778</v>
@@ -6115,22 +6115,22 @@
         <v>73.88457482995778</v>
       </c>
       <c r="Q14" t="n">
-        <v>73.9181314709034</v>
+        <v>73.91813147090342</v>
       </c>
       <c r="R14" t="n">
-        <v>73.9181314709034</v>
+        <v>73.91813147090342</v>
       </c>
       <c r="S14" t="n">
         <v>73.78765645070207</v>
       </c>
       <c r="T14" t="n">
-        <v>73.9181314709034</v>
+        <v>73.91813147090342</v>
       </c>
       <c r="U14" t="n">
         <v>73.88457482995778</v>
       </c>
       <c r="V14" t="n">
-        <v>73.8863567124728</v>
+        <v>73.88635671247282</v>
       </c>
       <c r="W14" t="n">
         <v>73.88457482995778</v>
@@ -6139,16 +6139,16 @@
         <v>73.88457482995778</v>
       </c>
       <c r="Y14" t="n">
-        <v>73.9181314709034</v>
+        <v>73.91813147090342</v>
       </c>
       <c r="Z14" t="n">
-        <v>73.9181314709034</v>
+        <v>73.91813147090342</v>
       </c>
       <c r="AA14" t="n">
-        <v>73.9181314709034</v>
+        <v>73.91813147090342</v>
       </c>
       <c r="AB14" t="n">
-        <v>73.9181314709034</v>
+        <v>73.91813147090342</v>
       </c>
     </row>
     <row r="15">
@@ -6173,25 +6173,25 @@
         <v>69.14508287774859</v>
       </c>
       <c r="G15" t="n">
-        <v>76.50833021480292</v>
+        <v>76.50833021480284</v>
       </c>
       <c r="H15" t="n">
         <v>66.3964686412248</v>
       </c>
       <c r="I15" t="n">
-        <v>68.23266310295399</v>
+        <v>68.23266310295401</v>
       </c>
       <c r="J15" t="n">
-        <v>72.26051112680116</v>
+        <v>72.26051112680111</v>
       </c>
       <c r="K15" t="n">
         <v>68.46467862522591</v>
       </c>
       <c r="L15" t="n">
-        <v>67.21850850747954</v>
+        <v>67.21850850747951</v>
       </c>
       <c r="M15" t="n">
-        <v>79.7759329543388</v>
+        <v>79.77593295433877</v>
       </c>
       <c r="N15" t="n">
         <v>67.27110130234345</v>
@@ -6212,16 +6212,16 @@
         <v>69.44900251091111</v>
       </c>
       <c r="T15" t="n">
-        <v>67.19142676048308</v>
+        <v>67.19142676048307</v>
       </c>
       <c r="U15" t="n">
-        <v>68.12936619260569</v>
+        <v>68.12936619260566</v>
       </c>
       <c r="V15" t="n">
         <v>68.03248040597239</v>
       </c>
       <c r="W15" t="n">
-        <v>69.01345068933362</v>
+        <v>69.01345068933364</v>
       </c>
       <c r="X15" t="n">
         <v>69.31034548200611</v>
@@ -6246,7 +6246,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>66.54773420263091</v>
+        <v>66.54773420263092</v>
       </c>
       <c r="C16" t="n">
         <v>67.19761630881621</v>
@@ -6270,7 +6270,7 @@
         <v>67.19761630881621</v>
       </c>
       <c r="J16" t="n">
-        <v>67.1652883447137</v>
+        <v>67.16528834471372</v>
       </c>
       <c r="K16" t="n">
         <v>67.19761630881621</v>
@@ -6279,7 +6279,7 @@
         <v>67.19761630881621</v>
       </c>
       <c r="M16" t="n">
-        <v>67.19761630881631</v>
+        <v>67.19761630881632</v>
       </c>
       <c r="N16" t="n">
         <v>66.69384895362535</v>
@@ -6303,7 +6303,7 @@
         <v>67.19761630881621</v>
       </c>
       <c r="U16" t="n">
-        <v>66.84669987712647</v>
+        <v>66.84669987712648</v>
       </c>
       <c r="V16" t="n">
         <v>66.98804138395869</v>
@@ -6312,7 +6312,7 @@
         <v>67.16418738836747</v>
       </c>
       <c r="X16" t="n">
-        <v>66.44602388136676</v>
+        <v>66.44602388136677</v>
       </c>
       <c r="Y16" t="n">
         <v>67.84350385583163</v>
@@ -6496,79 +6496,79 @@
         <v>10.8708472963734</v>
       </c>
       <c r="D2" t="n">
-        <v>15.04194506781798</v>
+        <v>15.04194506781789</v>
       </c>
       <c r="E2" t="n">
-        <v>10.30837012148538</v>
+        <v>10.30837012148539</v>
       </c>
       <c r="F2" t="n">
-        <v>17.16082369631989</v>
+        <v>17.16082369631986</v>
       </c>
       <c r="G2" t="n">
-        <v>27.54604036878368</v>
+        <v>27.5460403687835</v>
       </c>
       <c r="H2" t="n">
-        <v>11.13203496219087</v>
+        <v>11.13203496219085</v>
       </c>
       <c r="I2" t="n">
-        <v>15.02034777867639</v>
+        <v>15.02034777867635</v>
       </c>
       <c r="J2" t="n">
-        <v>20.75754916869344</v>
+        <v>20.75754916869337</v>
       </c>
       <c r="K2" t="n">
         <v>15.32951675497808</v>
       </c>
       <c r="L2" t="n">
-        <v>12.54874490020054</v>
+        <v>12.54874490020046</v>
       </c>
       <c r="M2" t="n">
-        <v>32.19869710733998</v>
+        <v>32.19869710733992</v>
       </c>
       <c r="N2" t="n">
-        <v>12.09373520055707</v>
+        <v>12.09373520055703</v>
       </c>
       <c r="O2" t="n">
-        <v>14.0399586144773</v>
+        <v>14.03995861447724</v>
       </c>
       <c r="P2" t="n">
-        <v>19.62274418213163</v>
+        <v>19.62274418213161</v>
       </c>
       <c r="Q2" t="n">
-        <v>12.80096779021266</v>
+        <v>12.80096779021262</v>
       </c>
       <c r="R2" t="n">
-        <v>12.84123139663837</v>
+        <v>12.84123139663831</v>
       </c>
       <c r="S2" t="n">
-        <v>16.37909347077527</v>
+        <v>16.37909347077525</v>
       </c>
       <c r="T2" t="n">
-        <v>13.01050815000734</v>
+        <v>13.0105081500073</v>
       </c>
       <c r="U2" t="n">
-        <v>13.08767567458254</v>
+        <v>13.08767567458247</v>
       </c>
       <c r="V2" t="n">
-        <v>15.65706996235103</v>
+        <v>15.65706996235097</v>
       </c>
       <c r="W2" t="n">
-        <v>15.8589366068061</v>
+        <v>15.85893660680613</v>
       </c>
       <c r="X2" t="n">
-        <v>16.9198251053321</v>
+        <v>16.91982510533204</v>
       </c>
       <c r="Y2" t="n">
-        <v>28.31341075819102</v>
+        <v>28.31341075819093</v>
       </c>
       <c r="Z2" t="n">
-        <v>15.18866409129312</v>
+        <v>15.18866409129308</v>
       </c>
       <c r="AA2" t="n">
-        <v>13.91926507767585</v>
+        <v>13.91926507767583</v>
       </c>
       <c r="AB2" t="n">
-        <v>36.21562771399688</v>
+        <v>36.21562771399684</v>
       </c>
     </row>
     <row r="3">
@@ -6578,7 +6578,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>11.19187398084698</v>
+        <v>11.19187398084686</v>
       </c>
       <c r="C3" t="n">
         <v>12.41907699494234</v>
@@ -6587,13 +6587,13 @@
         <v>12.41325688882963</v>
       </c>
       <c r="E3" t="n">
-        <v>11.71033525408429</v>
+        <v>11.71033525408428</v>
       </c>
       <c r="F3" t="n">
         <v>11.37399294675472</v>
       </c>
       <c r="G3" t="n">
-        <v>12.66651859137586</v>
+        <v>12.66651859137591</v>
       </c>
       <c r="H3" t="n">
         <v>12.41325688882963</v>
@@ -6602,7 +6602,7 @@
         <v>12.41325688882963</v>
       </c>
       <c r="J3" t="n">
-        <v>12.39501901807051</v>
+        <v>12.39501901807052</v>
       </c>
       <c r="K3" t="n">
         <v>12.41325688882963</v>
@@ -6611,19 +6611,19 @@
         <v>12.41325688882963</v>
       </c>
       <c r="M3" t="n">
-        <v>12.44461898581032</v>
+        <v>12.4446189858103</v>
       </c>
       <c r="N3" t="n">
-        <v>11.46648080225444</v>
+        <v>11.46648080225434</v>
       </c>
       <c r="O3" t="n">
-        <v>11.72666309160782</v>
+        <v>11.72666309160781</v>
       </c>
       <c r="P3" t="n">
-        <v>11.66288612559707</v>
+        <v>11.66288612559711</v>
       </c>
       <c r="Q3" t="n">
-        <v>10.95184436270265</v>
+        <v>10.95184436270271</v>
       </c>
       <c r="R3" t="n">
         <v>12.41325688882963</v>
@@ -6635,28 +6635,28 @@
         <v>12.41325688882963</v>
       </c>
       <c r="U3" t="n">
-        <v>11.81687391961196</v>
+        <v>11.81687391961201</v>
       </c>
       <c r="V3" t="n">
-        <v>12.03098859621923</v>
+        <v>12.03098859621915</v>
       </c>
       <c r="W3" t="n">
         <v>12.4134969256489</v>
       </c>
       <c r="X3" t="n">
-        <v>11.06378653319379</v>
+        <v>11.06378653319378</v>
       </c>
       <c r="Y3" t="n">
-        <v>13.62723565432584</v>
+        <v>13.62723565432587</v>
       </c>
       <c r="Z3" t="n">
-        <v>11.16918616626534</v>
+        <v>11.16918616626542</v>
       </c>
       <c r="AA3" t="n">
         <v>12.41325688882963</v>
       </c>
       <c r="AB3" t="n">
-        <v>13.73645766734679</v>
+        <v>13.73645766734678</v>
       </c>
     </row>
     <row r="4">
@@ -6666,85 +6666,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>23.59771363714601</v>
+        <v>23.59771363714618</v>
       </c>
       <c r="C4" t="n">
-        <v>22.2175771451622</v>
+        <v>22.2175771451623</v>
       </c>
       <c r="D4" t="n">
-        <v>23.7341945575731</v>
+        <v>23.73419455757302</v>
       </c>
       <c r="E4" t="n">
-        <v>21.97545241799384</v>
+        <v>21.97545241799397</v>
       </c>
       <c r="F4" t="n">
-        <v>24.50131629410935</v>
+        <v>24.50131629410939</v>
       </c>
       <c r="G4" t="n">
-        <v>28.29179046427489</v>
+        <v>28.29179046427478</v>
       </c>
       <c r="H4" t="n">
-        <v>22.30907823655449</v>
+        <v>22.30907823655456</v>
       </c>
       <c r="I4" t="n">
         <v>23.72632259928915</v>
       </c>
       <c r="J4" t="n">
-        <v>24.87128022485116</v>
+        <v>24.87128022485121</v>
       </c>
       <c r="K4" t="n">
-        <v>23.83901106070569</v>
+        <v>23.83901106070574</v>
       </c>
       <c r="L4" t="n">
-        <v>22.82545237311101</v>
+        <v>22.82545237311094</v>
       </c>
       <c r="M4" t="n">
-        <v>30.00756019212829</v>
+        <v>30.00756019212832</v>
       </c>
       <c r="N4" t="n">
-        <v>22.65960668058461</v>
+        <v>22.65960668058455</v>
       </c>
       <c r="O4" t="n">
-        <v>23.36898226124938</v>
+        <v>23.3689822612493</v>
       </c>
       <c r="P4" t="n">
-        <v>25.40384204428144</v>
+        <v>25.40384204428136</v>
       </c>
       <c r="Q4" t="n">
-        <v>22.91738465476971</v>
+        <v>22.91738465476965</v>
       </c>
       <c r="R4" t="n">
         <v>22.93206026651276</v>
       </c>
       <c r="S4" t="n">
-        <v>24.22156944886174</v>
+        <v>24.22156944886166</v>
       </c>
       <c r="T4" t="n">
-        <v>22.99375965536775</v>
+        <v>22.99375965536767</v>
       </c>
       <c r="U4" t="n">
-        <v>23.02188631192858</v>
+        <v>23.02188631192851</v>
       </c>
       <c r="V4" t="n">
-        <v>17.69240489244387</v>
+        <v>17.69240489244378</v>
       </c>
       <c r="W4" t="n">
-        <v>24.03197837993526</v>
+        <v>24.0319783799355</v>
       </c>
       <c r="X4" t="n">
-        <v>24.41865978006627</v>
+        <v>24.41865978006619</v>
       </c>
       <c r="Y4" t="n">
-        <v>28.57148796029583</v>
+        <v>28.57148796029573</v>
       </c>
       <c r="Z4" t="n">
-        <v>23.78767191876802</v>
+        <v>23.78767191876791</v>
       </c>
       <c r="AA4" t="n">
-        <v>23.3249908843403</v>
+        <v>23.32499088434046</v>
       </c>
       <c r="AB4" t="n">
-        <v>31.48185375387844</v>
+        <v>31.48185375387841</v>
       </c>
     </row>
     <row r="5">
@@ -6754,85 +6754,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>22.3308888561894</v>
+        <v>22.33088885618947</v>
       </c>
       <c r="C5" t="n">
-        <v>22.7818886900596</v>
+        <v>22.78188869005965</v>
       </c>
       <c r="D5" t="n">
-        <v>22.77606858394686</v>
+        <v>22.77606858394697</v>
       </c>
       <c r="E5" t="n">
-        <v>22.48645224612039</v>
+        <v>22.48645224612048</v>
       </c>
       <c r="F5" t="n">
-        <v>22.39208443829028</v>
+        <v>22.39208443829038</v>
       </c>
       <c r="G5" t="n">
-        <v>22.86837950057591</v>
+        <v>22.86837950057601</v>
       </c>
       <c r="H5" t="n">
-        <v>22.77606858394686</v>
+        <v>22.77606858394697</v>
       </c>
       <c r="I5" t="n">
-        <v>22.77606858394686</v>
+        <v>22.77606858394697</v>
       </c>
       <c r="J5" t="n">
-        <v>21.8232361827359</v>
+        <v>21.82323618273595</v>
       </c>
       <c r="K5" t="n">
-        <v>22.77606858394686</v>
+        <v>22.77606858394697</v>
       </c>
       <c r="L5" t="n">
-        <v>22.77606858394686</v>
+        <v>22.77606858394697</v>
       </c>
       <c r="M5" t="n">
-        <v>22.80743068092737</v>
+        <v>22.80743068092746</v>
       </c>
       <c r="N5" t="n">
-        <v>22.43097981799635</v>
+        <v>22.4309798179963</v>
       </c>
       <c r="O5" t="n">
-        <v>22.52581320725095</v>
+        <v>22.52581320725092</v>
       </c>
       <c r="P5" t="n">
         <v>22.50256725204697</v>
       </c>
       <c r="Q5" t="n">
-        <v>22.24340087894588</v>
+        <v>22.24340087894599</v>
       </c>
       <c r="R5" t="n">
-        <v>22.77606858394686</v>
+        <v>22.77606858394697</v>
       </c>
       <c r="S5" t="n">
-        <v>22.77606858394686</v>
+        <v>22.77606858394697</v>
       </c>
       <c r="T5" t="n">
-        <v>22.77606858394686</v>
+        <v>22.77606858394697</v>
       </c>
       <c r="U5" t="n">
-        <v>22.55869399474943</v>
+        <v>22.55869399474951</v>
       </c>
       <c r="V5" t="n">
-        <v>16.3707408140859</v>
+        <v>16.37074081408591</v>
       </c>
       <c r="W5" t="n">
-        <v>22.77615607454884</v>
+        <v>22.77615607454897</v>
       </c>
       <c r="X5" t="n">
-        <v>22.28420248559856</v>
+        <v>22.2842024855985</v>
       </c>
       <c r="Y5" t="n">
-        <v>23.21854958871184</v>
+        <v>23.21854958871195</v>
       </c>
       <c r="Z5" t="n">
-        <v>22.32261941418817</v>
+        <v>22.32261941418803</v>
       </c>
       <c r="AA5" t="n">
-        <v>22.77606858394686</v>
+        <v>22.77606858394697</v>
       </c>
       <c r="AB5" t="n">
-        <v>23.28846023561616</v>
+        <v>23.28846023561611</v>
       </c>
     </row>
     <row r="6">
@@ -6842,85 +6842,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>11.27603460522693</v>
+        <v>11.27603460522689</v>
       </c>
       <c r="C6" t="n">
-        <v>9.895898113243096</v>
+        <v>9.895898113243099</v>
       </c>
       <c r="D6" t="n">
-        <v>11.41251552565397</v>
+        <v>11.41251552565388</v>
       </c>
       <c r="E6" t="n">
-        <v>9.653773386074727</v>
+        <v>9.653773386074736</v>
       </c>
       <c r="F6" t="n">
-        <v>12.17963726219025</v>
+        <v>12.17963726219023</v>
       </c>
       <c r="G6" t="n">
-        <v>15.93115565205746</v>
+        <v>15.93115565205735</v>
       </c>
       <c r="H6" t="n">
-        <v>9.987399204635382</v>
+        <v>9.98739920463537</v>
       </c>
       <c r="I6" t="n">
-        <v>11.40464356737004</v>
+        <v>11.40464356736995</v>
       </c>
       <c r="J6" t="n">
-        <v>13.44666728011802</v>
+        <v>13.44666728011806</v>
       </c>
       <c r="K6" t="n">
-        <v>11.51733202878657</v>
+        <v>11.51733202878661</v>
       </c>
       <c r="L6" t="n">
-        <v>10.50377334119189</v>
+        <v>10.5037733411918</v>
       </c>
       <c r="M6" t="n">
-        <v>17.68588116020915</v>
+        <v>17.68588116020913</v>
       </c>
       <c r="N6" t="n">
-        <v>10.33792764866552</v>
+        <v>10.33792764866542</v>
       </c>
       <c r="O6" t="n">
-        <v>11.00834744903196</v>
+        <v>11.00834744903188</v>
       </c>
       <c r="P6" t="n">
-        <v>13.04320723206403</v>
+        <v>13.04320723206391</v>
       </c>
       <c r="Q6" t="n">
-        <v>10.59570562285061</v>
+        <v>10.59570562285051</v>
       </c>
       <c r="R6" t="n">
-        <v>10.61038123459365</v>
+        <v>10.61038123459358</v>
       </c>
       <c r="S6" t="n">
-        <v>11.89989041694262</v>
+        <v>11.89989041694254</v>
       </c>
       <c r="T6" t="n">
-        <v>10.67208062344865</v>
+        <v>10.67208062344856</v>
       </c>
       <c r="U6" t="n">
-        <v>10.66125149971117</v>
+        <v>10.66125149971108</v>
       </c>
       <c r="V6" t="n">
-        <v>11.56921842633328</v>
+        <v>11.56921842633322</v>
       </c>
       <c r="W6" t="n">
-        <v>11.67134356771783</v>
+        <v>11.67134356771801</v>
       </c>
       <c r="X6" t="n">
-        <v>12.05802496784885</v>
+        <v>12.05802496784874</v>
       </c>
       <c r="Y6" t="n">
-        <v>16.24980892837671</v>
+        <v>16.24980892837659</v>
       </c>
       <c r="Z6" t="n">
-        <v>11.46599288684891</v>
+        <v>11.46599288684883</v>
       </c>
       <c r="AA6" t="n">
-        <v>11.0033118524212</v>
+        <v>11.00331185242124</v>
       </c>
       <c r="AB6" t="n">
-        <v>19.16017472195936</v>
+        <v>19.16017472195934</v>
       </c>
     </row>
     <row r="7">
@@ -6930,82 +6930,82 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>10.00920982427029</v>
+        <v>10.00920982427034</v>
       </c>
       <c r="C7" t="n">
-        <v>10.46020965814048</v>
+        <v>10.46020965814047</v>
       </c>
       <c r="D7" t="n">
-        <v>10.45438955202776</v>
+        <v>10.45438955202783</v>
       </c>
       <c r="E7" t="n">
-        <v>10.16477321420129</v>
+        <v>10.16477321420127</v>
       </c>
       <c r="F7" t="n">
         <v>10.07040540637117</v>
       </c>
       <c r="G7" t="n">
-        <v>10.50774468835848</v>
+        <v>10.50774468835853</v>
       </c>
       <c r="H7" t="n">
-        <v>10.45438955202776</v>
+        <v>10.45438955202783</v>
       </c>
       <c r="I7" t="n">
-        <v>10.45438955202776</v>
+        <v>10.45438955202783</v>
       </c>
       <c r="J7" t="n">
-        <v>10.39862323800279</v>
+        <v>10.39862323800283</v>
       </c>
       <c r="K7" t="n">
-        <v>10.45438955202776</v>
+        <v>10.45438955202783</v>
       </c>
       <c r="L7" t="n">
-        <v>10.45438955202776</v>
+        <v>10.45438955202783</v>
       </c>
       <c r="M7" t="n">
-        <v>10.48575164900828</v>
+        <v>10.48575164900826</v>
       </c>
       <c r="N7" t="n">
-        <v>10.10930078607722</v>
+        <v>10.10930078607709</v>
       </c>
       <c r="O7" t="n">
-        <v>10.16517839503353</v>
+        <v>10.16517839503346</v>
       </c>
       <c r="P7" t="n">
-        <v>10.14193243982955</v>
+        <v>10.14193243982953</v>
       </c>
       <c r="Q7" t="n">
-        <v>9.921721847026761</v>
+        <v>9.921721847026737</v>
       </c>
       <c r="R7" t="n">
-        <v>10.45438955202776</v>
+        <v>10.45438955202783</v>
       </c>
       <c r="S7" t="n">
-        <v>10.45438955202776</v>
+        <v>10.45438955202783</v>
       </c>
       <c r="T7" t="n">
-        <v>10.45438955202776</v>
+        <v>10.45438955202783</v>
       </c>
       <c r="U7" t="n">
-        <v>10.19805918253199</v>
+        <v>10.19805918253197</v>
       </c>
       <c r="V7" t="n">
-        <v>10.2475543479754</v>
+        <v>10.24755434797538</v>
       </c>
       <c r="W7" t="n">
-        <v>10.41552126233143</v>
+        <v>10.41552126233148</v>
       </c>
       <c r="X7" t="n">
-        <v>9.923567673381143</v>
+        <v>9.923567673381038</v>
       </c>
       <c r="Y7" t="n">
         <v>10.89687055679274</v>
       </c>
       <c r="Z7" t="n">
-        <v>10.00094038226906</v>
+        <v>10.0009403822689</v>
       </c>
       <c r="AA7" t="n">
-        <v>10.45438955202776</v>
+        <v>10.45438955202783</v>
       </c>
       <c r="AB7" t="n">
         <v>10.96678120369704</v>
@@ -7018,85 +7018,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>82.47344987630818</v>
+        <v>82.47344987630817</v>
       </c>
       <c r="C8" t="n">
-        <v>82.47344987630818</v>
+        <v>82.47344987630817</v>
       </c>
       <c r="D8" t="n">
-        <v>82.47344987630818</v>
+        <v>82.47344987630817</v>
       </c>
       <c r="E8" t="n">
-        <v>82.47344987630818</v>
+        <v>82.47344987630817</v>
       </c>
       <c r="F8" t="n">
-        <v>82.47344987630818</v>
+        <v>82.47344987630817</v>
       </c>
       <c r="G8" t="n">
-        <v>82.47344987630818</v>
+        <v>82.47344987630817</v>
       </c>
       <c r="H8" t="n">
-        <v>82.47344987630818</v>
+        <v>82.47344987630817</v>
       </c>
       <c r="I8" t="n">
-        <v>82.47344987630818</v>
+        <v>82.47344987630817</v>
       </c>
       <c r="J8" t="n">
-        <v>82.47344987630818</v>
+        <v>82.47344987630817</v>
       </c>
       <c r="K8" t="n">
-        <v>82.47344987630818</v>
+        <v>82.47344987630817</v>
       </c>
       <c r="L8" t="n">
         <v>82.47344987630818</v>
       </c>
       <c r="M8" t="n">
-        <v>82.47344987630818</v>
+        <v>82.47344987630817</v>
       </c>
       <c r="N8" t="n">
-        <v>82.47344987630818</v>
+        <v>82.47344987630817</v>
       </c>
       <c r="O8" t="n">
-        <v>82.47344987630818</v>
+        <v>82.47344987630817</v>
       </c>
       <c r="P8" t="n">
-        <v>82.47344987630818</v>
+        <v>82.47344987630817</v>
       </c>
       <c r="Q8" t="n">
-        <v>82.47344987630818</v>
+        <v>82.47344987630817</v>
       </c>
       <c r="R8" t="n">
-        <v>82.47344987630818</v>
+        <v>82.47344987630817</v>
       </c>
       <c r="S8" t="n">
         <v>82.2489789175913</v>
       </c>
       <c r="T8" t="n">
-        <v>82.47344987630818</v>
+        <v>82.47344987630817</v>
       </c>
       <c r="U8" t="n">
-        <v>82.47344987630818</v>
+        <v>82.47344987630817</v>
       </c>
       <c r="V8" t="n">
-        <v>82.47344987630818</v>
+        <v>82.47344987630817</v>
       </c>
       <c r="W8" t="n">
-        <v>82.47344987630818</v>
+        <v>82.47344987630817</v>
       </c>
       <c r="X8" t="n">
-        <v>82.47344987630818</v>
+        <v>82.47344987630817</v>
       </c>
       <c r="Y8" t="n">
-        <v>82.47344987630818</v>
+        <v>82.47344987630817</v>
       </c>
       <c r="Z8" t="n">
-        <v>82.47344987630818</v>
+        <v>82.47344987630817</v>
       </c>
       <c r="AA8" t="n">
-        <v>82.47344987630818</v>
+        <v>82.47344987630817</v>
       </c>
       <c r="AB8" t="n">
-        <v>82.47344987630818</v>
+        <v>82.47344987630817</v>
       </c>
     </row>
     <row r="9">
@@ -7106,22 +7106,22 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>71.27873602169581</v>
+        <v>71.27873602169583</v>
       </c>
       <c r="C9" t="n">
-        <v>67.19220739010888</v>
+        <v>67.19220739010886</v>
       </c>
       <c r="D9" t="n">
-        <v>71.68115352146202</v>
+        <v>71.68115352146198</v>
       </c>
       <c r="E9" t="n">
         <v>66.6504648694054</v>
       </c>
       <c r="F9" t="n">
-        <v>73.96708637836518</v>
+        <v>73.96708637836512</v>
       </c>
       <c r="G9" t="n">
-        <v>85.11934212673258</v>
+        <v>85.11934212673243</v>
       </c>
       <c r="H9" t="n">
         <v>67.47916144091442</v>
@@ -7130,25 +7130,25 @@
         <v>71.657942850249</v>
       </c>
       <c r="J9" t="n">
-        <v>77.84333063168378</v>
+        <v>77.84333063168376</v>
       </c>
       <c r="K9" t="n">
-        <v>71.99020767344813</v>
+        <v>71.9902076734481</v>
       </c>
       <c r="L9" t="n">
-        <v>69.00170384703829</v>
+        <v>69.00170384703827</v>
       </c>
       <c r="M9" t="n">
-        <v>90.08586129499477</v>
+        <v>90.08586129499474</v>
       </c>
       <c r="N9" t="n">
-        <v>68.51270356242249</v>
+        <v>68.51270356242247</v>
       </c>
       <c r="O9" t="n">
         <v>70.60431568427137</v>
       </c>
       <c r="P9" t="n">
-        <v>76.60415202550007</v>
+        <v>76.6041520255001</v>
       </c>
       <c r="Q9" t="n">
         <v>69.27276854104201</v>
@@ -7157,34 +7157,34 @@
         <v>69.31603995924972</v>
       </c>
       <c r="S9" t="n">
-        <v>73.11819090798838</v>
+        <v>73.11819090798836</v>
       </c>
       <c r="T9" t="n">
         <v>69.4979621922069</v>
       </c>
       <c r="U9" t="n">
-        <v>69.58089436158681</v>
+        <v>69.58089436158677</v>
       </c>
       <c r="V9" t="n">
-        <v>72.39400788532059</v>
+        <v>72.39400788532058</v>
       </c>
       <c r="W9" t="n">
         <v>72.55917677109171</v>
       </c>
       <c r="X9" t="n">
-        <v>73.6993168123511</v>
+        <v>73.69931681235107</v>
       </c>
       <c r="Y9" t="n">
-        <v>85.94403737854816</v>
+        <v>85.94403737854806</v>
       </c>
       <c r="Z9" t="n">
         <v>71.83883289465808</v>
       </c>
       <c r="AA9" t="n">
-        <v>70.47460597941576</v>
+        <v>70.47460597941574</v>
       </c>
       <c r="AB9" t="n">
-        <v>94.38567111928911</v>
+        <v>94.38567111928906</v>
       </c>
     </row>
     <row r="10">
@@ -7194,7 +7194,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>67.54347061317355</v>
+        <v>67.54347061317354</v>
       </c>
       <c r="C10" t="n">
         <v>68.85609447612968</v>
@@ -7209,7 +7209,7 @@
         <v>67.74796207007309</v>
       </c>
       <c r="G10" t="n">
-        <v>69.12827558506967</v>
+        <v>69.12827558506966</v>
       </c>
       <c r="H10" t="n">
         <v>68.85609447612968</v>
@@ -7227,7 +7227,7 @@
         <v>68.85609447612968</v>
       </c>
       <c r="M10" t="n">
-        <v>68.85609447612997</v>
+        <v>68.85609447612995</v>
       </c>
       <c r="N10" t="n">
         <v>67.83859138517238</v>
@@ -7239,7 +7239,7 @@
         <v>68.04966877339044</v>
       </c>
       <c r="Q10" t="n">
-        <v>67.28551006490224</v>
+        <v>67.28551006490223</v>
       </c>
       <c r="R10" t="n">
         <v>68.85609447612968</v>
@@ -7263,7 +7263,7 @@
         <v>67.40581465021897</v>
       </c>
       <c r="Y10" t="n">
-        <v>70.16076108501835</v>
+        <v>70.16076108501834</v>
       </c>
       <c r="Z10" t="n">
         <v>67.51908795100962</v>
@@ -7282,85 +7282,85 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>84.46006879728469</v>
+        <v>84.46006879728476</v>
       </c>
       <c r="C11" t="n">
-        <v>84.46006879728469</v>
+        <v>84.46006879728476</v>
       </c>
       <c r="D11" t="n">
-        <v>84.46006879728469</v>
+        <v>84.46006879728476</v>
       </c>
       <c r="E11" t="n">
-        <v>84.46006879728469</v>
+        <v>84.46006879728476</v>
       </c>
       <c r="F11" t="n">
-        <v>84.46006879728469</v>
+        <v>84.46006879728476</v>
       </c>
       <c r="G11" t="n">
-        <v>84.46006879728469</v>
+        <v>84.46006879728476</v>
       </c>
       <c r="H11" t="n">
-        <v>84.46006879728469</v>
+        <v>84.46006879728476</v>
       </c>
       <c r="I11" t="n">
-        <v>84.46006879728469</v>
+        <v>84.46006879728476</v>
       </c>
       <c r="J11" t="n">
-        <v>83.6564362894575</v>
+        <v>83.65643628945752</v>
       </c>
       <c r="K11" t="n">
-        <v>84.46006879728469</v>
+        <v>84.46006879728476</v>
       </c>
       <c r="L11" t="n">
-        <v>84.46006879728469</v>
+        <v>84.46006879728478</v>
       </c>
       <c r="M11" t="n">
-        <v>84.46006879728469</v>
+        <v>84.46006879728476</v>
       </c>
       <c r="N11" t="n">
-        <v>84.46006879728469</v>
+        <v>84.46006879728476</v>
       </c>
       <c r="O11" t="n">
-        <v>84.46006879728469</v>
+        <v>84.46006879728476</v>
       </c>
       <c r="P11" t="n">
-        <v>84.46006879728469</v>
+        <v>84.46006879728476</v>
       </c>
       <c r="Q11" t="n">
-        <v>84.46006879728469</v>
+        <v>84.46006879728476</v>
       </c>
       <c r="R11" t="n">
-        <v>84.46006879728469</v>
+        <v>84.46006879728476</v>
       </c>
       <c r="S11" t="n">
-        <v>84.34973561195727</v>
+        <v>84.34973561195734</v>
       </c>
       <c r="T11" t="n">
-        <v>84.46006879728469</v>
+        <v>84.46006879728476</v>
       </c>
       <c r="U11" t="n">
-        <v>84.46006879728469</v>
+        <v>84.46006879728476</v>
       </c>
       <c r="V11" t="n">
-        <v>79.09843869185744</v>
+        <v>79.09843869185757</v>
       </c>
       <c r="W11" t="n">
-        <v>84.46006879728469</v>
+        <v>84.46006879728476</v>
       </c>
       <c r="X11" t="n">
-        <v>84.46006879728469</v>
+        <v>84.46006879728476</v>
       </c>
       <c r="Y11" t="n">
-        <v>84.46006879728469</v>
+        <v>84.46006879728476</v>
       </c>
       <c r="Z11" t="n">
-        <v>84.46006879728469</v>
+        <v>84.46006879728476</v>
       </c>
       <c r="AA11" t="n">
-        <v>84.46006879728469</v>
+        <v>84.46006879728476</v>
       </c>
       <c r="AB11" t="n">
-        <v>84.46006879728469</v>
+        <v>84.46006879728476</v>
       </c>
     </row>
     <row r="12">
@@ -7370,85 +7370,85 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>78.95758221519596</v>
+        <v>78.95758221519597</v>
       </c>
       <c r="C12" t="n">
-        <v>76.94894945739094</v>
+        <v>76.94894945739102</v>
       </c>
       <c r="D12" t="n">
-        <v>79.15538065128099</v>
+        <v>79.15538065128109</v>
       </c>
       <c r="E12" t="n">
-        <v>76.68266922997</v>
+        <v>76.68266922997007</v>
       </c>
       <c r="F12" t="n">
-        <v>80.27897479008809</v>
+        <v>80.27897479008816</v>
       </c>
       <c r="G12" t="n">
-        <v>85.76059213309237</v>
+        <v>85.76059213309235</v>
       </c>
       <c r="H12" t="n">
-        <v>77.08999467165366</v>
+        <v>77.08999467165376</v>
       </c>
       <c r="I12" t="n">
-        <v>79.14397201604741</v>
+        <v>79.1439720160474</v>
       </c>
       <c r="J12" t="n">
-        <v>81.38061491984564</v>
+        <v>81.38061491984567</v>
       </c>
       <c r="K12" t="n">
-        <v>79.30728862736036</v>
+        <v>79.30728862736046</v>
       </c>
       <c r="L12" t="n">
-        <v>77.83836298808953</v>
+        <v>77.83836298808959</v>
       </c>
       <c r="M12" t="n">
-        <v>88.20176262105348</v>
+        <v>88.20176262105352</v>
       </c>
       <c r="N12" t="n">
-        <v>77.59800691113387</v>
+        <v>77.59800691113394</v>
       </c>
       <c r="O12" t="n">
-        <v>78.62608746637429</v>
+        <v>78.62608746637433</v>
       </c>
       <c r="P12" t="n">
-        <v>81.57515962588614</v>
+        <v>81.57515962588622</v>
       </c>
       <c r="Q12" t="n">
-        <v>77.97159817935963</v>
+        <v>77.97159817935969</v>
       </c>
       <c r="R12" t="n">
-        <v>77.9928671819593</v>
+        <v>77.99286718195926</v>
       </c>
       <c r="S12" t="n">
-        <v>79.86172107587907</v>
+        <v>79.86172107587913</v>
       </c>
       <c r="T12" t="n">
-        <v>78.08228658640591</v>
+        <v>78.08228658640598</v>
       </c>
       <c r="U12" t="n">
-        <v>78.12304985692477</v>
+        <v>78.12304985692484</v>
       </c>
       <c r="V12" t="n">
-        <v>74.14413659618626</v>
+        <v>74.1441365961859</v>
       </c>
       <c r="W12" t="n">
-        <v>79.58695140981882</v>
+        <v>79.58695140981878</v>
       </c>
       <c r="X12" t="n">
-        <v>80.14735923803205</v>
+        <v>80.14735923803208</v>
       </c>
       <c r="Y12" t="n">
         <v>86.1659508243784</v>
       </c>
       <c r="Z12" t="n">
-        <v>79.23288407357043</v>
+        <v>79.23288407357052</v>
       </c>
       <c r="AA12" t="n">
-        <v>78.56233184744517</v>
+        <v>78.56233184744531</v>
       </c>
       <c r="AB12" t="n">
-        <v>90.31522850959558</v>
+        <v>90.31522850959563</v>
       </c>
     </row>
     <row r="13">
@@ -7458,85 +7458,85 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>77.12160426543664</v>
+        <v>77.12160426543667</v>
       </c>
       <c r="C13" t="n">
-        <v>77.76679227890868</v>
+        <v>77.76679227890878</v>
       </c>
       <c r="D13" t="n">
-        <v>77.76679227890868</v>
+        <v>77.76679227890878</v>
       </c>
       <c r="E13" t="n">
-        <v>77.42324869358198</v>
+        <v>77.42324869358204</v>
       </c>
       <c r="F13" t="n">
-        <v>77.222117017469</v>
+        <v>77.22211701746902</v>
       </c>
       <c r="G13" t="n">
-        <v>77.90057621651455</v>
+        <v>77.90057621651462</v>
       </c>
       <c r="H13" t="n">
-        <v>77.76679227890868</v>
+        <v>77.76679227890878</v>
       </c>
       <c r="I13" t="n">
-        <v>77.76679227890868</v>
+        <v>77.76679227890878</v>
       </c>
       <c r="J13" t="n">
-        <v>76.96315977108148</v>
+        <v>76.96315977108149</v>
       </c>
       <c r="K13" t="n">
-        <v>77.76679227890868</v>
+        <v>77.76679227890878</v>
       </c>
       <c r="L13" t="n">
-        <v>77.76679227890868</v>
+        <v>77.76679227890878</v>
       </c>
       <c r="M13" t="n">
-        <v>77.76679227890885</v>
+        <v>77.76679227890892</v>
       </c>
       <c r="N13" t="n">
-        <v>77.26666363087548</v>
+        <v>77.26666363087544</v>
       </c>
       <c r="O13" t="n">
-        <v>77.40410332592225</v>
+        <v>77.40410332592228</v>
       </c>
       <c r="P13" t="n">
-        <v>77.37041353565516</v>
+        <v>77.37041353565523</v>
       </c>
       <c r="Q13" t="n">
-        <v>76.9948100950804</v>
+        <v>76.99481009508044</v>
       </c>
       <c r="R13" t="n">
-        <v>77.76679227890868</v>
+        <v>77.76679227890878</v>
       </c>
       <c r="S13" t="n">
-        <v>77.76679227890868</v>
+        <v>77.76679227890878</v>
       </c>
       <c r="T13" t="n">
-        <v>77.76679227890868</v>
+        <v>77.76679227890878</v>
       </c>
       <c r="U13" t="n">
-        <v>77.45175664130213</v>
+        <v>77.45175664130217</v>
       </c>
       <c r="V13" t="n">
-        <v>72.22868140354144</v>
+        <v>72.22868140354143</v>
       </c>
       <c r="W13" t="n">
-        <v>77.76691907688303</v>
+        <v>77.76691907688304</v>
       </c>
       <c r="X13" t="n">
-        <v>77.05394285854948</v>
+        <v>77.05394285854949</v>
       </c>
       <c r="Y13" t="n">
-        <v>78.4080690996245</v>
+        <v>78.40806909962456</v>
       </c>
       <c r="Z13" t="n">
-        <v>77.10961956684272</v>
+        <v>77.10961956684274</v>
       </c>
       <c r="AA13" t="n">
-        <v>77.76679227890868</v>
+        <v>77.76679227890878</v>
       </c>
       <c r="AB13" t="n">
-        <v>78.44074510876472</v>
+        <v>78.44074510876482</v>
       </c>
     </row>
     <row r="14">
@@ -7561,7 +7561,7 @@
         <v>73.86499463733007</v>
       </c>
       <c r="G14" t="n">
-        <v>73.83149762932081</v>
+        <v>73.83149762932079</v>
       </c>
       <c r="H14" t="n">
         <v>73.86499463733007</v>
@@ -7570,7 +7570,7 @@
         <v>73.86499463733007</v>
       </c>
       <c r="J14" t="n">
-        <v>73.83272495732184</v>
+        <v>73.83272495732183</v>
       </c>
       <c r="K14" t="n">
         <v>73.86499463733007</v>
@@ -7585,10 +7585,10 @@
         <v>73.86499463733007</v>
       </c>
       <c r="O14" t="n">
-        <v>73.83149762932081</v>
+        <v>73.83149762932079</v>
       </c>
       <c r="P14" t="n">
-        <v>73.83149762932081</v>
+        <v>73.83149762932079</v>
       </c>
       <c r="Q14" t="n">
         <v>73.86499463733007</v>
@@ -7603,16 +7603,16 @@
         <v>73.86499463733007</v>
       </c>
       <c r="U14" t="n">
-        <v>73.83149762932081</v>
+        <v>73.83149762932079</v>
       </c>
       <c r="V14" t="n">
-        <v>73.83327843768006</v>
+        <v>73.83327843768008</v>
       </c>
       <c r="W14" t="n">
-        <v>73.83149762932081</v>
+        <v>73.83149762932079</v>
       </c>
       <c r="X14" t="n">
-        <v>73.83149762932081</v>
+        <v>73.83149762932079</v>
       </c>
       <c r="Y14" t="n">
         <v>73.86499463733007</v>
@@ -7640,43 +7640,43 @@
         <v>66.35387529743628</v>
       </c>
       <c r="D15" t="n">
-        <v>68.56030649132634</v>
+        <v>68.56030649132632</v>
       </c>
       <c r="E15" t="n">
         <v>66.08759507001541</v>
       </c>
       <c r="F15" t="n">
-        <v>69.68390063013348</v>
+        <v>69.68390063013346</v>
       </c>
       <c r="G15" t="n">
-        <v>75.13202096512846</v>
+        <v>75.1320209651284</v>
       </c>
       <c r="H15" t="n">
-        <v>66.49492051169899</v>
+        <v>66.49492051169898</v>
       </c>
       <c r="I15" t="n">
         <v>68.54889785609279</v>
       </c>
       <c r="J15" t="n">
-        <v>71.55690358771001</v>
+        <v>71.55690358770998</v>
       </c>
       <c r="K15" t="n">
         <v>68.71221446740576</v>
       </c>
       <c r="L15" t="n">
-        <v>67.24328882813495</v>
+        <v>67.24328882813494</v>
       </c>
       <c r="M15" t="n">
-        <v>77.60668846109883</v>
+        <v>77.60668846109881</v>
       </c>
       <c r="N15" t="n">
         <v>67.0029327511792</v>
       </c>
       <c r="O15" t="n">
-        <v>67.99751629841043</v>
+        <v>67.9975162984104</v>
       </c>
       <c r="P15" t="n">
-        <v>70.94658845792229</v>
+        <v>70.94658845792227</v>
       </c>
       <c r="Q15" t="n">
         <v>67.37652401940503</v>
@@ -7691,28 +7691,28 @@
         <v>67.48721242645129</v>
       </c>
       <c r="U15" t="n">
-        <v>67.49447868896094</v>
+        <v>67.49447868896092</v>
       </c>
       <c r="V15" t="n">
-        <v>68.87897634200847</v>
+        <v>68.87897634200846</v>
       </c>
       <c r="W15" t="n">
-        <v>68.958380241855</v>
+        <v>68.95838024185497</v>
       </c>
       <c r="X15" t="n">
         <v>69.51878807006813</v>
       </c>
       <c r="Y15" t="n">
-        <v>75.57087666442381</v>
+        <v>75.57087666442374</v>
       </c>
       <c r="Z15" t="n">
-        <v>68.63780991361581</v>
+        <v>68.63780991361578</v>
       </c>
       <c r="AA15" t="n">
         <v>67.96725768749054</v>
       </c>
       <c r="AB15" t="n">
-        <v>79.72015434964091</v>
+        <v>79.72015434964092</v>
       </c>
     </row>
     <row r="16">
@@ -7725,37 +7725,37 @@
         <v>66.52653010548208</v>
       </c>
       <c r="C16" t="n">
-        <v>67.17171811895408</v>
+        <v>67.17171811895406</v>
       </c>
       <c r="D16" t="n">
-        <v>67.17171811895408</v>
+        <v>67.17171811895406</v>
       </c>
       <c r="E16" t="n">
         <v>66.82817453362742</v>
       </c>
       <c r="F16" t="n">
-        <v>66.62704285751434</v>
+        <v>66.62704285751433</v>
       </c>
       <c r="G16" t="n">
-        <v>67.27200504855065</v>
+        <v>67.27200504855064</v>
       </c>
       <c r="H16" t="n">
-        <v>67.17171811895408</v>
+        <v>67.17171811895406</v>
       </c>
       <c r="I16" t="n">
-        <v>67.17171811895408</v>
+        <v>67.17171811895406</v>
       </c>
       <c r="J16" t="n">
         <v>67.13944843894583</v>
       </c>
       <c r="K16" t="n">
-        <v>67.17171811895408</v>
+        <v>67.17171811895406</v>
       </c>
       <c r="L16" t="n">
-        <v>67.17171811895408</v>
+        <v>67.17171811895406</v>
       </c>
       <c r="M16" t="n">
-        <v>67.1717181189542</v>
+        <v>67.17171811895419</v>
       </c>
       <c r="N16" t="n">
         <v>66.67158947092085</v>
@@ -7770,19 +7770,19 @@
         <v>66.39973593512575</v>
       </c>
       <c r="R16" t="n">
-        <v>67.17171811895408</v>
+        <v>67.17171811895406</v>
       </c>
       <c r="S16" t="n">
-        <v>67.17171811895408</v>
+        <v>67.17171811895406</v>
       </c>
       <c r="T16" t="n">
-        <v>67.17171811895408</v>
+        <v>67.17171811895406</v>
       </c>
       <c r="U16" t="n">
-        <v>66.82318547333826</v>
+        <v>66.82318547333824</v>
       </c>
       <c r="V16" t="n">
-        <v>66.96352114936398</v>
+        <v>66.96352114936397</v>
       </c>
       <c r="W16" t="n">
         <v>67.13834790891914</v>
@@ -7797,10 +7797,10 @@
         <v>66.51454540688808</v>
       </c>
       <c r="AA16" t="n">
-        <v>67.17171811895408</v>
+        <v>67.17171811895406</v>
       </c>
       <c r="AB16" t="n">
-        <v>67.84567094881005</v>
+        <v>67.84567094881002</v>
       </c>
     </row>
   </sheetData>
@@ -9451,7 +9451,7 @@
         <v>10.28252860012752</v>
       </c>
       <c r="E2" t="n">
-        <v>9.902525506716339</v>
+        <v>9.902525506716337</v>
       </c>
       <c r="F2" t="n">
         <v>10.8641042570837</v>
@@ -9681,7 +9681,7 @@
         <v>15.84263328297068</v>
       </c>
       <c r="W4" t="n">
-        <v>22.17782106374895</v>
+        <v>22.17782106374896</v>
       </c>
       <c r="X4" t="n">
         <v>22.97173508690678</v>
@@ -9715,7 +9715,7 @@
         <v>21.65683364431793</v>
       </c>
       <c r="E5" t="n">
-        <v>21.40497453166444</v>
+        <v>21.40497453166445</v>
       </c>
       <c r="F5" t="n">
         <v>21.29605047118218</v>
@@ -9748,7 +9748,7 @@
         <v>21.42011321439829</v>
       </c>
       <c r="P5" t="n">
-        <v>21.39812450597197</v>
+        <v>21.39812450597196</v>
       </c>
       <c r="Q5" t="n">
         <v>21.15297502676881</v>
@@ -9803,7 +9803,7 @@
         <v>9.574038024073111</v>
       </c>
       <c r="E6" t="n">
-        <v>9.417969301120943</v>
+        <v>9.417969301120944</v>
       </c>
       <c r="F6" t="n">
         <v>9.782657721628784</v>
@@ -9894,7 +9894,7 @@
         <v>9.978483609092926</v>
       </c>
       <c r="F7" t="n">
-        <v>9.869559548610811</v>
+        <v>9.869559548610807</v>
       </c>
       <c r="G7" t="n">
         <v>10.28069474216079</v>
@@ -9939,13 +9939,13 @@
         <v>10.23034272174635</v>
       </c>
       <c r="U7" t="n">
-        <v>9.987810657384422</v>
+        <v>9.987810657384424</v>
       </c>
       <c r="V7" t="n">
         <v>10.05283628651934</v>
       </c>
       <c r="W7" t="n">
-        <v>10.19345917765711</v>
+        <v>10.1934591776571</v>
       </c>
       <c r="X7" t="n">
         <v>9.72811267194334</v>
@@ -10322,7 +10322,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>76.87263643271534</v>
+        <v>76.87263643271532</v>
       </c>
       <c r="C12" t="n">
         <v>75.83666490093263</v>
@@ -10370,7 +10370,7 @@
         <v>76.64652691625736</v>
       </c>
       <c r="R12" t="n">
-        <v>76.30762040166755</v>
+        <v>76.30762040166756</v>
       </c>
       <c r="S12" t="n">
         <v>76.47522778326957</v>
@@ -10446,7 +10446,7 @@
         <v>76.74545843391306</v>
       </c>
       <c r="N13" t="n">
-        <v>76.27237901343105</v>
+        <v>76.27237901343103</v>
       </c>
       <c r="O13" t="n">
         <v>76.40238534588796</v>

--- a/Results/Phase 2/Carbon dioxide/carbon dioxide ecotoxicity freshwater results.xlsx
+++ b/Results/Phase 2/Carbon dioxide/carbon dioxide ecotoxicity freshwater results.xlsx
@@ -586,85 +586,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>14.93325938507006</v>
+        <v>14.93325938506969</v>
       </c>
       <c r="C2" t="n">
         <v>11.56006611085829</v>
       </c>
       <c r="D2" t="n">
-        <v>13.79960781539452</v>
+        <v>13.79960781539429</v>
       </c>
       <c r="E2" t="n">
-        <v>11.27701055125628</v>
+        <v>11.27701055125623</v>
       </c>
       <c r="F2" t="n">
-        <v>14.94558616409035</v>
+        <v>14.94558616409033</v>
       </c>
       <c r="G2" t="n">
-        <v>32.14584736683722</v>
+        <v>32.14584736683695</v>
       </c>
       <c r="H2" t="n">
-        <v>11.9503194575461</v>
+        <v>11.95031945754585</v>
       </c>
       <c r="I2" t="n">
-        <v>14.54973373624069</v>
+        <v>14.54973373624098</v>
       </c>
       <c r="J2" t="n">
-        <v>22.43660268812367</v>
+        <v>22.4366026881236</v>
       </c>
       <c r="K2" t="n">
-        <v>14.25803332677583</v>
+        <v>14.25803332677559</v>
       </c>
       <c r="L2" t="n">
-        <v>13.46815761476345</v>
+        <v>13.46815761476333</v>
       </c>
       <c r="M2" t="n">
-        <v>42.17514535278002</v>
+        <v>42.17514535278001</v>
       </c>
       <c r="N2" t="n">
-        <v>13.8225221641047</v>
+        <v>13.82252216410444</v>
       </c>
       <c r="O2" t="n">
-        <v>16.7319474759115</v>
+        <v>16.73194747591128</v>
       </c>
       <c r="P2" t="n">
-        <v>19.01842795374371</v>
+        <v>19.01842795374347</v>
       </c>
       <c r="Q2" t="n">
-        <v>12.5289353429547</v>
+        <v>12.52893534295447</v>
       </c>
       <c r="R2" t="n">
-        <v>12.03056331820892</v>
+        <v>12.03056331820871</v>
       </c>
       <c r="S2" t="n">
-        <v>17.35758708809642</v>
+        <v>17.35758708809623</v>
       </c>
       <c r="T2" t="n">
-        <v>12.80084839257731</v>
+        <v>12.80084839257712</v>
       </c>
       <c r="U2" t="n">
-        <v>20.72985935794761</v>
+        <v>20.7298593579474</v>
       </c>
       <c r="V2" t="n">
-        <v>14.3854856215494</v>
+        <v>14.38548562154939</v>
       </c>
       <c r="W2" t="n">
-        <v>17.35801589022392</v>
+        <v>17.35801589022375</v>
       </c>
       <c r="X2" t="n">
-        <v>15.03867189690451</v>
+        <v>15.03867189690419</v>
       </c>
       <c r="Y2" t="n">
-        <v>17.88363148133844</v>
+        <v>17.88363148133802</v>
       </c>
       <c r="Z2" t="n">
-        <v>17.06456998541777</v>
+        <v>17.06456998541764</v>
       </c>
       <c r="AA2" t="n">
-        <v>18.44750107874738</v>
+        <v>18.44750107874717</v>
       </c>
       <c r="AB2" t="n">
-        <v>41.96856324698676</v>
+        <v>41.96856324698678</v>
       </c>
     </row>
     <row r="3">
@@ -674,13 +674,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>11.26790124866849</v>
+        <v>11.26790124866879</v>
       </c>
       <c r="C3" t="n">
         <v>12.51606440545664</v>
       </c>
       <c r="D3" t="n">
-        <v>12.51400454913918</v>
+        <v>12.51400454913873</v>
       </c>
       <c r="E3" t="n">
         <v>11.791894274244</v>
@@ -689,67 +689,67 @@
         <v>11.43903791339342</v>
       </c>
       <c r="G3" t="n">
-        <v>12.77239218610539</v>
+        <v>12.77239218610517</v>
       </c>
       <c r="H3" t="n">
-        <v>12.51400454913918</v>
+        <v>12.51400454913873</v>
       </c>
       <c r="I3" t="n">
-        <v>12.51400454913918</v>
+        <v>12.51400454913873</v>
       </c>
       <c r="J3" t="n">
-        <v>12.49242968764251</v>
+        <v>12.49242968764233</v>
       </c>
       <c r="K3" t="n">
-        <v>12.51400454913918</v>
+        <v>12.51400454913873</v>
       </c>
       <c r="L3" t="n">
-        <v>12.51400454913918</v>
+        <v>12.51400454913873</v>
       </c>
       <c r="M3" t="n">
         <v>12.56640220172351</v>
       </c>
       <c r="N3" t="n">
-        <v>11.54806602275362</v>
+        <v>11.54806602275359</v>
       </c>
       <c r="O3" t="n">
-        <v>11.81351431694959</v>
+        <v>11.81351431694883</v>
       </c>
       <c r="P3" t="n">
-        <v>11.74844652590751</v>
+        <v>11.74844652590699</v>
       </c>
       <c r="Q3" t="n">
-        <v>11.02301350918628</v>
+        <v>11.02301350918617</v>
       </c>
       <c r="R3" t="n">
-        <v>12.51400454913918</v>
+        <v>12.51400454913873</v>
       </c>
       <c r="S3" t="n">
-        <v>12.51400454913918</v>
+        <v>12.51400454913873</v>
       </c>
       <c r="T3" t="n">
-        <v>12.51400454913918</v>
+        <v>12.51400454913873</v>
       </c>
       <c r="U3" t="n">
-        <v>11.90554048627177</v>
+        <v>11.90554048627231</v>
       </c>
       <c r="V3" t="n">
-        <v>12.11427469083105</v>
+        <v>12.11427469083106</v>
       </c>
       <c r="W3" t="n">
-        <v>12.51424944422039</v>
+        <v>12.51424944422004</v>
       </c>
       <c r="X3" t="n">
-        <v>11.13722135276677</v>
+        <v>11.13722135276693</v>
       </c>
       <c r="Y3" t="n">
-        <v>13.75253589326903</v>
+        <v>13.75253589326899</v>
       </c>
       <c r="Z3" t="n">
-        <v>11.24475424010561</v>
+        <v>11.24475424010529</v>
       </c>
       <c r="AA3" t="n">
-        <v>12.51400454913918</v>
+        <v>12.51400454913873</v>
       </c>
       <c r="AB3" t="n">
         <v>13.87599254721157</v>
@@ -762,85 +762,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>23.96957058952745</v>
+        <v>23.96957058952728</v>
       </c>
       <c r="C4" t="n">
-        <v>22.74139031399032</v>
+        <v>22.74139031399022</v>
       </c>
       <c r="D4" t="n">
-        <v>23.55636790438954</v>
+        <v>23.55636790438929</v>
       </c>
       <c r="E4" t="n">
-        <v>22.5996717258945</v>
+        <v>22.59967172589441</v>
       </c>
       <c r="F4" t="n">
-        <v>23.95945208201945</v>
+        <v>23.95945208201939</v>
       </c>
       <c r="G4" t="n">
-        <v>30.24335678846888</v>
+        <v>30.24335678846869</v>
       </c>
       <c r="H4" t="n">
-        <v>22.88232401339406</v>
+        <v>22.88232401339384</v>
       </c>
       <c r="I4" t="n">
-        <v>23.82977999411469</v>
+        <v>23.8297799941143</v>
       </c>
       <c r="J4" t="n">
-        <v>25.71006420631146</v>
+        <v>25.71006420631161</v>
       </c>
       <c r="K4" t="n">
-        <v>23.72345862018389</v>
+        <v>23.72345862018363</v>
       </c>
       <c r="L4" t="n">
-        <v>23.43555819834429</v>
+        <v>23.43555819834405</v>
       </c>
       <c r="M4" t="n">
-        <v>33.9322174578837</v>
+        <v>33.93221745788361</v>
       </c>
       <c r="N4" t="n">
-        <v>23.56471991542054</v>
+        <v>23.564719915421</v>
       </c>
       <c r="O4" t="n">
-        <v>24.62517127737723</v>
+        <v>24.625171277377</v>
       </c>
       <c r="P4" t="n">
-        <v>25.45856656233774</v>
+        <v>25.45856656233754</v>
       </c>
       <c r="Q4" t="n">
-        <v>23.09322270917474</v>
+        <v>23.09322270917448</v>
       </c>
       <c r="R4" t="n">
-        <v>22.91157195833467</v>
+        <v>22.91157195833443</v>
       </c>
       <c r="S4" t="n">
-        <v>24.8532095693874</v>
+        <v>24.8532095693871</v>
       </c>
       <c r="T4" t="n">
-        <v>23.19233182279793</v>
+        <v>23.1923318227977</v>
       </c>
       <c r="U4" t="n">
-        <v>26.08236321252788</v>
+        <v>26.08236321252761</v>
       </c>
       <c r="V4" t="n">
-        <v>17.18968281454015</v>
+        <v>17.18968281454013</v>
       </c>
       <c r="W4" t="n">
-        <v>24.85336586272761</v>
+        <v>24.85336586272733</v>
       </c>
       <c r="X4" t="n">
-        <v>24.0079922122749</v>
+        <v>24.00799221227444</v>
       </c>
       <c r="Y4" t="n">
-        <v>25.04494657359898</v>
+        <v>25.04494657359821</v>
       </c>
       <c r="Z4" t="n">
-        <v>24.74640827624156</v>
+        <v>24.74640827624134</v>
       </c>
       <c r="AA4" t="n">
-        <v>25.25047042056341</v>
+        <v>25.25047042056317</v>
       </c>
       <c r="AB4" t="n">
-        <v>33.86196110902881</v>
+        <v>33.86196110902875</v>
       </c>
     </row>
     <row r="5">
@@ -850,85 +850,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>22.63359058961737</v>
+        <v>22.63359058961712</v>
       </c>
       <c r="C5" t="n">
-        <v>23.08984046647267</v>
+        <v>23.08984046647258</v>
       </c>
       <c r="D5" t="n">
-        <v>23.0877806101552</v>
+        <v>23.0877806101554</v>
       </c>
       <c r="E5" t="n">
-        <v>22.78734079685361</v>
+        <v>22.78734079685352</v>
       </c>
       <c r="F5" t="n">
-        <v>22.68135642060887</v>
+        <v>22.68135642060881</v>
       </c>
       <c r="G5" t="n">
-        <v>23.18195986968857</v>
+        <v>23.18195986968815</v>
       </c>
       <c r="H5" t="n">
-        <v>23.0877806101552</v>
+        <v>23.0877806101554</v>
       </c>
       <c r="I5" t="n">
-        <v>23.0877806101552</v>
+        <v>23.0877806101554</v>
       </c>
       <c r="J5" t="n">
-        <v>22.08552991801093</v>
+        <v>22.08552991801106</v>
       </c>
       <c r="K5" t="n">
-        <v>23.0877806101552</v>
+        <v>23.0877806101554</v>
       </c>
       <c r="L5" t="n">
-        <v>23.0877806101552</v>
+        <v>23.0877806101554</v>
       </c>
       <c r="M5" t="n">
-        <v>23.1401782627395</v>
+        <v>23.14017826273945</v>
       </c>
       <c r="N5" t="n">
-        <v>22.73570735991051</v>
+        <v>22.73570735990997</v>
       </c>
       <c r="O5" t="n">
-        <v>22.8324601460937</v>
+        <v>22.83246014609324</v>
       </c>
       <c r="P5" t="n">
-        <v>22.80874370032344</v>
+        <v>22.80874370032301</v>
       </c>
       <c r="Q5" t="n">
-        <v>22.54433188419311</v>
+        <v>22.54433188419341</v>
       </c>
       <c r="R5" t="n">
-        <v>23.0877806101552</v>
+        <v>23.0877806101554</v>
       </c>
       <c r="S5" t="n">
-        <v>23.0877806101552</v>
+        <v>23.0877806101554</v>
       </c>
       <c r="T5" t="n">
-        <v>23.0877806101552</v>
+        <v>23.0877806101554</v>
       </c>
       <c r="U5" t="n">
-        <v>22.8660026041858</v>
+        <v>22.8660026041856</v>
       </c>
       <c r="V5" t="n">
-        <v>16.36185310019856</v>
+        <v>16.36185310019854</v>
       </c>
       <c r="W5" t="n">
-        <v>23.08786987153659</v>
+        <v>23.08786987153644</v>
       </c>
       <c r="X5" t="n">
-        <v>22.58595930208199</v>
+        <v>22.58595930208138</v>
       </c>
       <c r="Y5" t="n">
-        <v>23.53921074152122</v>
+        <v>23.53921074152094</v>
       </c>
       <c r="Z5" t="n">
-        <v>22.62515377680209</v>
+        <v>22.62515377680202</v>
       </c>
       <c r="AA5" t="n">
-        <v>23.0877806101552</v>
+        <v>23.0877806101554</v>
       </c>
       <c r="AB5" t="n">
-        <v>23.62254896858084</v>
+        <v>23.62254896858076</v>
       </c>
     </row>
     <row r="6">
@@ -938,85 +938,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>11.39675824147776</v>
+        <v>11.39675824147763</v>
       </c>
       <c r="C6" t="n">
-        <v>10.16857796594064</v>
+        <v>10.16857796594063</v>
       </c>
       <c r="D6" t="n">
-        <v>10.98355555633986</v>
+        <v>10.98355555633961</v>
       </c>
       <c r="E6" t="n">
-        <v>10.02685937784482</v>
+        <v>10.02685937784481</v>
       </c>
       <c r="F6" t="n">
         <v>11.38663973396976</v>
       </c>
       <c r="G6" t="n">
-        <v>17.63132232077105</v>
+        <v>17.63132232077086</v>
       </c>
       <c r="H6" t="n">
-        <v>10.30951166534438</v>
+        <v>10.30951166534419</v>
       </c>
       <c r="I6" t="n">
-        <v>11.25696764606501</v>
+        <v>11.25696764606469</v>
       </c>
       <c r="J6" t="n">
-        <v>14.08014586319498</v>
+        <v>14.08014586319481</v>
       </c>
       <c r="K6" t="n">
-        <v>11.15064627213422</v>
+        <v>11.15064627213407</v>
       </c>
       <c r="L6" t="n">
-        <v>10.86274585029459</v>
+        <v>10.86274585029444</v>
       </c>
       <c r="M6" t="n">
-        <v>21.35940510983403</v>
+        <v>21.35940510983402</v>
       </c>
       <c r="N6" t="n">
-        <v>10.99190756737085</v>
+        <v>10.99190756737128</v>
       </c>
       <c r="O6" t="n">
-        <v>12.0131368096794</v>
+        <v>12.01313680967925</v>
       </c>
       <c r="P6" t="n">
-        <v>12.84653209463992</v>
+        <v>12.84653209463973</v>
       </c>
       <c r="Q6" t="n">
-        <v>10.52041036112506</v>
+        <v>10.52041036112493</v>
       </c>
       <c r="R6" t="n">
-        <v>10.338759610285</v>
+        <v>10.33875961028477</v>
       </c>
       <c r="S6" t="n">
-        <v>12.28039722133772</v>
+        <v>12.28039722133754</v>
       </c>
       <c r="T6" t="n">
-        <v>10.61951947474826</v>
+        <v>10.61951947474804</v>
       </c>
       <c r="U6" t="n">
-        <v>13.47032874483005</v>
+        <v>13.47032874482989</v>
       </c>
       <c r="V6" t="n">
-        <v>11.12256164661978</v>
+        <v>11.12256164661977</v>
       </c>
       <c r="W6" t="n">
-        <v>12.24133139502979</v>
+        <v>12.24133139502967</v>
       </c>
       <c r="X6" t="n">
-        <v>11.39595774457709</v>
+        <v>11.39595774457678</v>
       </c>
       <c r="Y6" t="n">
-        <v>12.4721342255493</v>
+        <v>12.47213422554852</v>
       </c>
       <c r="Z6" t="n">
-        <v>12.17359592819189</v>
+        <v>12.17359592819169</v>
       </c>
       <c r="AA6" t="n">
-        <v>12.67765807251374</v>
+        <v>12.67765807251359</v>
       </c>
       <c r="AB6" t="n">
-        <v>21.28914876097917</v>
+        <v>21.28914876097914</v>
       </c>
     </row>
     <row r="7">
@@ -1026,13 +1026,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>10.06077824156768</v>
+        <v>10.06077824156751</v>
       </c>
       <c r="C7" t="n">
-        <v>10.51702811842299</v>
+        <v>10.51702811842298</v>
       </c>
       <c r="D7" t="n">
-        <v>10.51496826210553</v>
+        <v>10.51496826210574</v>
       </c>
       <c r="E7" t="n">
         <v>10.21452844880393</v>
@@ -1041,70 +1041,70 @@
         <v>10.10854407255919</v>
       </c>
       <c r="G7" t="n">
-        <v>10.56992540199076</v>
+        <v>10.56992540199047</v>
       </c>
       <c r="H7" t="n">
-        <v>10.51496826210553</v>
+        <v>10.51496826210574</v>
       </c>
       <c r="I7" t="n">
-        <v>10.51496826210553</v>
+        <v>10.51496826210574</v>
       </c>
       <c r="J7" t="n">
-        <v>10.45561157489444</v>
+        <v>10.45561157489459</v>
       </c>
       <c r="K7" t="n">
-        <v>10.51496826210553</v>
+        <v>10.51496826210574</v>
       </c>
       <c r="L7" t="n">
-        <v>10.51496826210553</v>
+        <v>10.51496826210574</v>
       </c>
       <c r="M7" t="n">
-        <v>10.56736591468982</v>
+        <v>10.56736591468981</v>
       </c>
       <c r="N7" t="n">
-        <v>10.16289501186083</v>
+        <v>10.16289501186035</v>
       </c>
       <c r="O7" t="n">
-        <v>10.22042567839589</v>
+        <v>10.22042567839545</v>
       </c>
       <c r="P7" t="n">
-        <v>10.19670923262562</v>
+        <v>10.19670923262523</v>
       </c>
       <c r="Q7" t="n">
-        <v>9.97151953614344</v>
+        <v>9.971519536143743</v>
       </c>
       <c r="R7" t="n">
-        <v>10.51496826210553</v>
+        <v>10.51496826210574</v>
       </c>
       <c r="S7" t="n">
-        <v>10.51496826210553</v>
+        <v>10.51496826210574</v>
       </c>
       <c r="T7" t="n">
-        <v>10.51496826210553</v>
+        <v>10.51496826210574</v>
       </c>
       <c r="U7" t="n">
-        <v>10.25396813648798</v>
+        <v>10.25396813648791</v>
       </c>
       <c r="V7" t="n">
         <v>10.29473193227819</v>
       </c>
       <c r="W7" t="n">
-        <v>10.47583540383879</v>
+        <v>10.47583540383873</v>
       </c>
       <c r="X7" t="n">
-        <v>9.973924834384166</v>
+        <v>9.97392483438359</v>
       </c>
       <c r="Y7" t="n">
-        <v>10.96639839347153</v>
+        <v>10.96639839347138</v>
       </c>
       <c r="Z7" t="n">
-        <v>10.05234142875241</v>
+        <v>10.05234142875236</v>
       </c>
       <c r="AA7" t="n">
-        <v>10.51496826210553</v>
+        <v>10.51496826210574</v>
       </c>
       <c r="AB7" t="n">
-        <v>11.04973662053116</v>
+        <v>11.04973662053115</v>
       </c>
     </row>
   </sheetData>
@@ -1270,85 +1270,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>12.24218760800875</v>
+        <v>12.24218760800809</v>
       </c>
       <c r="C2" t="n">
         <v>10.27319597322997</v>
       </c>
       <c r="D2" t="n">
-        <v>10.58597048646973</v>
+        <v>10.58597048646904</v>
       </c>
       <c r="E2" t="n">
-        <v>9.714529278784504</v>
+        <v>9.714529278784507</v>
       </c>
       <c r="F2" t="n">
-        <v>10.86786718019331</v>
+        <v>10.8678671801933</v>
       </c>
       <c r="G2" t="n">
-        <v>11.89420298691519</v>
+        <v>11.8942029869146</v>
       </c>
       <c r="H2" t="n">
-        <v>11.72846692504753</v>
+        <v>11.72846692504687</v>
       </c>
       <c r="I2" t="n">
-        <v>12.45386169070827</v>
+        <v>12.45386169070762</v>
       </c>
       <c r="J2" t="n">
-        <v>11.68260013614935</v>
+        <v>11.68260013614917</v>
       </c>
       <c r="K2" t="n">
-        <v>12.03337440626131</v>
+        <v>12.03337440626065</v>
       </c>
       <c r="L2" t="n">
-        <v>11.40583538564921</v>
+        <v>11.40583538564834</v>
       </c>
       <c r="M2" t="n">
-        <v>11.43734499900166</v>
+        <v>11.43734499900163</v>
       </c>
       <c r="N2" t="n">
-        <v>11.30060291539604</v>
+        <v>11.30060291539639</v>
       </c>
       <c r="O2" t="n">
-        <v>11.52019358849427</v>
+        <v>11.52019358849353</v>
       </c>
       <c r="P2" t="n">
-        <v>11.79693497636927</v>
+        <v>11.79693497636924</v>
       </c>
       <c r="Q2" t="n">
-        <v>11.82442041162217</v>
+        <v>11.82442041162153</v>
       </c>
       <c r="R2" t="n">
-        <v>12.14058514998502</v>
+        <v>12.14058514998438</v>
       </c>
       <c r="S2" t="n">
-        <v>11.5966867436034</v>
+        <v>11.59668674360282</v>
       </c>
       <c r="T2" t="n">
-        <v>10.69751602611798</v>
+        <v>10.69751602611761</v>
       </c>
       <c r="U2" t="n">
-        <v>12.00478746819008</v>
+        <v>12.00478746818942</v>
       </c>
       <c r="V2" t="n">
         <v>11.62082497977259</v>
       </c>
       <c r="W2" t="n">
-        <v>13.85941369180017</v>
+        <v>13.85941369179987</v>
       </c>
       <c r="X2" t="n">
-        <v>16.08766256866194</v>
+        <v>16.08766256866125</v>
       </c>
       <c r="Y2" t="n">
-        <v>15.50227599216891</v>
+        <v>15.5022759921682</v>
       </c>
       <c r="Z2" t="n">
-        <v>11.1131034369295</v>
+        <v>11.11310343692919</v>
       </c>
       <c r="AA2" t="n">
-        <v>12.72742377576061</v>
+        <v>12.72742377576008</v>
       </c>
       <c r="AB2" t="n">
-        <v>10.92748306541928</v>
+        <v>10.92748306541927</v>
       </c>
     </row>
     <row r="3">
@@ -1358,85 +1358,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>10.93552602233197</v>
+        <v>10.93552602233138</v>
       </c>
       <c r="C3" t="n">
-        <v>12.12049977417571</v>
+        <v>12.12049977417569</v>
       </c>
       <c r="D3" t="n">
-        <v>12.09526418536882</v>
+        <v>12.09526418536887</v>
       </c>
       <c r="E3" t="n">
-        <v>11.45138107257338</v>
+        <v>11.45138107257339</v>
       </c>
       <c r="F3" t="n">
-        <v>11.11273164934341</v>
+        <v>11.11273164934342</v>
       </c>
       <c r="G3" t="n">
-        <v>12.33574344847387</v>
+        <v>12.33574344847377</v>
       </c>
       <c r="H3" t="n">
-        <v>12.09526418536882</v>
+        <v>12.09526418536887</v>
       </c>
       <c r="I3" t="n">
-        <v>12.09526418536882</v>
+        <v>12.09526418536887</v>
       </c>
       <c r="J3" t="n">
-        <v>12.08428930015631</v>
+        <v>12.08428930015603</v>
       </c>
       <c r="K3" t="n">
-        <v>12.09526418536882</v>
+        <v>12.09526418536887</v>
       </c>
       <c r="L3" t="n">
-        <v>12.09526418536882</v>
+        <v>12.09526418536887</v>
       </c>
       <c r="M3" t="n">
-        <v>12.09298033769532</v>
+        <v>12.09298033769531</v>
       </c>
       <c r="N3" t="n">
-        <v>11.19627308907334</v>
+        <v>11.19627308907297</v>
       </c>
       <c r="O3" t="n">
-        <v>11.44332364819975</v>
+        <v>11.44332364819926</v>
       </c>
       <c r="P3" t="n">
-        <v>11.38276558657356</v>
+        <v>11.3827655865729</v>
       </c>
       <c r="Q3" t="n">
-        <v>10.70761100353491</v>
+        <v>10.70761100353493</v>
       </c>
       <c r="R3" t="n">
-        <v>12.09526418536882</v>
+        <v>12.09526418536887</v>
       </c>
       <c r="S3" t="n">
-        <v>12.09526418536882</v>
+        <v>12.09526418536887</v>
       </c>
       <c r="T3" t="n">
-        <v>12.09526418536882</v>
+        <v>12.09526418536887</v>
       </c>
       <c r="U3" t="n">
-        <v>11.52909490683068</v>
+        <v>11.52909490683054</v>
       </c>
       <c r="V3" t="n">
-        <v>11.75202409278997</v>
+        <v>11.75202409278996</v>
       </c>
       <c r="W3" t="n">
-        <v>12.09549210725218</v>
+        <v>12.09549210725208</v>
       </c>
       <c r="X3" t="n">
-        <v>10.81390331067648</v>
+        <v>10.81390331067589</v>
       </c>
       <c r="Y3" t="n">
-        <v>13.2481660431859</v>
+        <v>13.24816604318574</v>
       </c>
       <c r="Z3" t="n">
-        <v>10.91398329053372</v>
+        <v>10.9139832905333</v>
       </c>
       <c r="AA3" t="n">
-        <v>12.09526418536882</v>
+        <v>12.09526418536887</v>
       </c>
       <c r="AB3" t="n">
-        <v>13.29267193180458</v>
+        <v>13.29267193180459</v>
       </c>
     </row>
     <row r="4">
@@ -1446,85 +1446,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>21.71159867858269</v>
+        <v>21.71159867858198</v>
       </c>
       <c r="C4" t="n">
-        <v>21.00996186179032</v>
+        <v>21.00996186179043</v>
       </c>
       <c r="D4" t="n">
-        <v>21.10792698606505</v>
+        <v>21.10792698606422</v>
       </c>
       <c r="E4" t="n">
-        <v>20.7735468740266</v>
+        <v>20.77354687402668</v>
       </c>
       <c r="F4" t="n">
-        <v>21.20847105033694</v>
+        <v>21.20847105033698</v>
       </c>
       <c r="G4" t="n">
-        <v>21.58476237043579</v>
+        <v>21.58476237043493</v>
       </c>
       <c r="H4" t="n">
-        <v>21.52435352205612</v>
+        <v>21.52435352205541</v>
       </c>
       <c r="I4" t="n">
-        <v>21.78875139612409</v>
+        <v>21.78875139612339</v>
       </c>
       <c r="J4" t="n">
         <v>20.64450052140959</v>
       </c>
       <c r="K4" t="n">
-        <v>21.63548871855413</v>
+        <v>21.63548871855344</v>
       </c>
       <c r="L4" t="n">
-        <v>21.40675811447592</v>
+        <v>21.40675811447543</v>
       </c>
       <c r="M4" t="n">
-        <v>21.41679158652332</v>
+        <v>21.41679158652336</v>
       </c>
       <c r="N4" t="n">
-        <v>21.36840211477094</v>
+        <v>21.36840211477069</v>
       </c>
       <c r="O4" t="n">
-        <v>21.44844033655148</v>
+        <v>21.44844033655076</v>
       </c>
       <c r="P4" t="n">
-        <v>21.54930932276993</v>
+        <v>21.54930932276997</v>
       </c>
       <c r="Q4" t="n">
-        <v>21.55932744116987</v>
+        <v>21.55932744116916</v>
       </c>
       <c r="R4" t="n">
-        <v>21.67456577570933</v>
+        <v>21.6745657757086</v>
       </c>
       <c r="S4" t="n">
-        <v>21.47632119336073</v>
+        <v>21.47632119336009</v>
       </c>
       <c r="T4" t="n">
-        <v>21.14858402543241</v>
+        <v>21.14858402543236</v>
       </c>
       <c r="U4" t="n">
-        <v>21.62506911531197</v>
+        <v>21.62506911531124</v>
       </c>
       <c r="V4" t="n">
-        <v>15.7564236502408</v>
+        <v>15.75642365024082</v>
       </c>
       <c r="W4" t="n">
-        <v>22.30105859569712</v>
+        <v>22.3010585956966</v>
       </c>
       <c r="X4" t="n">
-        <v>23.11322914589396</v>
+        <v>23.11322914589326</v>
       </c>
       <c r="Y4" t="n">
-        <v>22.89986261271847</v>
+        <v>22.89986261271778</v>
       </c>
       <c r="Z4" t="n">
-        <v>21.30006075659966</v>
+        <v>21.30006075659943</v>
       </c>
       <c r="AA4" t="n">
-        <v>21.88846156379709</v>
+        <v>21.88846156379683</v>
       </c>
       <c r="AB4" t="n">
-        <v>21.22348443282911</v>
+        <v>21.22348443282912</v>
       </c>
     </row>
     <row r="5">
@@ -1537,82 +1537,82 @@
         <v>21.23533587419785</v>
       </c>
       <c r="C5" t="n">
-        <v>21.68328240509872</v>
+        <v>21.68328240509873</v>
       </c>
       <c r="D5" t="n">
-        <v>21.65804681629186</v>
+        <v>21.65804681629189</v>
       </c>
       <c r="E5" t="n">
-        <v>21.40660895771929</v>
+        <v>21.40660895771925</v>
       </c>
       <c r="F5" t="n">
-        <v>21.29772127399835</v>
+        <v>21.29772127399843</v>
       </c>
       <c r="G5" t="n">
-        <v>21.74569868384368</v>
+        <v>21.74569868384358</v>
       </c>
       <c r="H5" t="n">
-        <v>21.65804681629186</v>
+        <v>21.65804681629189</v>
       </c>
       <c r="I5" t="n">
-        <v>21.65804681629186</v>
+        <v>21.65804681629189</v>
       </c>
       <c r="J5" t="n">
-        <v>20.79091150481774</v>
+        <v>20.79091150481775</v>
       </c>
       <c r="K5" t="n">
-        <v>21.65804681629186</v>
+        <v>21.65804681629189</v>
       </c>
       <c r="L5" t="n">
-        <v>21.65804681629186</v>
+        <v>21.65804681629189</v>
       </c>
       <c r="M5" t="n">
-        <v>21.65576296861837</v>
+        <v>21.65576296861832</v>
       </c>
       <c r="N5" t="n">
-        <v>21.33037511817868</v>
+        <v>21.33037511817848</v>
       </c>
       <c r="O5" t="n">
-        <v>21.42042214596598</v>
+        <v>21.42042214596588</v>
       </c>
       <c r="P5" t="n">
-        <v>21.39834944361233</v>
+        <v>21.39834944361173</v>
       </c>
       <c r="Q5" t="n">
-        <v>21.15226352615989</v>
+        <v>21.15226352615977</v>
       </c>
       <c r="R5" t="n">
-        <v>21.65804681629186</v>
+        <v>21.65804681629189</v>
       </c>
       <c r="S5" t="n">
-        <v>21.65804681629186</v>
+        <v>21.65804681629189</v>
       </c>
       <c r="T5" t="n">
-        <v>21.65804681629186</v>
+        <v>21.65804681629189</v>
       </c>
       <c r="U5" t="n">
-        <v>21.4516847625601</v>
+        <v>21.45168476256</v>
       </c>
       <c r="V5" t="n">
-        <v>15.80424418631788</v>
+        <v>15.80424418631789</v>
       </c>
       <c r="W5" t="n">
-        <v>21.65812989114222</v>
+        <v>21.65812989114194</v>
       </c>
       <c r="X5" t="n">
-        <v>21.19100582396583</v>
+        <v>21.19100582396537</v>
       </c>
       <c r="Y5" t="n">
-        <v>22.07826600540922</v>
+        <v>22.07826600540903</v>
       </c>
       <c r="Z5" t="n">
-        <v>21.22748380142513</v>
+        <v>21.22748380142494</v>
       </c>
       <c r="AA5" t="n">
-        <v>21.65804681629186</v>
+        <v>21.65804681629189</v>
       </c>
       <c r="AB5" t="n">
-        <v>22.08556800117658</v>
+        <v>22.08556800117668</v>
       </c>
     </row>
     <row r="6">
@@ -1622,85 +1622,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>10.28891357175823</v>
+        <v>10.28891357175743</v>
       </c>
       <c r="C6" t="n">
-        <v>9.587276754965998</v>
+        <v>9.587276754966007</v>
       </c>
       <c r="D6" t="n">
-        <v>9.685241879240602</v>
+        <v>9.685241879239902</v>
       </c>
       <c r="E6" t="n">
-        <v>9.35086176720224</v>
+        <v>9.350861767202241</v>
       </c>
       <c r="F6" t="n">
-        <v>9.785785943512568</v>
+        <v>9.785785943512554</v>
       </c>
       <c r="G6" t="n">
-        <v>10.12498928978197</v>
+        <v>10.12498928978112</v>
       </c>
       <c r="H6" t="n">
-        <v>10.10166841523168</v>
+        <v>10.1016684152309</v>
       </c>
       <c r="I6" t="n">
-        <v>10.36606628929963</v>
+        <v>10.36606628929885</v>
       </c>
       <c r="J6" t="n">
-        <v>10.04224357004259</v>
+        <v>10.04224357004244</v>
       </c>
       <c r="K6" t="n">
-        <v>10.21280361172969</v>
+        <v>10.21280361172891</v>
       </c>
       <c r="L6" t="n">
-        <v>9.984073007651521</v>
+        <v>9.984073007651228</v>
       </c>
       <c r="M6" t="n">
-        <v>9.994106479698935</v>
+        <v>9.994106479698898</v>
       </c>
       <c r="N6" t="n">
-        <v>9.945717007946582</v>
+        <v>9.945717007946156</v>
       </c>
       <c r="O6" t="n">
-        <v>9.988667255897619</v>
+        <v>9.98866725589696</v>
       </c>
       <c r="P6" t="n">
-        <v>10.08953624211608</v>
+        <v>10.08953624211617</v>
       </c>
       <c r="Q6" t="n">
-        <v>10.13664233434542</v>
+        <v>10.13664233434462</v>
       </c>
       <c r="R6" t="n">
-        <v>10.25188066888488</v>
+        <v>10.25188066888402</v>
       </c>
       <c r="S6" t="n">
-        <v>10.05363608653634</v>
+        <v>10.05363608653555</v>
       </c>
       <c r="T6" t="n">
-        <v>9.725898918607994</v>
+        <v>9.725898918607841</v>
       </c>
       <c r="U6" t="n">
-        <v>10.16529603465812</v>
+        <v>10.16529603465743</v>
       </c>
       <c r="V6" t="n">
         <v>10.01069916125437</v>
       </c>
       <c r="W6" t="n">
-        <v>10.84128551504331</v>
+        <v>10.84128551504279</v>
       </c>
       <c r="X6" t="n">
-        <v>11.65345606524011</v>
+        <v>11.65345606523941</v>
       </c>
       <c r="Y6" t="n">
-        <v>11.47717750589402</v>
+        <v>11.47717750589329</v>
       </c>
       <c r="Z6" t="n">
-        <v>9.877375649775225</v>
+        <v>9.877375649774915</v>
       </c>
       <c r="AA6" t="n">
-        <v>10.46577645697263</v>
+        <v>10.46577645697248</v>
       </c>
       <c r="AB6" t="n">
-        <v>9.800799326004714</v>
+        <v>9.800799326004705</v>
       </c>
     </row>
     <row r="7">
@@ -1710,85 +1710,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>9.812650767373441</v>
+        <v>9.81265076737326</v>
       </c>
       <c r="C7" t="n">
         <v>10.26059729827431</v>
       </c>
       <c r="D7" t="n">
-        <v>10.23536170946744</v>
+        <v>10.23536170946737</v>
       </c>
       <c r="E7" t="n">
-        <v>9.983923850894815</v>
+        <v>9.983923850894818</v>
       </c>
       <c r="F7" t="n">
-        <v>9.875036167174002</v>
+        <v>9.875036167174008</v>
       </c>
       <c r="G7" t="n">
-        <v>10.28592560318989</v>
+        <v>10.28592560318976</v>
       </c>
       <c r="H7" t="n">
-        <v>10.23536170946744</v>
+        <v>10.23536170946737</v>
       </c>
       <c r="I7" t="n">
-        <v>10.23536170946744</v>
+        <v>10.23536170946737</v>
       </c>
       <c r="J7" t="n">
-        <v>10.18865455345088</v>
+        <v>10.1886545534506</v>
       </c>
       <c r="K7" t="n">
-        <v>10.23536170946744</v>
+        <v>10.23536170946737</v>
       </c>
       <c r="L7" t="n">
-        <v>10.23536170946744</v>
+        <v>10.23536170946737</v>
       </c>
       <c r="M7" t="n">
-        <v>10.23307786179393</v>
+        <v>10.2330778617939</v>
       </c>
       <c r="N7" t="n">
-        <v>9.907690011354331</v>
+        <v>9.907690011353946</v>
       </c>
       <c r="O7" t="n">
-        <v>9.960649065312147</v>
+        <v>9.960649065312046</v>
       </c>
       <c r="P7" t="n">
-        <v>9.938576362958521</v>
+        <v>9.938576362957917</v>
       </c>
       <c r="Q7" t="n">
-        <v>9.729578419335501</v>
+        <v>9.729578419335249</v>
       </c>
       <c r="R7" t="n">
-        <v>10.23536170946744</v>
+        <v>10.23536170946737</v>
       </c>
       <c r="S7" t="n">
-        <v>10.23536170946744</v>
+        <v>10.23536170946737</v>
       </c>
       <c r="T7" t="n">
-        <v>10.23536170946744</v>
+        <v>10.23536170946737</v>
       </c>
       <c r="U7" t="n">
-        <v>9.991911681906268</v>
+        <v>9.991911681906199</v>
       </c>
       <c r="V7" t="n">
-        <v>10.05851969733144</v>
+        <v>10.05851969733143</v>
       </c>
       <c r="W7" t="n">
-        <v>10.19835681048839</v>
+        <v>10.19835681048813</v>
       </c>
       <c r="X7" t="n">
-        <v>9.731232743312049</v>
+        <v>9.731232743311558</v>
       </c>
       <c r="Y7" t="n">
-        <v>10.6555808985848</v>
+        <v>10.65558089858448</v>
       </c>
       <c r="Z7" t="n">
-        <v>9.804798694600727</v>
+        <v>9.804798694600418</v>
       </c>
       <c r="AA7" t="n">
-        <v>10.23536170946744</v>
+        <v>10.23536170946737</v>
       </c>
       <c r="AB7" t="n">
-        <v>10.66288289435226</v>
+        <v>10.66288289435225</v>
       </c>
     </row>
   </sheetData>
@@ -1954,85 +1954,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>14.88685140176313</v>
+        <v>14.8868514017635</v>
       </c>
       <c r="C2" t="n">
-        <v>10.62773791962989</v>
+        <v>10.62773791962994</v>
       </c>
       <c r="D2" t="n">
-        <v>15.62934693112435</v>
+        <v>15.6293469311243</v>
       </c>
       <c r="E2" t="n">
-        <v>11.01092583028926</v>
+        <v>11.01092583028967</v>
       </c>
       <c r="F2" t="n">
-        <v>14.3643311379682</v>
+        <v>14.36433113796822</v>
       </c>
       <c r="G2" t="n">
-        <v>31.47406369326839</v>
+        <v>31.47406369326808</v>
       </c>
       <c r="H2" t="n">
-        <v>10.91246384593515</v>
+        <v>10.91246384593513</v>
       </c>
       <c r="I2" t="n">
-        <v>12.41535855543833</v>
+        <v>12.41535855543828</v>
       </c>
       <c r="J2" t="n">
-        <v>22.73404552274084</v>
+        <v>22.73404552274055</v>
       </c>
       <c r="K2" t="n">
-        <v>14.26072850575713</v>
+        <v>14.26072850575715</v>
       </c>
       <c r="L2" t="n">
-        <v>12.85750326776108</v>
+        <v>12.85750326776357</v>
       </c>
       <c r="M2" t="n">
-        <v>39.99481603190918</v>
+        <v>39.99481603190917</v>
       </c>
       <c r="N2" t="n">
-        <v>13.36537853043638</v>
+        <v>13.36537853043637</v>
       </c>
       <c r="O2" t="n">
-        <v>16.19913541153635</v>
+        <v>16.19913541153631</v>
       </c>
       <c r="P2" t="n">
-        <v>20.80896697502772</v>
+        <v>20.80896697502777</v>
       </c>
       <c r="Q2" t="n">
         <v>12.73456676577361</v>
       </c>
       <c r="R2" t="n">
-        <v>11.30853562483398</v>
+        <v>11.30853562483396</v>
       </c>
       <c r="S2" t="n">
-        <v>17.24982146147993</v>
+        <v>17.2498214614801</v>
       </c>
       <c r="T2" t="n">
-        <v>12.43290498369847</v>
+        <v>12.43290498369848</v>
       </c>
       <c r="U2" t="n">
-        <v>18.98518957593024</v>
+        <v>18.9851895759302</v>
       </c>
       <c r="V2" t="n">
-        <v>13.06387158157731</v>
+        <v>13.06387158157722</v>
       </c>
       <c r="W2" t="n">
-        <v>16.83944979904365</v>
+        <v>16.83944979904364</v>
       </c>
       <c r="X2" t="n">
-        <v>15.34242480740951</v>
+        <v>15.34242480740936</v>
       </c>
       <c r="Y2" t="n">
-        <v>17.29017583865079</v>
+        <v>17.29017583865076</v>
       </c>
       <c r="Z2" t="n">
-        <v>15.94107830932113</v>
+        <v>15.94107830932125</v>
       </c>
       <c r="AA2" t="n">
-        <v>14.7008659929878</v>
+        <v>14.70086599298796</v>
       </c>
       <c r="AB2" t="n">
-        <v>41.05819512422183</v>
+        <v>41.05819512422204</v>
       </c>
     </row>
     <row r="3">
@@ -2042,85 +2042,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>11.24147159992107</v>
+        <v>11.24147159992089</v>
       </c>
       <c r="C3" t="n">
-        <v>12.48344700139672</v>
+        <v>12.48344700139661</v>
       </c>
       <c r="D3" t="n">
-        <v>12.48107557758979</v>
+        <v>12.48107557758976</v>
       </c>
       <c r="E3" t="n">
-        <v>11.76515706104207</v>
+        <v>11.76515706104206</v>
       </c>
       <c r="F3" t="n">
-        <v>11.41263898919725</v>
+        <v>11.41263898919726</v>
       </c>
       <c r="G3" t="n">
-        <v>12.73811553763439</v>
+        <v>12.73811553763434</v>
       </c>
       <c r="H3" t="n">
-        <v>12.48107557758979</v>
+        <v>12.48107557758976</v>
       </c>
       <c r="I3" t="n">
-        <v>12.48107557758979</v>
+        <v>12.48107557758976</v>
       </c>
       <c r="J3" t="n">
-        <v>12.45977378022565</v>
+        <v>12.45977378022563</v>
       </c>
       <c r="K3" t="n">
-        <v>12.48107557758979</v>
+        <v>12.48107557758976</v>
       </c>
       <c r="L3" t="n">
-        <v>12.48107557758979</v>
+        <v>12.48107557758976</v>
       </c>
       <c r="M3" t="n">
         <v>12.53037798948439</v>
       </c>
       <c r="N3" t="n">
-        <v>11.52017511368877</v>
+        <v>11.5201751136887</v>
       </c>
       <c r="O3" t="n">
-        <v>11.78423890456954</v>
+        <v>11.7842389045693</v>
       </c>
       <c r="P3" t="n">
-        <v>11.71951048874439</v>
+        <v>11.71951048874432</v>
       </c>
       <c r="Q3" t="n">
-        <v>10.99786112570906</v>
+        <v>10.99786112570887</v>
       </c>
       <c r="R3" t="n">
-        <v>12.48107557758979</v>
+        <v>12.48107557758976</v>
       </c>
       <c r="S3" t="n">
-        <v>12.48107557758979</v>
+        <v>12.48107557758976</v>
       </c>
       <c r="T3" t="n">
-        <v>12.48107557758979</v>
+        <v>12.48107557758976</v>
       </c>
       <c r="U3" t="n">
-        <v>11.87575519357728</v>
+        <v>11.87575519357711</v>
       </c>
       <c r="V3" t="n">
-        <v>12.08411135087675</v>
+        <v>12.08411135087683</v>
       </c>
       <c r="W3" t="n">
-        <v>12.48131919536821</v>
+        <v>12.48131919536815</v>
       </c>
       <c r="X3" t="n">
-        <v>11.1114732934407</v>
+        <v>11.11147329344062</v>
       </c>
       <c r="Y3" t="n">
-        <v>13.71309594564586</v>
+        <v>13.71309594564569</v>
       </c>
       <c r="Z3" t="n">
-        <v>11.21844531961588</v>
+        <v>11.2184453196157</v>
       </c>
       <c r="AA3" t="n">
-        <v>12.48107557758979</v>
+        <v>12.48107557758976</v>
       </c>
       <c r="AB3" t="n">
-        <v>13.8361354994872</v>
+        <v>13.83613549948719</v>
       </c>
     </row>
     <row r="4">
@@ -2130,82 +2130,82 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>23.88472425063211</v>
+        <v>23.88472425063215</v>
       </c>
       <c r="C4" t="n">
-        <v>22.33383446710607</v>
+        <v>22.33383446710597</v>
       </c>
       <c r="D4" t="n">
-        <v>24.15535515226157</v>
+        <v>24.15535515226147</v>
       </c>
       <c r="E4" t="n">
-        <v>22.4364914168244</v>
+        <v>22.43649141682444</v>
       </c>
       <c r="F4" t="n">
-        <v>23.68032326973967</v>
+        <v>23.68032326973965</v>
       </c>
       <c r="G4" t="n">
         <v>29.93056835400519</v>
       </c>
       <c r="H4" t="n">
-        <v>22.43610665614775</v>
+        <v>22.43610665614772</v>
       </c>
       <c r="I4" t="n">
-        <v>22.98389412988098</v>
+        <v>22.98389412988093</v>
       </c>
       <c r="J4" t="n">
-        <v>25.74344018994918</v>
+        <v>25.74344018994903</v>
       </c>
       <c r="K4" t="n">
-        <v>23.65650980734417</v>
+        <v>23.65650980734413</v>
       </c>
       <c r="L4" t="n">
-        <v>23.14505068559727</v>
+        <v>23.14505068559759</v>
       </c>
       <c r="M4" t="n">
-        <v>33.06761478741131</v>
+        <v>33.0676147874113</v>
       </c>
       <c r="N4" t="n">
-        <v>23.33016525507</v>
+        <v>23.33016525506994</v>
       </c>
       <c r="O4" t="n">
-        <v>24.36303636257762</v>
+        <v>24.36303636257755</v>
       </c>
       <c r="P4" t="n">
-        <v>26.04326583609502</v>
+        <v>26.04326583609498</v>
       </c>
       <c r="Q4" t="n">
-        <v>23.10024177421613</v>
+        <v>23.10024177421617</v>
       </c>
       <c r="R4" t="n">
-        <v>22.58047016864673</v>
+        <v>22.58047016864665</v>
       </c>
       <c r="S4" t="n">
-        <v>24.74599909000354</v>
+        <v>24.74599909000348</v>
       </c>
       <c r="T4" t="n">
-        <v>22.99028959694123</v>
+        <v>22.99028959694116</v>
       </c>
       <c r="U4" t="n">
-        <v>25.37852038999943</v>
+        <v>25.37852038999939</v>
       </c>
       <c r="V4" t="n">
-        <v>16.59211189198781</v>
+        <v>16.592111891988</v>
       </c>
       <c r="W4" t="n">
-        <v>24.59642343787287</v>
+        <v>24.59642343787282</v>
       </c>
       <c r="X4" t="n">
-        <v>24.0507754073772</v>
+        <v>24.05077540737739</v>
       </c>
       <c r="Y4" t="n">
-        <v>24.76070778661729</v>
+        <v>24.76070778661726</v>
       </c>
       <c r="Z4" t="n">
-        <v>24.26897757907965</v>
+        <v>24.26897757907955</v>
       </c>
       <c r="AA4" t="n">
-        <v>23.81693475308443</v>
+        <v>23.81693475308442</v>
       </c>
       <c r="AB4" t="n">
         <v>33.4621231146278</v>
@@ -2218,85 +2218,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>22.5560261190715</v>
+        <v>22.55602611907143</v>
       </c>
       <c r="C5" t="n">
-        <v>23.01021863657388</v>
+        <v>23.01021863657364</v>
       </c>
       <c r="D5" t="n">
-        <v>23.00784721276694</v>
+        <v>23.00784721276674</v>
       </c>
       <c r="E5" t="n">
-        <v>22.71139984380353</v>
+        <v>22.71139984380351</v>
       </c>
       <c r="F5" t="n">
-        <v>22.60446614203184</v>
+        <v>22.6044661420318</v>
       </c>
       <c r="G5" t="n">
-        <v>23.10153525988761</v>
+        <v>23.10153525988748</v>
       </c>
       <c r="H5" t="n">
-        <v>23.00784721276694</v>
+        <v>23.00784721276674</v>
       </c>
       <c r="I5" t="n">
-        <v>23.00784721276694</v>
+        <v>23.00784721276674</v>
       </c>
       <c r="J5" t="n">
-        <v>21.99858878639237</v>
+        <v>21.99858878639231</v>
       </c>
       <c r="K5" t="n">
-        <v>23.00784721276694</v>
+        <v>23.00784721276674</v>
       </c>
       <c r="L5" t="n">
-        <v>23.00784721276694</v>
+        <v>23.00784721276674</v>
       </c>
       <c r="M5" t="n">
-        <v>23.0571496246615</v>
+        <v>23.05714962466146</v>
       </c>
       <c r="N5" t="n">
-        <v>22.65761027713794</v>
+        <v>22.65761027713786</v>
       </c>
       <c r="O5" t="n">
-        <v>22.75385842812038</v>
+        <v>22.75385842812021</v>
       </c>
       <c r="P5" t="n">
-        <v>22.73026568063158</v>
+        <v>22.73026568063142</v>
       </c>
       <c r="Q5" t="n">
-        <v>22.46723296183984</v>
+        <v>22.46723296183978</v>
       </c>
       <c r="R5" t="n">
-        <v>23.00784721276694</v>
+        <v>23.00784721276674</v>
       </c>
       <c r="S5" t="n">
-        <v>23.00784721276694</v>
+        <v>23.00784721276674</v>
       </c>
       <c r="T5" t="n">
-        <v>23.00784721276694</v>
+        <v>23.00784721276674</v>
       </c>
       <c r="U5" t="n">
-        <v>22.7872150408252</v>
+        <v>22.78721504082504</v>
       </c>
       <c r="V5" t="n">
-        <v>16.23500079282296</v>
+        <v>16.23500079282291</v>
       </c>
       <c r="W5" t="n">
-        <v>23.00793600858647</v>
+        <v>23.0079360085864</v>
       </c>
       <c r="X5" t="n">
-        <v>22.5086432628766</v>
+        <v>22.50864326287657</v>
       </c>
       <c r="Y5" t="n">
-        <v>23.45690416980981</v>
+        <v>23.45690416980959</v>
       </c>
       <c r="Z5" t="n">
-        <v>22.54763331028851</v>
+        <v>22.54763331028836</v>
       </c>
       <c r="AA5" t="n">
-        <v>23.00784721276694</v>
+        <v>23.00784721276674</v>
       </c>
       <c r="AB5" t="n">
-        <v>23.54000203897495</v>
+        <v>23.54000203897492</v>
       </c>
     </row>
     <row r="6">
@@ -2306,85 +2306,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>11.36941578154658</v>
+        <v>11.3694157815466</v>
       </c>
       <c r="C6" t="n">
-        <v>9.818525998020553</v>
+        <v>9.818525998020533</v>
       </c>
       <c r="D6" t="n">
-        <v>11.64004668317604</v>
+        <v>11.64004668317591</v>
       </c>
       <c r="E6" t="n">
-        <v>9.921182947738862</v>
+        <v>9.921182947738989</v>
       </c>
       <c r="F6" t="n">
-        <v>11.16501480065416</v>
+        <v>11.16501480065419</v>
       </c>
       <c r="G6" t="n">
-        <v>17.37616929220507</v>
+        <v>17.37616929220484</v>
       </c>
       <c r="H6" t="n">
-        <v>9.920798187062214</v>
+        <v>9.920798187062067</v>
       </c>
       <c r="I6" t="n">
-        <v>10.46858566079544</v>
+        <v>10.46858566079531</v>
       </c>
       <c r="J6" t="n">
-        <v>14.17843005620865</v>
+        <v>14.17843005620849</v>
       </c>
       <c r="K6" t="n">
-        <v>11.14120133825865</v>
+        <v>11.14120133825853</v>
       </c>
       <c r="L6" t="n">
-        <v>10.62974221651174</v>
+        <v>10.62974221651179</v>
       </c>
       <c r="M6" t="n">
-        <v>20.5523063183258</v>
+        <v>20.55230631832578</v>
       </c>
       <c r="N6" t="n">
-        <v>10.81485678598445</v>
+        <v>10.81485678598433</v>
       </c>
       <c r="O6" t="n">
-        <v>11.80863730077749</v>
+        <v>11.80863730077744</v>
       </c>
       <c r="P6" t="n">
-        <v>13.48886677429489</v>
+        <v>13.48886677429485</v>
       </c>
       <c r="Q6" t="n">
-        <v>10.58493330513061</v>
+        <v>10.58493330513047</v>
       </c>
       <c r="R6" t="n">
-        <v>10.06516169956119</v>
+        <v>10.06516169956106</v>
       </c>
       <c r="S6" t="n">
-        <v>12.23069062091802</v>
+        <v>12.2306906209179</v>
       </c>
       <c r="T6" t="n">
-        <v>10.4749811278557</v>
+        <v>10.4749811278556</v>
       </c>
       <c r="U6" t="n">
-        <v>12.82412132819931</v>
+        <v>12.82412132819928</v>
       </c>
       <c r="V6" t="n">
-        <v>10.6311868328826</v>
+        <v>10.63118683288246</v>
       </c>
       <c r="W6" t="n">
         <v>12.04202437607274</v>
       </c>
       <c r="X6" t="n">
-        <v>11.49637634557707</v>
+        <v>11.49637634557717</v>
       </c>
       <c r="Y6" t="n">
-        <v>12.24539931753177</v>
+        <v>12.24539931753163</v>
       </c>
       <c r="Z6" t="n">
-        <v>11.75366910999413</v>
+        <v>11.75366910999421</v>
       </c>
       <c r="AA6" t="n">
-        <v>11.30162628399891</v>
+        <v>11.30162628399883</v>
       </c>
       <c r="AB6" t="n">
-        <v>20.94681464554228</v>
+        <v>20.94681464554231</v>
       </c>
     </row>
     <row r="7">
@@ -2394,82 +2394,82 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>10.04071764998598</v>
+        <v>10.0407176499858</v>
       </c>
       <c r="C7" t="n">
-        <v>10.49491016748834</v>
+        <v>10.49491016748804</v>
       </c>
       <c r="D7" t="n">
-        <v>10.49253874368142</v>
+        <v>10.49253874368137</v>
       </c>
       <c r="E7" t="n">
-        <v>10.196091374718</v>
+        <v>10.19609137471801</v>
       </c>
       <c r="F7" t="n">
-        <v>10.08915767294629</v>
+        <v>10.08915767294631</v>
       </c>
       <c r="G7" t="n">
-        <v>10.54713619808749</v>
+        <v>10.54713619808739</v>
       </c>
       <c r="H7" t="n">
-        <v>10.49253874368142</v>
+        <v>10.49253874368137</v>
       </c>
       <c r="I7" t="n">
-        <v>10.49253874368142</v>
+        <v>10.49253874368137</v>
       </c>
       <c r="J7" t="n">
-        <v>10.43357865265185</v>
+        <v>10.4335786526518</v>
       </c>
       <c r="K7" t="n">
-        <v>10.49253874368142</v>
+        <v>10.49253874368137</v>
       </c>
       <c r="L7" t="n">
-        <v>10.49253874368142</v>
+        <v>10.49253874368137</v>
       </c>
       <c r="M7" t="n">
         <v>10.54184115557596</v>
       </c>
       <c r="N7" t="n">
-        <v>10.14230180805242</v>
+        <v>10.14230180805226</v>
       </c>
       <c r="O7" t="n">
-        <v>10.19945936632027</v>
+        <v>10.19945936632012</v>
       </c>
       <c r="P7" t="n">
-        <v>10.17586661883145</v>
+        <v>10.17586661883131</v>
       </c>
       <c r="Q7" t="n">
-        <v>9.951924492754316</v>
+        <v>9.951924492754101</v>
       </c>
       <c r="R7" t="n">
-        <v>10.49253874368142</v>
+        <v>10.49253874368137</v>
       </c>
       <c r="S7" t="n">
-        <v>10.49253874368142</v>
+        <v>10.49253874368137</v>
       </c>
       <c r="T7" t="n">
-        <v>10.49253874368142</v>
+        <v>10.49253874368137</v>
       </c>
       <c r="U7" t="n">
-        <v>10.23281597902506</v>
+        <v>10.23281597902498</v>
       </c>
       <c r="V7" t="n">
-        <v>10.27407573371772</v>
+        <v>10.27407573371785</v>
       </c>
       <c r="W7" t="n">
-        <v>10.45353694678633</v>
+        <v>10.45353694678632</v>
       </c>
       <c r="X7" t="n">
-        <v>9.954244201076472</v>
+        <v>9.954244201076488</v>
       </c>
       <c r="Y7" t="n">
-        <v>10.94159570072428</v>
+        <v>10.94159570072413</v>
       </c>
       <c r="Z7" t="n">
-        <v>10.03232484120298</v>
+        <v>10.03232484120287</v>
       </c>
       <c r="AA7" t="n">
-        <v>10.49253874368142</v>
+        <v>10.49253874368137</v>
       </c>
       <c r="AB7" t="n">
         <v>11.02469356988943</v>
@@ -2638,85 +2638,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>14.82728848146607</v>
+        <v>14.82728848146608</v>
       </c>
       <c r="C2" t="n">
-        <v>10.56773154003308</v>
+        <v>10.56773154003309</v>
       </c>
       <c r="D2" t="n">
-        <v>16.59710956329358</v>
+        <v>16.59710956329356</v>
       </c>
       <c r="E2" t="n">
-        <v>10.82033362177221</v>
+        <v>10.8203336217722</v>
       </c>
       <c r="F2" t="n">
-        <v>16.12402908264006</v>
+        <v>16.12402908264007</v>
       </c>
       <c r="G2" t="n">
-        <v>30.14227935199255</v>
+        <v>30.14227935199257</v>
       </c>
       <c r="H2" t="n">
-        <v>10.93634225643013</v>
+        <v>10.93634225643009</v>
       </c>
       <c r="I2" t="n">
-        <v>14.41237789946614</v>
+        <v>14.41237789946611</v>
       </c>
       <c r="J2" t="n">
-        <v>22.07774374567766</v>
+        <v>22.07774374567763</v>
       </c>
       <c r="K2" t="n">
-        <v>14.85159838616524</v>
+        <v>14.85159838616523</v>
       </c>
       <c r="L2" t="n">
-        <v>12.4925172338925</v>
+        <v>12.49251723389244</v>
       </c>
       <c r="M2" t="n">
         <v>36.30378577156744</v>
       </c>
       <c r="N2" t="n">
-        <v>12.59207881809516</v>
+        <v>12.59207881809512</v>
       </c>
       <c r="O2" t="n">
-        <v>15.57093842739465</v>
+        <v>15.57093842739464</v>
       </c>
       <c r="P2" t="n">
-        <v>20.62688517930855</v>
+        <v>20.62688517930857</v>
       </c>
       <c r="Q2" t="n">
-        <v>13.16733112656407</v>
+        <v>13.16733112656408</v>
       </c>
       <c r="R2" t="n">
-        <v>11.05425234267899</v>
+        <v>11.05425234267894</v>
       </c>
       <c r="S2" t="n">
-        <v>16.71498757627921</v>
+        <v>16.71498757627917</v>
       </c>
       <c r="T2" t="n">
-        <v>12.44124972394334</v>
+        <v>12.44124972394332</v>
       </c>
       <c r="U2" t="n">
-        <v>14.28035502974753</v>
+        <v>14.28035502974752</v>
       </c>
       <c r="V2" t="n">
-        <v>14.03814588170131</v>
+        <v>14.03814588170142</v>
       </c>
       <c r="W2" t="n">
-        <v>15.9539845314877</v>
+        <v>15.9539845314876</v>
       </c>
       <c r="X2" t="n">
-        <v>16.51602570036772</v>
+        <v>16.51602570036768</v>
       </c>
       <c r="Y2" t="n">
-        <v>22.39982918835571</v>
+        <v>22.39982918835566</v>
       </c>
       <c r="Z2" t="n">
-        <v>15.93502411903017</v>
+        <v>15.93502411903012</v>
       </c>
       <c r="AA2" t="n">
-        <v>13.53151047811795</v>
+        <v>13.53151047811792</v>
       </c>
       <c r="AB2" t="n">
-        <v>38.90559816779673</v>
+        <v>38.90559816779645</v>
       </c>
     </row>
     <row r="3">
@@ -2726,85 +2726,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>11.22269781079564</v>
+        <v>11.22269781079572</v>
       </c>
       <c r="C3" t="n">
         <v>12.45498804954638</v>
       </c>
       <c r="D3" t="n">
-        <v>12.45296694184632</v>
+        <v>12.45296694184634</v>
       </c>
       <c r="E3" t="n">
-        <v>11.74220983961227</v>
+        <v>11.74220983961228</v>
       </c>
       <c r="F3" t="n">
         <v>11.39874051853363</v>
       </c>
       <c r="G3" t="n">
-        <v>12.70807126063389</v>
+        <v>12.70807126063395</v>
       </c>
       <c r="H3" t="n">
-        <v>12.45296694184632</v>
+        <v>12.45296694184634</v>
       </c>
       <c r="I3" t="n">
-        <v>12.45296694184632</v>
+        <v>12.45296694184634</v>
       </c>
       <c r="J3" t="n">
-        <v>12.4321553459249</v>
+        <v>12.432155345925</v>
       </c>
       <c r="K3" t="n">
-        <v>12.45296694184632</v>
+        <v>12.45296694184634</v>
       </c>
       <c r="L3" t="n">
-        <v>12.45296694184632</v>
+        <v>12.45296694184634</v>
       </c>
       <c r="M3" t="n">
-        <v>12.49221357672783</v>
+        <v>12.49221357672782</v>
       </c>
       <c r="N3" t="n">
-        <v>11.49930254576028</v>
+        <v>11.49930254576031</v>
       </c>
       <c r="O3" t="n">
-        <v>11.76137780237615</v>
+        <v>11.76137780237627</v>
       </c>
       <c r="P3" t="n">
-        <v>11.69713682434904</v>
+        <v>11.69713682434909</v>
       </c>
       <c r="Q3" t="n">
-        <v>10.98092184700131</v>
+        <v>10.9809218470014</v>
       </c>
       <c r="R3" t="n">
-        <v>12.45296694184632</v>
+        <v>12.45296694184634</v>
       </c>
       <c r="S3" t="n">
-        <v>12.45296694184632</v>
+        <v>12.45296694184634</v>
       </c>
       <c r="T3" t="n">
-        <v>12.45296694184632</v>
+        <v>12.45296694184634</v>
       </c>
       <c r="U3" t="n">
-        <v>11.85218419944847</v>
+        <v>11.8521841994487</v>
       </c>
       <c r="V3" t="n">
-        <v>12.06095482532594</v>
+        <v>12.06095482532605</v>
       </c>
       <c r="W3" t="n">
-        <v>12.4532087250607</v>
+        <v>12.45320872506077</v>
       </c>
       <c r="X3" t="n">
-        <v>11.09367845749227</v>
+        <v>11.09367845749233</v>
       </c>
       <c r="Y3" t="n">
-        <v>13.67567411236267</v>
+        <v>13.67567411236256</v>
       </c>
       <c r="Z3" t="n">
-        <v>11.19984493005886</v>
+        <v>11.19984493005883</v>
       </c>
       <c r="AA3" t="n">
-        <v>12.45296694184632</v>
+        <v>12.45296694184634</v>
       </c>
       <c r="AB3" t="n">
-        <v>13.79092406175516</v>
+        <v>13.79092406175506</v>
       </c>
     </row>
     <row r="4">
@@ -2814,85 +2814,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>23.80567667775716</v>
+        <v>23.80567667775806</v>
       </c>
       <c r="C4" t="n">
-        <v>22.2544026285255</v>
+        <v>22.25440262852509</v>
       </c>
       <c r="D4" t="n">
-        <v>24.4507556797952</v>
+        <v>24.45075567979579</v>
       </c>
       <c r="E4" t="n">
-        <v>22.30980651594571</v>
+        <v>22.3098065159462</v>
       </c>
       <c r="F4" t="n">
-        <v>24.26839744074768</v>
+        <v>24.26839744074811</v>
       </c>
       <c r="G4" t="n">
-        <v>29.38781101236319</v>
+        <v>29.38781101236254</v>
       </c>
       <c r="H4" t="n">
-        <v>22.38747246852996</v>
+        <v>22.38747246852979</v>
       </c>
       <c r="I4" t="n">
-        <v>23.65444664274514</v>
+        <v>23.65444664274511</v>
       </c>
       <c r="J4" t="n">
-        <v>25.46402272726198</v>
+        <v>25.46402272726175</v>
       </c>
       <c r="K4" t="n">
-        <v>23.81453735255838</v>
+        <v>23.81453735255958</v>
       </c>
       <c r="L4" t="n">
-        <v>22.95467997428506</v>
+        <v>22.95467997428564</v>
       </c>
       <c r="M4" t="n">
-        <v>31.65854944756052</v>
+        <v>31.65854944756064</v>
       </c>
       <c r="N4" t="n">
-        <v>22.9909690026168</v>
+        <v>22.99096900261637</v>
       </c>
       <c r="O4" t="n">
-        <v>24.07672835067117</v>
+        <v>24.07672835067045</v>
       </c>
       <c r="P4" t="n">
-        <v>25.91956157181798</v>
+        <v>25.91956157181885</v>
       </c>
       <c r="Q4" t="n">
-        <v>23.20064171409919</v>
+        <v>23.20064171409967</v>
       </c>
       <c r="R4" t="n">
-        <v>22.43044931039676</v>
+        <v>22.43044931039735</v>
       </c>
       <c r="S4" t="n">
-        <v>24.49372083133588</v>
+        <v>24.4937208313355</v>
       </c>
       <c r="T4" t="n">
-        <v>22.93599356892325</v>
+        <v>22.93599356892268</v>
       </c>
       <c r="U4" t="n">
-        <v>23.60632585702403</v>
+        <v>23.60632585702348</v>
       </c>
       <c r="V4" t="n">
-        <v>17.00366262639221</v>
+        <v>17.00366262639249</v>
       </c>
       <c r="W4" t="n">
-        <v>24.21634415766002</v>
+        <v>24.21634415765794</v>
       </c>
       <c r="X4" t="n">
-        <v>24.42120156389358</v>
+        <v>24.42120156389409</v>
       </c>
       <c r="Y4" t="n">
-        <v>26.56577884415777</v>
+        <v>26.56577884415688</v>
       </c>
       <c r="Z4" t="n">
-        <v>24.20943330996133</v>
+        <v>24.20943330996158</v>
       </c>
       <c r="AA4" t="n">
-        <v>23.33338081133087</v>
+        <v>23.33338081133117</v>
       </c>
       <c r="AB4" t="n">
-        <v>32.61551707444259</v>
+        <v>32.61551707444292</v>
       </c>
     </row>
     <row r="5">
@@ -2902,85 +2902,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>22.49184570554025</v>
+        <v>22.49184570553938</v>
       </c>
       <c r="C5" t="n">
-        <v>22.9422854649586</v>
+        <v>22.94228546495786</v>
       </c>
       <c r="D5" t="n">
-        <v>22.9402643572575</v>
+        <v>22.94026435725792</v>
       </c>
       <c r="E5" t="n">
-        <v>22.64581957213233</v>
+        <v>22.6458195721318</v>
       </c>
       <c r="F5" t="n">
-        <v>22.54608524627093</v>
+        <v>22.54608524627105</v>
       </c>
       <c r="G5" t="n">
-        <v>23.03324688587058</v>
+        <v>23.03324688586987</v>
       </c>
       <c r="H5" t="n">
-        <v>22.9402643572575</v>
+        <v>22.94026435725792</v>
       </c>
       <c r="I5" t="n">
-        <v>22.9402643572575</v>
+        <v>22.94026435725792</v>
       </c>
       <c r="J5" t="n">
-        <v>21.94831901977024</v>
+        <v>21.94831901976934</v>
       </c>
       <c r="K5" t="n">
-        <v>22.9402643572575</v>
+        <v>22.94026435725792</v>
       </c>
       <c r="L5" t="n">
-        <v>22.9402643572575</v>
+        <v>22.94026435725792</v>
       </c>
       <c r="M5" t="n">
-        <v>22.97951099213958</v>
+        <v>22.97951099213923</v>
       </c>
       <c r="N5" t="n">
-        <v>22.59266488337738</v>
+        <v>22.5926648833773</v>
       </c>
       <c r="O5" t="n">
-        <v>22.68818823697168</v>
+        <v>22.68818823697074</v>
       </c>
       <c r="P5" t="n">
-        <v>22.66477315483545</v>
+        <v>22.66477315483538</v>
       </c>
       <c r="Q5" t="n">
-        <v>22.40372120581275</v>
+        <v>22.40372120581306</v>
       </c>
       <c r="R5" t="n">
-        <v>22.9402643572575</v>
+        <v>22.94026435725792</v>
       </c>
       <c r="S5" t="n">
-        <v>22.9402643572575</v>
+        <v>22.94026435725792</v>
       </c>
       <c r="T5" t="n">
-        <v>22.9402643572575</v>
+        <v>22.94026435725792</v>
       </c>
       <c r="U5" t="n">
-        <v>22.72128610240063</v>
+        <v>22.72128610240103</v>
       </c>
       <c r="V5" t="n">
-        <v>16.28299970369297</v>
+        <v>16.28299970369284</v>
       </c>
       <c r="W5" t="n">
-        <v>22.94035248440007</v>
+        <v>22.94035248440039</v>
       </c>
       <c r="X5" t="n">
-        <v>22.44481966628256</v>
+        <v>22.44481966628216</v>
       </c>
       <c r="Y5" t="n">
-        <v>23.38592676315825</v>
+        <v>23.3859267631585</v>
       </c>
       <c r="Z5" t="n">
-        <v>22.4835160988634</v>
+        <v>22.48351609886289</v>
       </c>
       <c r="AA5" t="n">
-        <v>22.9402643572575</v>
+        <v>22.94026435725792</v>
       </c>
       <c r="AB5" t="n">
-        <v>23.46151327418477</v>
+        <v>23.46151327418366</v>
       </c>
     </row>
     <row r="6">
@@ -2990,85 +2990,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>11.34504602975433</v>
+        <v>11.3450460297543</v>
       </c>
       <c r="C6" t="n">
-        <v>9.793771980521333</v>
+        <v>9.79377198052134</v>
       </c>
       <c r="D6" t="n">
-        <v>11.99012503179208</v>
+        <v>11.99012503179204</v>
       </c>
       <c r="E6" t="n">
         <v>9.849175867942458</v>
       </c>
       <c r="F6" t="n">
-        <v>11.80776679274435</v>
+        <v>11.80776679274436</v>
       </c>
       <c r="G6" t="n">
-        <v>16.88815523316315</v>
+        <v>16.88815523316311</v>
       </c>
       <c r="H6" t="n">
-        <v>9.926841820526098</v>
+        <v>9.926841820526054</v>
       </c>
       <c r="I6" t="n">
-        <v>11.1938159947414</v>
+        <v>11.19381599474136</v>
       </c>
       <c r="J6" t="n">
-        <v>13.93692959531508</v>
+        <v>13.93692959531517</v>
       </c>
       <c r="K6" t="n">
-        <v>11.35390670455588</v>
+        <v>11.35390670455583</v>
       </c>
       <c r="L6" t="n">
-        <v>10.49404932628193</v>
+        <v>10.49404932628189</v>
       </c>
       <c r="M6" t="n">
-        <v>19.19791879955692</v>
+        <v>19.19791879955693</v>
       </c>
       <c r="N6" t="n">
-        <v>10.53033835461265</v>
+        <v>10.53033835461262</v>
       </c>
       <c r="O6" t="n">
-        <v>11.57707257147111</v>
+        <v>11.57707257147103</v>
       </c>
       <c r="P6" t="n">
-        <v>13.41990579261949</v>
+        <v>13.41990579261945</v>
       </c>
       <c r="Q6" t="n">
         <v>10.74001106609592</v>
       </c>
       <c r="R6" t="n">
-        <v>9.969818662393676</v>
+        <v>9.969818662393619</v>
       </c>
       <c r="S6" t="n">
-        <v>12.03309018333182</v>
+        <v>12.03309018333177</v>
       </c>
       <c r="T6" t="n">
-        <v>10.475362920919</v>
+        <v>10.47536292091893</v>
       </c>
       <c r="U6" t="n">
-        <v>11.10667007782409</v>
+        <v>11.10667007782405</v>
       </c>
       <c r="V6" t="n">
-        <v>10.98523682215982</v>
+        <v>10.98523682215993</v>
       </c>
       <c r="W6" t="n">
-        <v>11.71668837845855</v>
+        <v>11.71668837845849</v>
       </c>
       <c r="X6" t="n">
-        <v>11.9215457846947</v>
+        <v>11.92154578469465</v>
       </c>
       <c r="Y6" t="n">
-        <v>14.10514819615318</v>
+        <v>14.10514819615315</v>
       </c>
       <c r="Z6" t="n">
-        <v>11.74880266195789</v>
+        <v>11.74880266195781</v>
       </c>
       <c r="AA6" t="n">
-        <v>10.87275016332746</v>
+        <v>10.87275016332743</v>
       </c>
       <c r="AB6" t="n">
-        <v>20.15488642643925</v>
+        <v>20.15488642643917</v>
       </c>
     </row>
     <row r="7">
@@ -3078,85 +3078,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>10.03121505753564</v>
+        <v>10.03121505753561</v>
       </c>
       <c r="C7" t="n">
         <v>10.48165481695413</v>
       </c>
       <c r="D7" t="n">
-        <v>10.47963370925409</v>
+        <v>10.47963370925417</v>
       </c>
       <c r="E7" t="n">
-        <v>10.18518892412808</v>
+        <v>10.18518892412807</v>
       </c>
       <c r="F7" t="n">
-        <v>10.0854545982673</v>
+        <v>10.08545459826731</v>
       </c>
       <c r="G7" t="n">
-        <v>10.5335911066703</v>
+        <v>10.53359110667042</v>
       </c>
       <c r="H7" t="n">
-        <v>10.47963370925409</v>
+        <v>10.47963370925417</v>
       </c>
       <c r="I7" t="n">
-        <v>10.47963370925409</v>
+        <v>10.47963370925417</v>
       </c>
       <c r="J7" t="n">
         <v>10.42122588782274</v>
       </c>
       <c r="K7" t="n">
-        <v>10.47963370925409</v>
+        <v>10.47963370925417</v>
       </c>
       <c r="L7" t="n">
-        <v>10.47963370925409</v>
+        <v>10.47963370925417</v>
       </c>
       <c r="M7" t="n">
-        <v>10.51888034413548</v>
+        <v>10.51888034413547</v>
       </c>
       <c r="N7" t="n">
-        <v>10.13203423537346</v>
+        <v>10.13203423537355</v>
       </c>
       <c r="O7" t="n">
-        <v>10.18853245777129</v>
+        <v>10.18853245777131</v>
       </c>
       <c r="P7" t="n">
-        <v>10.165117375636</v>
+        <v>10.16511737563595</v>
       </c>
       <c r="Q7" t="n">
-        <v>9.943090557809338</v>
+        <v>9.943090557809304</v>
       </c>
       <c r="R7" t="n">
-        <v>10.47963370925409</v>
+        <v>10.47963370925417</v>
       </c>
       <c r="S7" t="n">
-        <v>10.47963370925409</v>
+        <v>10.47963370925417</v>
       </c>
       <c r="T7" t="n">
-        <v>10.47963370925409</v>
+        <v>10.47963370925417</v>
       </c>
       <c r="U7" t="n">
-        <v>10.22163032320153</v>
+        <v>10.22163032320158</v>
       </c>
       <c r="V7" t="n">
-        <v>10.26457389946057</v>
+        <v>10.2645738994606</v>
       </c>
       <c r="W7" t="n">
-        <v>10.44069670520091</v>
+        <v>10.44069670520097</v>
       </c>
       <c r="X7" t="n">
-        <v>9.945163887082666</v>
+        <v>9.945163887082691</v>
       </c>
       <c r="Y7" t="n">
-        <v>10.9252961151548</v>
+        <v>10.92529611515474</v>
       </c>
       <c r="Z7" t="n">
         <v>10.02288545085914</v>
       </c>
       <c r="AA7" t="n">
-        <v>10.47963370925409</v>
+        <v>10.47963370925417</v>
       </c>
       <c r="AB7" t="n">
-        <v>11.00088262617993</v>
+        <v>11.0008826261799</v>
       </c>
     </row>
   </sheetData>
@@ -3322,82 +3322,82 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>14.6674997526304</v>
+        <v>14.66749975263022</v>
       </c>
       <c r="C2" t="n">
-        <v>10.8708472963734</v>
+        <v>10.87084729637339</v>
       </c>
       <c r="D2" t="n">
-        <v>15.04194506781815</v>
+        <v>15.04194506781798</v>
       </c>
       <c r="E2" t="n">
-        <v>10.30837012148539</v>
+        <v>10.30837012148538</v>
       </c>
       <c r="F2" t="n">
         <v>17.16082369631989</v>
       </c>
       <c r="G2" t="n">
-        <v>27.54604036878357</v>
+        <v>27.54604036878352</v>
       </c>
       <c r="H2" t="n">
-        <v>11.13203496219106</v>
+        <v>11.13203496219087</v>
       </c>
       <c r="I2" t="n">
-        <v>15.02034777867657</v>
+        <v>15.02034777867638</v>
       </c>
       <c r="J2" t="n">
-        <v>20.7575491686935</v>
+        <v>20.75754916869341</v>
       </c>
       <c r="K2" t="n">
-        <v>15.32951675497825</v>
+        <v>15.32951675497809</v>
       </c>
       <c r="L2" t="n">
-        <v>12.54874490020064</v>
+        <v>12.54874490020053</v>
       </c>
       <c r="M2" t="n">
-        <v>32.19869710733995</v>
+        <v>32.19869710734007</v>
       </c>
       <c r="N2" t="n">
-        <v>12.09373520055726</v>
+        <v>12.09373520055707</v>
       </c>
       <c r="O2" t="n">
-        <v>14.03995861447749</v>
+        <v>14.0399586144773</v>
       </c>
       <c r="P2" t="n">
-        <v>19.62274418213174</v>
+        <v>19.62274418213165</v>
       </c>
       <c r="Q2" t="n">
-        <v>12.80096779021284</v>
+        <v>12.80096779021265</v>
       </c>
       <c r="R2" t="n">
-        <v>12.84123139663857</v>
+        <v>12.84123139663839</v>
       </c>
       <c r="S2" t="n">
-        <v>16.37909347077539</v>
+        <v>16.37909347077526</v>
       </c>
       <c r="T2" t="n">
-        <v>13.01050815000752</v>
+        <v>13.01050815000735</v>
       </c>
       <c r="U2" t="n">
-        <v>13.08767567458271</v>
+        <v>13.08767567458253</v>
       </c>
       <c r="V2" t="n">
-        <v>15.65706996235109</v>
+        <v>15.65706996235105</v>
       </c>
       <c r="W2" t="n">
-        <v>15.85893660680629</v>
+        <v>15.8589366068061</v>
       </c>
       <c r="X2" t="n">
-        <v>16.91982510533224</v>
+        <v>16.91982510533212</v>
       </c>
       <c r="Y2" t="n">
-        <v>28.31341075819107</v>
+        <v>28.31341075819101</v>
       </c>
       <c r="Z2" t="n">
-        <v>15.18866409129319</v>
+        <v>15.18866409129313</v>
       </c>
       <c r="AA2" t="n">
-        <v>13.91926507767603</v>
+        <v>13.91926507767586</v>
       </c>
       <c r="AB2" t="n">
         <v>36.21562771399684</v>
@@ -3410,13 +3410,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>11.19187398084706</v>
+        <v>11.19187398084698</v>
       </c>
       <c r="C3" t="n">
-        <v>12.41907699494234</v>
+        <v>12.41907699494235</v>
       </c>
       <c r="D3" t="n">
-        <v>12.41325688882981</v>
+        <v>12.41325688882964</v>
       </c>
       <c r="E3" t="n">
         <v>11.71033525408429</v>
@@ -3425,67 +3425,67 @@
         <v>11.37399294675473</v>
       </c>
       <c r="G3" t="n">
-        <v>12.66651859137607</v>
+        <v>12.66651859137586</v>
       </c>
       <c r="H3" t="n">
-        <v>12.41325688882981</v>
+        <v>12.41325688882964</v>
       </c>
       <c r="I3" t="n">
-        <v>12.41325688882981</v>
+        <v>12.41325688882964</v>
       </c>
       <c r="J3" t="n">
         <v>12.39501901807052</v>
       </c>
       <c r="K3" t="n">
-        <v>12.41325688882981</v>
+        <v>12.41325688882964</v>
       </c>
       <c r="L3" t="n">
-        <v>12.41325688882981</v>
+        <v>12.41325688882964</v>
       </c>
       <c r="M3" t="n">
-        <v>12.44461898581031</v>
+        <v>12.44461898581042</v>
       </c>
       <c r="N3" t="n">
-        <v>11.4664808022545</v>
+        <v>11.46648080225444</v>
       </c>
       <c r="O3" t="n">
-        <v>11.72666309160804</v>
+        <v>11.72666309160781</v>
       </c>
       <c r="P3" t="n">
-        <v>11.66288612559729</v>
+        <v>11.66288612559707</v>
       </c>
       <c r="Q3" t="n">
-        <v>10.95184436270273</v>
+        <v>10.95184436270267</v>
       </c>
       <c r="R3" t="n">
-        <v>12.41325688882981</v>
+        <v>12.41325688882964</v>
       </c>
       <c r="S3" t="n">
-        <v>12.41325688882981</v>
+        <v>12.41325688882964</v>
       </c>
       <c r="T3" t="n">
-        <v>12.41325688882981</v>
+        <v>12.41325688882964</v>
       </c>
       <c r="U3" t="n">
-        <v>11.81687391961214</v>
+        <v>11.81687391961197</v>
       </c>
       <c r="V3" t="n">
-        <v>12.0309885962193</v>
+        <v>12.03098859621923</v>
       </c>
       <c r="W3" t="n">
-        <v>12.41349692564903</v>
+        <v>12.4134969256489</v>
       </c>
       <c r="X3" t="n">
-        <v>11.06378653319383</v>
+        <v>11.0637865331938</v>
       </c>
       <c r="Y3" t="n">
-        <v>13.62723565432596</v>
+        <v>13.62723565432585</v>
       </c>
       <c r="Z3" t="n">
-        <v>11.16918616626551</v>
+        <v>11.16918616626535</v>
       </c>
       <c r="AA3" t="n">
-        <v>12.41325688882981</v>
+        <v>12.41325688882964</v>
       </c>
       <c r="AB3" t="n">
         <v>13.73645766734679</v>
@@ -3498,82 +3498,82 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>23.59771363714614</v>
+        <v>23.59771363714604</v>
       </c>
       <c r="C4" t="n">
-        <v>22.21757714516221</v>
+        <v>22.21757714516219</v>
       </c>
       <c r="D4" t="n">
-        <v>23.73419455757322</v>
+        <v>23.73419455757309</v>
       </c>
       <c r="E4" t="n">
-        <v>21.97545241799386</v>
+        <v>21.97545241799385</v>
       </c>
       <c r="F4" t="n">
-        <v>24.50131629410937</v>
+        <v>24.50131629410934</v>
       </c>
       <c r="G4" t="n">
-        <v>28.29179046427491</v>
+        <v>28.29179046427486</v>
       </c>
       <c r="H4" t="n">
-        <v>22.30907823655461</v>
+        <v>22.30907823655449</v>
       </c>
       <c r="I4" t="n">
-        <v>23.72632259928926</v>
+        <v>23.72632259928914</v>
       </c>
       <c r="J4" t="n">
-        <v>24.87128022485125</v>
+        <v>24.87128022485116</v>
       </c>
       <c r="K4" t="n">
-        <v>23.83901106070584</v>
+        <v>23.83901106070571</v>
       </c>
       <c r="L4" t="n">
-        <v>22.82545237311108</v>
+        <v>22.82545237311101</v>
       </c>
       <c r="M4" t="n">
-        <v>30.00756019212827</v>
+        <v>30.00756019212834</v>
       </c>
       <c r="N4" t="n">
-        <v>22.65960668058474</v>
+        <v>22.65960668058462</v>
       </c>
       <c r="O4" t="n">
-        <v>23.36898226124949</v>
+        <v>23.36898226124938</v>
       </c>
       <c r="P4" t="n">
-        <v>25.40384204428154</v>
+        <v>25.40384204428145</v>
       </c>
       <c r="Q4" t="n">
-        <v>22.91738465476984</v>
+        <v>22.91738465476971</v>
       </c>
       <c r="R4" t="n">
-        <v>22.93206026651288</v>
+        <v>22.93206026651276</v>
       </c>
       <c r="S4" t="n">
-        <v>24.22156944886191</v>
+        <v>24.22156944886171</v>
       </c>
       <c r="T4" t="n">
-        <v>22.99375965536789</v>
+        <v>22.99375965536775</v>
       </c>
       <c r="U4" t="n">
-        <v>23.02188631192871</v>
+        <v>23.02188631192858</v>
       </c>
       <c r="V4" t="n">
-        <v>17.69240489244378</v>
+        <v>17.69240489244407</v>
       </c>
       <c r="W4" t="n">
-        <v>24.03197837993537</v>
+        <v>24.03197837993526</v>
       </c>
       <c r="X4" t="n">
-        <v>24.41865978006636</v>
+        <v>24.41865978006628</v>
       </c>
       <c r="Y4" t="n">
-        <v>28.57148796029589</v>
+        <v>28.57148796029581</v>
       </c>
       <c r="Z4" t="n">
-        <v>23.78767191876819</v>
+        <v>23.78767191876801</v>
       </c>
       <c r="AA4" t="n">
-        <v>23.32499088434043</v>
+        <v>23.32499088434031</v>
       </c>
       <c r="AB4" t="n">
         <v>31.48185375387846</v>
@@ -3586,85 +3586,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>22.33088885618957</v>
+        <v>22.3308888561894</v>
       </c>
       <c r="C5" t="n">
-        <v>22.78188869005962</v>
+        <v>22.78188869005958</v>
       </c>
       <c r="D5" t="n">
-        <v>22.77606858394698</v>
+        <v>22.77606858394687</v>
       </c>
       <c r="E5" t="n">
-        <v>22.48645224612042</v>
+        <v>22.48645224612039</v>
       </c>
       <c r="F5" t="n">
-        <v>22.39208443829029</v>
+        <v>22.39208443829028</v>
       </c>
       <c r="G5" t="n">
-        <v>22.8683795005761</v>
+        <v>22.86837950057592</v>
       </c>
       <c r="H5" t="n">
-        <v>22.77606858394698</v>
+        <v>22.77606858394687</v>
       </c>
       <c r="I5" t="n">
-        <v>22.77606858394698</v>
+        <v>22.77606858394687</v>
       </c>
       <c r="J5" t="n">
-        <v>21.82323618273599</v>
+        <v>21.82323618273594</v>
       </c>
       <c r="K5" t="n">
-        <v>22.77606858394698</v>
+        <v>22.77606858394687</v>
       </c>
       <c r="L5" t="n">
-        <v>22.77606858394698</v>
+        <v>22.77606858394687</v>
       </c>
       <c r="M5" t="n">
-        <v>22.80743068092742</v>
+        <v>22.8074306809275</v>
       </c>
       <c r="N5" t="n">
-        <v>22.43097981799651</v>
+        <v>22.43097981799632</v>
       </c>
       <c r="O5" t="n">
-        <v>22.52581320725106</v>
+        <v>22.52581320725093</v>
       </c>
       <c r="P5" t="n">
-        <v>22.50256725204706</v>
+        <v>22.50256725204696</v>
       </c>
       <c r="Q5" t="n">
-        <v>22.2434008789461</v>
+        <v>22.24340087894588</v>
       </c>
       <c r="R5" t="n">
-        <v>22.77606858394698</v>
+        <v>22.77606858394687</v>
       </c>
       <c r="S5" t="n">
-        <v>22.77606858394698</v>
+        <v>22.77606858394687</v>
       </c>
       <c r="T5" t="n">
-        <v>22.77606858394698</v>
+        <v>22.77606858394687</v>
       </c>
       <c r="U5" t="n">
-        <v>22.55869399474962</v>
+        <v>22.55869399474943</v>
       </c>
       <c r="V5" t="n">
-        <v>16.37074081408586</v>
+        <v>16.37074081408618</v>
       </c>
       <c r="W5" t="n">
-        <v>22.77615607454901</v>
+        <v>22.77615607454885</v>
       </c>
       <c r="X5" t="n">
-        <v>22.28420248559865</v>
+        <v>22.28420248559856</v>
       </c>
       <c r="Y5" t="n">
-        <v>23.21854958871196</v>
+        <v>23.21854958871185</v>
       </c>
       <c r="Z5" t="n">
-        <v>22.32261941418832</v>
+        <v>22.32261941418817</v>
       </c>
       <c r="AA5" t="n">
-        <v>22.77606858394698</v>
+        <v>22.77606858394687</v>
       </c>
       <c r="AB5" t="n">
-        <v>23.28846023561617</v>
+        <v>23.28846023561615</v>
       </c>
     </row>
     <row r="6">
@@ -3674,82 +3674,82 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>11.27603460522708</v>
+        <v>11.27603460522692</v>
       </c>
       <c r="C6" t="n">
-        <v>9.895898113243099</v>
+        <v>9.895898113243097</v>
       </c>
       <c r="D6" t="n">
-        <v>11.41251552565412</v>
+        <v>11.41251552565397</v>
       </c>
       <c r="E6" t="n">
         <v>9.653773386074727</v>
       </c>
       <c r="F6" t="n">
-        <v>12.17963726219025</v>
+        <v>12.17963726219022</v>
       </c>
       <c r="G6" t="n">
-        <v>15.93115565205768</v>
+        <v>15.93115565205743</v>
       </c>
       <c r="H6" t="n">
-        <v>9.987399204635537</v>
+        <v>9.987399204635384</v>
       </c>
       <c r="I6" t="n">
-        <v>11.40464356737019</v>
+        <v>11.40464356737002</v>
       </c>
       <c r="J6" t="n">
-        <v>13.44666728011812</v>
+        <v>13.44666728011803</v>
       </c>
       <c r="K6" t="n">
-        <v>11.51733202878673</v>
+        <v>11.51733202878658</v>
       </c>
       <c r="L6" t="n">
-        <v>10.50377334119203</v>
+        <v>10.5037733411919</v>
       </c>
       <c r="M6" t="n">
-        <v>17.68588116020915</v>
+        <v>17.6858811602091</v>
       </c>
       <c r="N6" t="n">
-        <v>10.33792764866566</v>
+        <v>10.33792764866551</v>
       </c>
       <c r="O6" t="n">
-        <v>11.00834744903215</v>
+        <v>11.00834744903197</v>
       </c>
       <c r="P6" t="n">
-        <v>13.04320723206419</v>
+        <v>13.04320723206403</v>
       </c>
       <c r="Q6" t="n">
-        <v>10.59570562285076</v>
+        <v>10.59570562285061</v>
       </c>
       <c r="R6" t="n">
-        <v>10.61038123459381</v>
+        <v>10.61038123459365</v>
       </c>
       <c r="S6" t="n">
-        <v>11.89989041694283</v>
+        <v>11.89989041694262</v>
       </c>
       <c r="T6" t="n">
-        <v>10.67208062344881</v>
+        <v>10.67208062344864</v>
       </c>
       <c r="U6" t="n">
-        <v>10.66125149971137</v>
+        <v>10.66125149971117</v>
       </c>
       <c r="V6" t="n">
-        <v>11.56921842633333</v>
+        <v>11.56921842633329</v>
       </c>
       <c r="W6" t="n">
-        <v>11.67134356771803</v>
+        <v>11.67134356771783</v>
       </c>
       <c r="X6" t="n">
-        <v>12.0580249678489</v>
+        <v>12.05802496784885</v>
       </c>
       <c r="Y6" t="n">
-        <v>16.24980892837682</v>
+        <v>16.24980892837671</v>
       </c>
       <c r="Z6" t="n">
-        <v>11.4659928868491</v>
+        <v>11.4659928868489</v>
       </c>
       <c r="AA6" t="n">
-        <v>11.00331185242136</v>
+        <v>11.00331185242121</v>
       </c>
       <c r="AB6" t="n">
         <v>19.16017472195935</v>
@@ -3762,82 +3762,82 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>10.00920982427034</v>
+        <v>10.00920982427028</v>
       </c>
       <c r="C7" t="n">
-        <v>10.46020965814048</v>
+        <v>10.46020965814047</v>
       </c>
       <c r="D7" t="n">
-        <v>10.45438955202798</v>
+        <v>10.45438955202777</v>
       </c>
       <c r="E7" t="n">
         <v>10.16477321420128</v>
       </c>
       <c r="F7" t="n">
-        <v>10.07040540637118</v>
+        <v>10.07040540637117</v>
       </c>
       <c r="G7" t="n">
-        <v>10.50774468835858</v>
+        <v>10.5077446883585</v>
       </c>
       <c r="H7" t="n">
-        <v>10.45438955202798</v>
+        <v>10.45438955202777</v>
       </c>
       <c r="I7" t="n">
-        <v>10.45438955202798</v>
+        <v>10.45438955202777</v>
       </c>
       <c r="J7" t="n">
-        <v>10.39862323800281</v>
+        <v>10.39862323800279</v>
       </c>
       <c r="K7" t="n">
-        <v>10.45438955202798</v>
+        <v>10.45438955202777</v>
       </c>
       <c r="L7" t="n">
-        <v>10.45438955202798</v>
+        <v>10.45438955202777</v>
       </c>
       <c r="M7" t="n">
-        <v>10.48575164900828</v>
+        <v>10.4857516490082</v>
       </c>
       <c r="N7" t="n">
-        <v>10.10930078607728</v>
+        <v>10.10930078607721</v>
       </c>
       <c r="O7" t="n">
-        <v>10.16517839503369</v>
+        <v>10.16517839503354</v>
       </c>
       <c r="P7" t="n">
-        <v>10.14193243982969</v>
+        <v>10.14193243982955</v>
       </c>
       <c r="Q7" t="n">
-        <v>9.921721847026889</v>
+        <v>9.921721847026769</v>
       </c>
       <c r="R7" t="n">
-        <v>10.45438955202798</v>
+        <v>10.45438955202777</v>
       </c>
       <c r="S7" t="n">
-        <v>10.45438955202798</v>
+        <v>10.45438955202777</v>
       </c>
       <c r="T7" t="n">
-        <v>10.45438955202798</v>
+        <v>10.45438955202777</v>
       </c>
       <c r="U7" t="n">
-        <v>10.19805918253228</v>
+        <v>10.198059182532</v>
       </c>
       <c r="V7" t="n">
-        <v>10.24755434797537</v>
+        <v>10.2475543479754</v>
       </c>
       <c r="W7" t="n">
-        <v>10.41552126233155</v>
+        <v>10.41552126233142</v>
       </c>
       <c r="X7" t="n">
-        <v>9.92356767338131</v>
+        <v>9.923567673381154</v>
       </c>
       <c r="Y7" t="n">
-        <v>10.89687055679292</v>
+        <v>10.89687055679275</v>
       </c>
       <c r="Z7" t="n">
-        <v>10.00094038226925</v>
+        <v>10.00094038226905</v>
       </c>
       <c r="AA7" t="n">
-        <v>10.45438955202798</v>
+        <v>10.45438955202777</v>
       </c>
       <c r="AB7" t="n">
         <v>10.96678120369705</v>
@@ -4006,25 +4006,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>12.57124161591577</v>
+        <v>12.57124161591576</v>
       </c>
       <c r="C2" t="n">
         <v>10.12137117194905</v>
       </c>
       <c r="D2" t="n">
-        <v>11.18381452669846</v>
+        <v>11.18381452669847</v>
       </c>
       <c r="E2" t="n">
-        <v>10.58603257188571</v>
+        <v>10.58603257188572</v>
       </c>
       <c r="F2" t="n">
-        <v>11.02255996106693</v>
+        <v>11.02255996106694</v>
       </c>
       <c r="G2" t="n">
         <v>15.91486338241976</v>
       </c>
       <c r="H2" t="n">
-        <v>12.64260720460724</v>
+        <v>12.64260720460725</v>
       </c>
       <c r="I2" t="n">
         <v>11.54322816550942</v>
@@ -4033,7 +4033,7 @@
         <v>14.21007716521929</v>
       </c>
       <c r="K2" t="n">
-        <v>12.67951591729828</v>
+        <v>12.67951591729827</v>
       </c>
       <c r="L2" t="n">
         <v>12.77219444863345</v>
@@ -4048,34 +4048,34 @@
         <v>12.21475382529604</v>
       </c>
       <c r="P2" t="n">
-        <v>14.06637869064924</v>
+        <v>14.06637869064926</v>
       </c>
       <c r="Q2" t="n">
-        <v>12.60192239994415</v>
+        <v>12.60192239994414</v>
       </c>
       <c r="R2" t="n">
         <v>11.28022747040185</v>
       </c>
       <c r="S2" t="n">
-        <v>12.98302119004551</v>
+        <v>12.98302119004552</v>
       </c>
       <c r="T2" t="n">
-        <v>11.2616971519483</v>
+        <v>11.26169715194831</v>
       </c>
       <c r="U2" t="n">
-        <v>12.8104272278079</v>
+        <v>12.81042722780792</v>
       </c>
       <c r="V2" t="n">
-        <v>11.48628960111955</v>
+        <v>11.48628960111954</v>
       </c>
       <c r="W2" t="n">
         <v>15.63981004672912</v>
       </c>
       <c r="X2" t="n">
-        <v>12.95410083359613</v>
+        <v>12.95410083359614</v>
       </c>
       <c r="Y2" t="n">
-        <v>12.22048361703194</v>
+        <v>12.22048361703193</v>
       </c>
       <c r="Z2" t="n">
         <v>13.33545161702219</v>
@@ -4084,7 +4084,7 @@
         <v>12.13817980506644</v>
       </c>
       <c r="AB2" t="n">
-        <v>17.81667134274491</v>
+        <v>17.8166713427449</v>
       </c>
     </row>
     <row r="3">
@@ -4094,37 +4094,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>11.00044149648069</v>
+        <v>11.00044149648073</v>
       </c>
       <c r="C3" t="n">
-        <v>12.19441811502986</v>
+        <v>12.19441811502985</v>
       </c>
       <c r="D3" t="n">
-        <v>12.17695567794965</v>
+        <v>12.17695567794968</v>
       </c>
       <c r="E3" t="n">
         <v>11.5165293533171</v>
       </c>
       <c r="F3" t="n">
-        <v>11.17186424487917</v>
+        <v>11.17186424487916</v>
       </c>
       <c r="G3" t="n">
-        <v>12.4209135577613</v>
+        <v>12.42091355776132</v>
       </c>
       <c r="H3" t="n">
-        <v>12.17695567794965</v>
+        <v>12.17695567794968</v>
       </c>
       <c r="I3" t="n">
-        <v>12.17695567794965</v>
+        <v>12.17695567794968</v>
       </c>
       <c r="J3" t="n">
-        <v>12.1626240336713</v>
+        <v>12.16262403367129</v>
       </c>
       <c r="K3" t="n">
-        <v>12.17695567794965</v>
+        <v>12.17695567794968</v>
       </c>
       <c r="L3" t="n">
-        <v>12.17695567794965</v>
+        <v>12.17695567794968</v>
       </c>
       <c r="M3" t="n">
         <v>12.18976228064609</v>
@@ -4136,43 +4136,43 @@
         <v>11.51558459272671</v>
       </c>
       <c r="P3" t="n">
-        <v>11.45415053754562</v>
+        <v>11.45415053754565</v>
       </c>
       <c r="Q3" t="n">
         <v>10.76922960717114</v>
       </c>
       <c r="R3" t="n">
-        <v>12.17695567794965</v>
+        <v>12.17695567794968</v>
       </c>
       <c r="S3" t="n">
-        <v>12.17695567794965</v>
+        <v>12.17695567794968</v>
       </c>
       <c r="T3" t="n">
-        <v>12.17695567794965</v>
+        <v>12.17695567794968</v>
       </c>
       <c r="U3" t="n">
-        <v>11.60254798492077</v>
+        <v>11.60254798492076</v>
       </c>
       <c r="V3" t="n">
         <v>11.81906236212942</v>
       </c>
       <c r="W3" t="n">
-        <v>12.17718689679275</v>
+        <v>12.17718689679276</v>
       </c>
       <c r="X3" t="n">
         <v>10.87705946973053</v>
       </c>
       <c r="Y3" t="n">
-        <v>13.34645156231193</v>
+        <v>13.3464515623119</v>
       </c>
       <c r="Z3" t="n">
-        <v>10.97858714152844</v>
+        <v>10.97858714152845</v>
       </c>
       <c r="AA3" t="n">
-        <v>12.17695567794965</v>
+        <v>12.17695567794968</v>
       </c>
       <c r="AB3" t="n">
-        <v>13.40692220361865</v>
+        <v>13.40692220361863</v>
       </c>
     </row>
     <row r="4">
@@ -4182,49 +4182,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>22.10143843179105</v>
+        <v>22.10143843179104</v>
       </c>
       <c r="C4" t="n">
-        <v>21.21958700661512</v>
+        <v>21.21958700661514</v>
       </c>
       <c r="D4" t="n">
-        <v>21.5957375497628</v>
+        <v>21.59573754976277</v>
       </c>
       <c r="E4" t="n">
-        <v>21.35626647450009</v>
+        <v>21.35626647450008</v>
       </c>
       <c r="F4" t="n">
-        <v>21.52942218170759</v>
+        <v>21.5294221817076</v>
       </c>
       <c r="G4" t="n">
-        <v>23.32014930289269</v>
+        <v>23.32014930289265</v>
       </c>
       <c r="H4" t="n">
-        <v>22.12745035085206</v>
+        <v>22.12745035085209</v>
       </c>
       <c r="I4" t="n">
-        <v>21.72673960066135</v>
+        <v>21.7267396006614</v>
       </c>
       <c r="J4" t="n">
-        <v>21.7989358973596</v>
+        <v>21.79893589735962</v>
       </c>
       <c r="K4" t="n">
-        <v>22.14090314322395</v>
+        <v>22.14090314322394</v>
       </c>
       <c r="L4" t="n">
-        <v>22.17468337960934</v>
+        <v>22.17468337960935</v>
       </c>
       <c r="M4" t="n">
-        <v>24.7650833629852</v>
+        <v>24.76508336298519</v>
       </c>
       <c r="N4" t="n">
-        <v>22.00530298732441</v>
+        <v>22.0053029873244</v>
       </c>
       <c r="O4" t="n">
-        <v>21.97150281820115</v>
+        <v>21.97150281820114</v>
       </c>
       <c r="P4" t="n">
-        <v>22.6463983387455</v>
+        <v>22.64639833874548</v>
       </c>
       <c r="Q4" t="n">
         <v>22.11262121729744</v>
@@ -4233,19 +4233,19 @@
         <v>21.63087893560472</v>
       </c>
       <c r="S4" t="n">
-        <v>22.25152725120147</v>
+        <v>22.25152725120146</v>
       </c>
       <c r="T4" t="n">
         <v>21.62412485212239</v>
       </c>
       <c r="U4" t="n">
-        <v>22.18861877866649</v>
+        <v>22.18861877866647</v>
       </c>
       <c r="V4" t="n">
-        <v>15.74028178347838</v>
+        <v>15.74028178347833</v>
       </c>
       <c r="W4" t="n">
-        <v>23.2198955918728</v>
+        <v>23.21989559187276</v>
       </c>
       <c r="X4" t="n">
         <v>22.24098612087563</v>
@@ -4254,10 +4254,10 @@
         <v>21.97359126000627</v>
       </c>
       <c r="Z4" t="n">
-        <v>22.37998400338744</v>
+        <v>22.37998400338743</v>
       </c>
       <c r="AA4" t="n">
-        <v>21.94359248700501</v>
+        <v>21.943592487005</v>
       </c>
       <c r="AB4" t="n">
         <v>24.01397090221897</v>
@@ -4270,85 +4270,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>21.52890023352325</v>
+        <v>21.52890023352327</v>
       </c>
       <c r="C5" t="n">
-        <v>21.97518827442187</v>
+        <v>21.97518827442186</v>
       </c>
       <c r="D5" t="n">
-        <v>21.95772583734167</v>
+        <v>21.95772583734163</v>
       </c>
       <c r="E5" t="n">
         <v>21.69542162488696</v>
       </c>
       <c r="F5" t="n">
-        <v>21.58384183993773</v>
+        <v>21.58384183993772</v>
       </c>
       <c r="G5" t="n">
-        <v>22.04664561983494</v>
+        <v>22.04664561983497</v>
       </c>
       <c r="H5" t="n">
-        <v>21.95772583734167</v>
+        <v>21.95772583734163</v>
       </c>
       <c r="I5" t="n">
-        <v>21.95772583734167</v>
+        <v>21.95772583734163</v>
       </c>
       <c r="J5" t="n">
         <v>21.05266327331886</v>
       </c>
       <c r="K5" t="n">
-        <v>21.95772583734167</v>
+        <v>21.95772583734163</v>
       </c>
       <c r="L5" t="n">
-        <v>21.95772583734167</v>
+        <v>21.95772583734163</v>
       </c>
       <c r="M5" t="n">
         <v>21.97053244003807</v>
       </c>
       <c r="N5" t="n">
-        <v>21.62531425343053</v>
+        <v>21.62531425343052</v>
       </c>
       <c r="O5" t="n">
-        <v>21.71666384298926</v>
+        <v>21.71666384298929</v>
       </c>
       <c r="P5" t="n">
-        <v>21.69427185127084</v>
+        <v>21.69427185127086</v>
       </c>
       <c r="Q5" t="n">
-        <v>21.44462621489698</v>
+        <v>21.444626214897</v>
       </c>
       <c r="R5" t="n">
-        <v>21.95772583734167</v>
+        <v>21.95772583734163</v>
       </c>
       <c r="S5" t="n">
-        <v>21.95772583734167</v>
+        <v>21.95772583734163</v>
       </c>
       <c r="T5" t="n">
-        <v>21.95772583734167</v>
+        <v>21.95772583734163</v>
       </c>
       <c r="U5" t="n">
-        <v>21.74836097826829</v>
+        <v>21.74836097826826</v>
       </c>
       <c r="V5" t="n">
-        <v>15.86157354725143</v>
+        <v>15.86157354725142</v>
       </c>
       <c r="W5" t="n">
-        <v>21.95781011389485</v>
+        <v>21.95781011389484</v>
       </c>
       <c r="X5" t="n">
-        <v>21.48392893359771</v>
+        <v>21.48392893359767</v>
       </c>
       <c r="Y5" t="n">
-        <v>22.38399335427769</v>
+        <v>22.3839933542777</v>
       </c>
       <c r="Z5" t="n">
-        <v>21.52093457776994</v>
+        <v>21.52093457776996</v>
       </c>
       <c r="AA5" t="n">
-        <v>21.95772583734167</v>
+        <v>21.95772583734163</v>
       </c>
       <c r="AB5" t="n">
-        <v>22.40666912289621</v>
+        <v>22.40666912289622</v>
       </c>
     </row>
     <row r="6">
@@ -4358,85 +4358,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>10.43373809754485</v>
+        <v>10.43373809754483</v>
       </c>
       <c r="C6" t="n">
-        <v>9.551886672368941</v>
+        <v>9.551886672368942</v>
       </c>
       <c r="D6" t="n">
-        <v>9.928037215516595</v>
+        <v>9.928037215516579</v>
       </c>
       <c r="E6" t="n">
-        <v>9.688566140253887</v>
+        <v>9.688566140253879</v>
       </c>
       <c r="F6" t="n">
-        <v>9.861721847461384</v>
+        <v>9.861721847461386</v>
       </c>
       <c r="G6" t="n">
-        <v>11.61494806297912</v>
+        <v>11.61494806297908</v>
       </c>
       <c r="H6" t="n">
-        <v>10.45975001660584</v>
+        <v>10.45975001660588</v>
       </c>
       <c r="I6" t="n">
-        <v>10.05903926641514</v>
+        <v>10.05903926641519</v>
       </c>
       <c r="J6" t="n">
-        <v>10.9858359476068</v>
+        <v>10.98583594760683</v>
       </c>
       <c r="K6" t="n">
-        <v>10.47320280897773</v>
+        <v>10.47320280897774</v>
       </c>
       <c r="L6" t="n">
-        <v>10.50698304536316</v>
+        <v>10.50698304536314</v>
       </c>
       <c r="M6" t="n">
         <v>13.097383028739</v>
       </c>
       <c r="N6" t="n">
-        <v>10.33760265307821</v>
+        <v>10.33760265307819</v>
       </c>
       <c r="O6" t="n">
-        <v>10.26630157828757</v>
+        <v>10.26630157828756</v>
       </c>
       <c r="P6" t="n">
-        <v>10.94119709883192</v>
+        <v>10.9411970988319</v>
       </c>
       <c r="Q6" t="n">
-        <v>10.44492088305125</v>
+        <v>10.44492088305124</v>
       </c>
       <c r="R6" t="n">
-        <v>9.963178601358521</v>
+        <v>9.963178601358514</v>
       </c>
       <c r="S6" t="n">
-        <v>10.58382691695527</v>
+        <v>10.58382691695526</v>
       </c>
       <c r="T6" t="n">
-        <v>9.956424517876178</v>
+        <v>9.956424517876179</v>
       </c>
       <c r="U6" t="n">
-        <v>10.48341753875291</v>
+        <v>10.48341753875289</v>
       </c>
       <c r="V6" t="n">
-        <v>9.979795507636366</v>
+        <v>9.979795507636386</v>
       </c>
       <c r="W6" t="n">
-        <v>11.51469435195922</v>
+        <v>11.51469435195919</v>
       </c>
       <c r="X6" t="n">
-        <v>10.53578488096206</v>
+        <v>10.53578488096205</v>
       </c>
       <c r="Y6" t="n">
-        <v>10.30589092576008</v>
+        <v>10.30589092576007</v>
       </c>
       <c r="Z6" t="n">
-        <v>10.71228366914125</v>
+        <v>10.71228366914123</v>
       </c>
       <c r="AA6" t="n">
-        <v>10.27589215275881</v>
+        <v>10.27589215275879</v>
       </c>
       <c r="AB6" t="n">
-        <v>12.34627056797279</v>
+        <v>12.34627056797278</v>
       </c>
     </row>
     <row r="7">
@@ -4446,85 +4446,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>9.861199899277043</v>
+        <v>9.861199899277066</v>
       </c>
       <c r="C7" t="n">
-        <v>10.30748794017566</v>
+        <v>10.30748794017567</v>
       </c>
       <c r="D7" t="n">
-        <v>10.29002550309545</v>
+        <v>10.29002550309542</v>
       </c>
       <c r="E7" t="n">
         <v>10.02772129064075</v>
       </c>
       <c r="F7" t="n">
-        <v>9.91614150569152</v>
+        <v>9.916141505691533</v>
       </c>
       <c r="G7" t="n">
-        <v>10.34144437992136</v>
+        <v>10.34144437992138</v>
       </c>
       <c r="H7" t="n">
-        <v>10.29002550309545</v>
+        <v>10.29002550309542</v>
       </c>
       <c r="I7" t="n">
-        <v>10.29002550309545</v>
+        <v>10.29002550309542</v>
       </c>
       <c r="J7" t="n">
-        <v>10.23956332356608</v>
+        <v>10.23956332356609</v>
       </c>
       <c r="K7" t="n">
-        <v>10.29002550309545</v>
+        <v>10.29002550309542</v>
       </c>
       <c r="L7" t="n">
-        <v>10.29002550309545</v>
+        <v>10.29002550309542</v>
       </c>
       <c r="M7" t="n">
-        <v>10.30283210579187</v>
+        <v>10.30283210579186</v>
       </c>
       <c r="N7" t="n">
-        <v>9.957613919184331</v>
+        <v>9.957613919184316</v>
       </c>
       <c r="O7" t="n">
-        <v>10.01146260307568</v>
+        <v>10.01146260307571</v>
       </c>
       <c r="P7" t="n">
-        <v>9.989070611357263</v>
+        <v>9.989070611357278</v>
       </c>
       <c r="Q7" t="n">
-        <v>9.776925880650776</v>
+        <v>9.776925880650786</v>
       </c>
       <c r="R7" t="n">
-        <v>10.29002550309545</v>
+        <v>10.29002550309542</v>
       </c>
       <c r="S7" t="n">
-        <v>10.29002550309545</v>
+        <v>10.29002550309542</v>
       </c>
       <c r="T7" t="n">
-        <v>10.29002550309545</v>
+        <v>10.29002550309542</v>
       </c>
       <c r="U7" t="n">
-        <v>10.04315973835471</v>
+        <v>10.04315973835466</v>
       </c>
       <c r="V7" t="n">
-        <v>10.10108727140943</v>
+        <v>10.10108727140941</v>
       </c>
       <c r="W7" t="n">
-        <v>10.25260887398126</v>
+        <v>10.25260887398125</v>
       </c>
       <c r="X7" t="n">
-        <v>9.778727693684136</v>
+        <v>9.778727693684084</v>
       </c>
       <c r="Y7" t="n">
-        <v>10.71629302003147</v>
+        <v>10.7162930200315</v>
       </c>
       <c r="Z7" t="n">
-        <v>9.853234243523737</v>
+        <v>9.853234243523733</v>
       </c>
       <c r="AA7" t="n">
-        <v>10.29002550309545</v>
+        <v>10.29002550309542</v>
       </c>
       <c r="AB7" t="n">
-        <v>10.73896878864999</v>
+        <v>10.73896878865001</v>
       </c>
     </row>
   </sheetData>
@@ -4690,85 +4690,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>12.3239044234161</v>
+        <v>12.32390442341601</v>
       </c>
       <c r="C2" t="n">
-        <v>10.38637371270205</v>
+        <v>10.3863737127021</v>
       </c>
       <c r="D2" t="n">
-        <v>10.28252860012754</v>
+        <v>10.28252860012745</v>
       </c>
       <c r="E2" t="n">
-        <v>9.902525506716355</v>
+        <v>9.902525506716353</v>
       </c>
       <c r="F2" t="n">
-        <v>10.86410425708372</v>
+        <v>10.86410425708371</v>
       </c>
       <c r="G2" t="n">
-        <v>11.63884917711149</v>
+        <v>11.63884917711125</v>
       </c>
       <c r="H2" t="n">
-        <v>12.03543187614167</v>
+        <v>12.03543187614157</v>
       </c>
       <c r="I2" t="n">
-        <v>11.52683369635122</v>
+        <v>11.52683369635113</v>
       </c>
       <c r="J2" t="n">
-        <v>11.65873542243286</v>
+        <v>11.6587354224328</v>
       </c>
       <c r="K2" t="n">
-        <v>11.46108947348288</v>
+        <v>11.46108947348278</v>
       </c>
       <c r="L2" t="n">
-        <v>11.00971589681025</v>
+        <v>11.00971589681014</v>
       </c>
       <c r="M2" t="n">
-        <v>10.86777292280826</v>
+        <v>10.86777292280824</v>
       </c>
       <c r="N2" t="n">
-        <v>11.79901782256543</v>
+        <v>11.79901782256534</v>
       </c>
       <c r="O2" t="n">
-        <v>12.89445587583972</v>
+        <v>12.89445587583961</v>
       </c>
       <c r="P2" t="n">
-        <v>11.73398709662879</v>
+        <v>11.73398709662868</v>
       </c>
       <c r="Q2" t="n">
-        <v>11.89586439017402</v>
+        <v>11.89586439017391</v>
       </c>
       <c r="R2" t="n">
-        <v>11.25429229695376</v>
+        <v>11.25429229695366</v>
       </c>
       <c r="S2" t="n">
-        <v>11.57158398072004</v>
+        <v>11.57158398071992</v>
       </c>
       <c r="T2" t="n">
-        <v>10.45406041344772</v>
+        <v>10.45406041344778</v>
       </c>
       <c r="U2" t="n">
-        <v>11.39145780260212</v>
+        <v>11.39145780260201</v>
       </c>
       <c r="V2" t="n">
-        <v>11.83516086935739</v>
+        <v>11.8351608693572</v>
       </c>
       <c r="W2" t="n">
-        <v>13.51251500758888</v>
+        <v>13.51251500758878</v>
       </c>
       <c r="X2" t="n">
-        <v>15.69067577689731</v>
+        <v>15.69067577689722</v>
       </c>
       <c r="Y2" t="n">
-        <v>13.25918284760189</v>
+        <v>13.25918284760179</v>
       </c>
       <c r="Z2" t="n">
-        <v>12.02844246985831</v>
+        <v>12.0284424698582</v>
       </c>
       <c r="AA2" t="n">
-        <v>11.99707054342097</v>
+        <v>11.99707054342086</v>
       </c>
       <c r="AB2" t="n">
-        <v>10.76311307679538</v>
+        <v>10.76311307679537</v>
       </c>
     </row>
     <row r="3">
@@ -4778,85 +4778,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>10.92782321701091</v>
+        <v>10.92782321701089</v>
       </c>
       <c r="C3" t="n">
-        <v>12.10677902850157</v>
+        <v>12.10677902850134</v>
       </c>
       <c r="D3" t="n">
-        <v>12.08314819303844</v>
+        <v>12.08314819303823</v>
       </c>
       <c r="E3" t="n">
-        <v>11.44033721005987</v>
+        <v>11.44033721005985</v>
       </c>
       <c r="F3" t="n">
-        <v>11.10252572942475</v>
+        <v>11.10252572942473</v>
       </c>
       <c r="G3" t="n">
-        <v>12.32271235306746</v>
+        <v>12.32271235306744</v>
       </c>
       <c r="H3" t="n">
-        <v>12.08314819303844</v>
+        <v>12.08314819303823</v>
       </c>
       <c r="I3" t="n">
-        <v>12.08314819303844</v>
+        <v>12.08314819303823</v>
       </c>
       <c r="J3" t="n">
-        <v>12.07149334053144</v>
+        <v>12.07149334053133</v>
       </c>
       <c r="K3" t="n">
-        <v>12.08314819303844</v>
+        <v>12.08314819303823</v>
       </c>
       <c r="L3" t="n">
-        <v>12.08314819303844</v>
+        <v>12.08314819303823</v>
       </c>
       <c r="M3" t="n">
-        <v>12.07754459303545</v>
+        <v>12.07754459303543</v>
       </c>
       <c r="N3" t="n">
-        <v>11.18757805498513</v>
+        <v>11.18757805498511</v>
       </c>
       <c r="O3" t="n">
-        <v>11.43368850508203</v>
+        <v>11.43368850508187</v>
       </c>
       <c r="P3" t="n">
-        <v>11.37336088689509</v>
+        <v>11.37336088689503</v>
       </c>
       <c r="Q3" t="n">
-        <v>10.70077549018846</v>
+        <v>10.70077549018852</v>
       </c>
       <c r="R3" t="n">
-        <v>12.08314819303844</v>
+        <v>12.08314819303823</v>
       </c>
       <c r="S3" t="n">
-        <v>12.08314819303844</v>
+        <v>12.08314819303823</v>
       </c>
       <c r="T3" t="n">
-        <v>12.08314819303844</v>
+        <v>12.08314819303823</v>
       </c>
       <c r="U3" t="n">
-        <v>11.51916359992011</v>
+        <v>11.51916359992006</v>
       </c>
       <c r="V3" t="n">
-        <v>11.73991401273396</v>
+        <v>11.73991401273379</v>
       </c>
       <c r="W3" t="n">
-        <v>12.08337524760276</v>
+        <v>12.08337524760258</v>
       </c>
       <c r="X3" t="n">
-        <v>10.80666331997007</v>
+        <v>10.80666331996996</v>
       </c>
       <c r="Y3" t="n">
-        <v>13.23171458304741</v>
+        <v>13.23171458304729</v>
       </c>
       <c r="Z3" t="n">
         <v>10.90636246242747</v>
       </c>
       <c r="AA3" t="n">
-        <v>12.08314819303844</v>
+        <v>12.08314819303823</v>
       </c>
       <c r="AB3" t="n">
-        <v>13.27349702530823</v>
+        <v>13.2734970253082</v>
       </c>
     </row>
     <row r="4">
@@ -4866,82 +4866,82 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>21.74458646318804</v>
+        <v>21.74458646318796</v>
       </c>
       <c r="C4" t="n">
-        <v>21.05339694419116</v>
+        <v>21.05339694419083</v>
       </c>
       <c r="D4" t="n">
-        <v>21.00052894664452</v>
+        <v>21.00052894664442</v>
       </c>
       <c r="E4" t="n">
-        <v>20.84446022369234</v>
+        <v>20.84446022369233</v>
       </c>
       <c r="F4" t="n">
-        <v>21.20914864420019</v>
+        <v>21.20914864420018</v>
       </c>
       <c r="G4" t="n">
-        <v>21.49489187023481</v>
+        <v>21.49489187023471</v>
       </c>
       <c r="H4" t="n">
-        <v>21.63944160712218</v>
+        <v>21.63944160712209</v>
       </c>
       <c r="I4" t="n">
-        <v>21.45406354284992</v>
+        <v>21.45406354284983</v>
       </c>
       <c r="J4" t="n">
-        <v>20.6394225097468</v>
+        <v>20.63942250974679</v>
       </c>
       <c r="K4" t="n">
-        <v>21.43010054562204</v>
+        <v>21.43010054562196</v>
       </c>
       <c r="L4" t="n">
-        <v>21.26558017722101</v>
+        <v>21.26558017722092</v>
       </c>
       <c r="M4" t="n">
-        <v>21.21028247637316</v>
+        <v>21.21028247637314</v>
       </c>
       <c r="N4" t="n">
-        <v>21.55327146070763</v>
+        <v>21.55327146070753</v>
       </c>
       <c r="O4" t="n">
-        <v>21.95254576784304</v>
+        <v>21.95254576784294</v>
       </c>
       <c r="P4" t="n">
-        <v>21.52956852473305</v>
+        <v>21.52956852473297</v>
       </c>
       <c r="Q4" t="n">
-        <v>21.58857089737114</v>
+        <v>21.58857089737123</v>
       </c>
       <c r="R4" t="n">
-        <v>21.35472540311224</v>
+        <v>21.35472540311214</v>
       </c>
       <c r="S4" t="n">
-        <v>21.47037449601797</v>
+        <v>21.47037449601789</v>
       </c>
       <c r="T4" t="n">
-        <v>21.06305027837148</v>
+        <v>21.06305027837146</v>
       </c>
       <c r="U4" t="n">
-        <v>21.40472061924237</v>
+        <v>21.40472061924227</v>
       </c>
       <c r="V4" t="n">
-        <v>15.84263328297077</v>
+        <v>15.84263328297065</v>
       </c>
       <c r="W4" t="n">
-        <v>22.17782106374886</v>
+        <v>22.17782106374877</v>
       </c>
       <c r="X4" t="n">
-        <v>22.97173508690669</v>
+        <v>22.9717350869066</v>
       </c>
       <c r="Y4" t="n">
-        <v>22.08548446621001</v>
+        <v>22.08548446620992</v>
       </c>
       <c r="Z4" t="n">
-        <v>21.63689405060565</v>
+        <v>21.63689405060556</v>
       </c>
       <c r="AA4" t="n">
-        <v>21.62545935180699</v>
+        <v>21.6254593518069</v>
       </c>
       <c r="AB4" t="n">
         <v>21.16522011703918</v>
@@ -4954,85 +4954,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>21.23573125706656</v>
+        <v>21.23573125706623</v>
       </c>
       <c r="C5" t="n">
-        <v>21.6804644797809</v>
+        <v>21.68046447978045</v>
       </c>
       <c r="D5" t="n">
-        <v>21.65683364431775</v>
+        <v>21.65683364431761</v>
       </c>
       <c r="E5" t="n">
         <v>21.40497453166432</v>
       </c>
       <c r="F5" t="n">
-        <v>21.29605047118221</v>
+        <v>21.2960504711822</v>
       </c>
       <c r="G5" t="n">
-        <v>21.74415196754394</v>
+        <v>21.74415196754381</v>
       </c>
       <c r="H5" t="n">
-        <v>21.65683364431775</v>
+        <v>21.65683364431761</v>
       </c>
       <c r="I5" t="n">
-        <v>21.65683364431775</v>
+        <v>21.65683364431761</v>
       </c>
       <c r="J5" t="n">
-        <v>20.78986792404556</v>
+        <v>20.78986792404551</v>
       </c>
       <c r="K5" t="n">
-        <v>21.65683364431775</v>
+        <v>21.65683364431761</v>
       </c>
       <c r="L5" t="n">
-        <v>21.65683364431775</v>
+        <v>21.65683364431761</v>
       </c>
       <c r="M5" t="n">
         <v>21.65123004431479</v>
       </c>
       <c r="N5" t="n">
-        <v>21.33040884531284</v>
+        <v>21.33040884531283</v>
       </c>
       <c r="O5" t="n">
-        <v>21.42011321439832</v>
+        <v>21.42011321439833</v>
       </c>
       <c r="P5" t="n">
-        <v>21.39812450597186</v>
+        <v>21.39812450597184</v>
       </c>
       <c r="Q5" t="n">
-        <v>21.15297502676878</v>
+        <v>21.15297502676872</v>
       </c>
       <c r="R5" t="n">
-        <v>21.65683364431775</v>
+        <v>21.65683364431761</v>
       </c>
       <c r="S5" t="n">
-        <v>21.65683364431775</v>
+        <v>21.65683364431761</v>
       </c>
       <c r="T5" t="n">
-        <v>21.65683364431775</v>
+        <v>21.65683364431761</v>
       </c>
       <c r="U5" t="n">
-        <v>21.45126788276758</v>
+        <v>21.45126788276756</v>
       </c>
       <c r="V5" t="n">
-        <v>15.80791692217652</v>
+        <v>15.80791692217642</v>
       </c>
       <c r="W5" t="n">
-        <v>21.65691640304025</v>
+        <v>21.65691640304016</v>
       </c>
       <c r="X5" t="n">
-        <v>21.19156989732651</v>
+        <v>21.19156989732634</v>
       </c>
       <c r="Y5" t="n">
-        <v>22.07547260632852</v>
+        <v>22.07547260632837</v>
       </c>
       <c r="Z5" t="n">
-        <v>21.22790906402579</v>
+        <v>21.22790906402576</v>
       </c>
       <c r="AA5" t="n">
-        <v>21.65683364431775</v>
+        <v>21.65683364431761</v>
       </c>
       <c r="AB5" t="n">
-        <v>22.08022558785548</v>
+        <v>22.08022558785546</v>
       </c>
     </row>
     <row r="6">
@@ -5042,85 +5042,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>10.31809554061663</v>
+        <v>10.31809554061656</v>
       </c>
       <c r="C6" t="n">
-        <v>9.626906021619758</v>
+        <v>9.626906021619641</v>
       </c>
       <c r="D6" t="n">
-        <v>9.574038024073113</v>
+        <v>9.574038024073042</v>
       </c>
       <c r="E6" t="n">
-        <v>9.417969301120957</v>
+        <v>9.417969301120946</v>
       </c>
       <c r="F6" t="n">
-        <v>9.782657721628803</v>
+        <v>9.782657721628787</v>
       </c>
       <c r="G6" t="n">
-        <v>10.03143464485171</v>
+        <v>10.03143464485158</v>
       </c>
       <c r="H6" t="n">
-        <v>10.21295068455077</v>
+        <v>10.2129506845507</v>
       </c>
       <c r="I6" t="n">
-        <v>10.02757262027852</v>
+        <v>10.02757262027845</v>
       </c>
       <c r="J6" t="n">
-        <v>10.03262839708451</v>
+        <v>10.03262839708442</v>
       </c>
       <c r="K6" t="n">
-        <v>10.00360962305064</v>
+        <v>10.00360962305057</v>
       </c>
       <c r="L6" t="n">
-        <v>9.839089254649608</v>
+        <v>9.839089254649538</v>
       </c>
       <c r="M6" t="n">
-        <v>9.783791553801773</v>
+        <v>9.783791553801768</v>
       </c>
       <c r="N6" t="n">
-        <v>10.12678053813621</v>
+        <v>10.12678053813614</v>
       </c>
       <c r="O6" t="n">
-        <v>10.48908854245989</v>
+        <v>10.4890885424598</v>
       </c>
       <c r="P6" t="n">
-        <v>10.0661112993499</v>
+        <v>10.06611129934982</v>
       </c>
       <c r="Q6" t="n">
-        <v>10.16207997479973</v>
+        <v>10.16207997479984</v>
       </c>
       <c r="R6" t="n">
-        <v>9.928234480540819</v>
+        <v>9.928234480540752</v>
       </c>
       <c r="S6" t="n">
-        <v>10.04388357344657</v>
+        <v>10.04388357344649</v>
       </c>
       <c r="T6" t="n">
-        <v>9.636559355800067</v>
+        <v>9.636559355800076</v>
       </c>
       <c r="U6" t="n">
-        <v>9.941263393859213</v>
+        <v>9.94126339385914</v>
       </c>
       <c r="V6" t="n">
-        <v>10.08755264731353</v>
+        <v>10.08755264731352</v>
       </c>
       <c r="W6" t="n">
-        <v>10.7143638383657</v>
+        <v>10.71436383836563</v>
       </c>
       <c r="X6" t="n">
-        <v>11.50827786152355</v>
+        <v>11.50827786152347</v>
       </c>
       <c r="Y6" t="n">
-        <v>10.65899354363861</v>
+        <v>10.65899354363854</v>
       </c>
       <c r="Z6" t="n">
-        <v>10.21040312803424</v>
+        <v>10.21040312803416</v>
       </c>
       <c r="AA6" t="n">
-        <v>10.19896842923559</v>
+        <v>10.19896842923552</v>
       </c>
       <c r="AB6" t="n">
-        <v>9.738729194467773</v>
+        <v>9.738729194467766</v>
       </c>
     </row>
     <row r="7">
@@ -5130,85 +5130,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>9.809240334495142</v>
+        <v>9.809240334494833</v>
       </c>
       <c r="C7" t="n">
-        <v>10.25397355720951</v>
+        <v>10.25397355720919</v>
       </c>
       <c r="D7" t="n">
-        <v>10.23034272174636</v>
+        <v>10.23034272174623</v>
       </c>
       <c r="E7" t="n">
-        <v>9.978483609092947</v>
+        <v>9.978483609092939</v>
       </c>
       <c r="F7" t="n">
-        <v>9.869559548610827</v>
+        <v>9.869559548610804</v>
       </c>
       <c r="G7" t="n">
-        <v>10.28069474216081</v>
+        <v>10.28069474216067</v>
       </c>
       <c r="H7" t="n">
-        <v>10.23034272174636</v>
+        <v>10.23034272174623</v>
       </c>
       <c r="I7" t="n">
-        <v>10.23034272174636</v>
+        <v>10.23034272174623</v>
       </c>
       <c r="J7" t="n">
-        <v>10.18307381138326</v>
+        <v>10.18307381138312</v>
       </c>
       <c r="K7" t="n">
-        <v>10.23034272174636</v>
+        <v>10.23034272174623</v>
       </c>
       <c r="L7" t="n">
-        <v>10.23034272174636</v>
+        <v>10.23034272174623</v>
       </c>
       <c r="M7" t="n">
         <v>10.2247391217434</v>
       </c>
       <c r="N7" t="n">
-        <v>9.903917922741455</v>
+        <v>9.903917922741435</v>
       </c>
       <c r="O7" t="n">
-        <v>9.956655989015209</v>
+        <v>9.9566559890152</v>
       </c>
       <c r="P7" t="n">
-        <v>9.934667280588716</v>
+        <v>9.934667280588698</v>
       </c>
       <c r="Q7" t="n">
-        <v>9.726484104197349</v>
+        <v>9.726484104197331</v>
       </c>
       <c r="R7" t="n">
-        <v>10.23034272174636</v>
+        <v>10.23034272174623</v>
       </c>
       <c r="S7" t="n">
-        <v>10.23034272174636</v>
+        <v>10.23034272174623</v>
       </c>
       <c r="T7" t="n">
-        <v>10.23034272174636</v>
+        <v>10.23034272174623</v>
       </c>
       <c r="U7" t="n">
-        <v>9.987810657384435</v>
+        <v>9.98781065738442</v>
       </c>
       <c r="V7" t="n">
-        <v>10.05283628651939</v>
+        <v>10.05283628651929</v>
       </c>
       <c r="W7" t="n">
-        <v>10.19345917765712</v>
+        <v>10.19345917765703</v>
       </c>
       <c r="X7" t="n">
-        <v>9.728112671943347</v>
+        <v>9.728112671943196</v>
       </c>
       <c r="Y7" t="n">
-        <v>10.64898168375714</v>
+        <v>10.64898168375699</v>
       </c>
       <c r="Z7" t="n">
-        <v>9.801418141454411</v>
+        <v>9.801418141454356</v>
       </c>
       <c r="AA7" t="n">
-        <v>10.23034272174636</v>
+        <v>10.23034272174623</v>
       </c>
       <c r="AB7" t="n">
-        <v>10.65373466528408</v>
+        <v>10.65373466528407</v>
       </c>
     </row>
   </sheetData>
@@ -5374,85 +5374,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>11.55917002562306</v>
+        <v>11.559170025623</v>
       </c>
       <c r="C2" t="n">
-        <v>10.13363370928083</v>
+        <v>10.13363370928082</v>
       </c>
       <c r="D2" t="n">
-        <v>10.57100134201125</v>
+        <v>10.57100134201115</v>
       </c>
       <c r="E2" t="n">
         <v>10.04557996157069</v>
       </c>
       <c r="F2" t="n">
-        <v>10.72783433341111</v>
+        <v>10.7278343334111</v>
       </c>
       <c r="G2" t="n">
-        <v>11.22080986907969</v>
+        <v>11.22080986907925</v>
       </c>
       <c r="H2" t="n">
-        <v>11.57908096249251</v>
+        <v>11.57908096249257</v>
       </c>
       <c r="I2" t="n">
-        <v>12.11466834781857</v>
+        <v>12.11466834781852</v>
       </c>
       <c r="J2" t="n">
-        <v>11.30861044845186</v>
+        <v>11.30861044845193</v>
       </c>
       <c r="K2" t="n">
-        <v>11.25796940623573</v>
+        <v>11.25796940623563</v>
       </c>
       <c r="L2" t="n">
-        <v>10.81791406607373</v>
+        <v>10.81791406607368</v>
       </c>
       <c r="M2" t="n">
-        <v>10.92586093078706</v>
+        <v>10.92586093078709</v>
       </c>
       <c r="N2" t="n">
-        <v>11.05039500285294</v>
+        <v>11.05039500285288</v>
       </c>
       <c r="O2" t="n">
-        <v>12.48664064292181</v>
+        <v>12.48664064292176</v>
       </c>
       <c r="P2" t="n">
-        <v>11.75817311947196</v>
+        <v>11.75817311947198</v>
       </c>
       <c r="Q2" t="n">
-        <v>11.01638201191269</v>
+        <v>11.01638201191262</v>
       </c>
       <c r="R2" t="n">
-        <v>12.25156053798576</v>
+        <v>12.2515605379857</v>
       </c>
       <c r="S2" t="n">
-        <v>11.25128334956333</v>
+        <v>11.2512833495632</v>
       </c>
       <c r="T2" t="n">
-        <v>10.50297312257078</v>
+        <v>10.50297312257071</v>
       </c>
       <c r="U2" t="n">
-        <v>11.24001690871385</v>
+        <v>11.24001690871377</v>
       </c>
       <c r="V2" t="n">
         <v>11.60760318941379</v>
       </c>
       <c r="W2" t="n">
-        <v>13.03794786227196</v>
+        <v>13.03794786227191</v>
       </c>
       <c r="X2" t="n">
-        <v>16.72813099969407</v>
+        <v>16.72813099969413</v>
       </c>
       <c r="Y2" t="n">
-        <v>12.76037035058079</v>
+        <v>12.76037035058074</v>
       </c>
       <c r="Z2" t="n">
-        <v>10.97020156855171</v>
+        <v>10.9702015685516</v>
       </c>
       <c r="AA2" t="n">
-        <v>12.21787238984815</v>
+        <v>12.21787238984808</v>
       </c>
       <c r="AB2" t="n">
-        <v>10.88642174830141</v>
+        <v>10.88642174830119</v>
       </c>
     </row>
     <row r="3">
@@ -5465,82 +5465,82 @@
         <v>10.91242341177786</v>
       </c>
       <c r="C3" t="n">
-        <v>12.08945964912656</v>
+        <v>12.08945964912654</v>
       </c>
       <c r="D3" t="n">
-        <v>12.06385484443891</v>
+        <v>12.06385484443886</v>
       </c>
       <c r="E3" t="n">
-        <v>11.42666129021592</v>
+        <v>11.42666129021591</v>
       </c>
       <c r="F3" t="n">
         <v>11.08904077327992</v>
       </c>
       <c r="G3" t="n">
-        <v>12.30261165288695</v>
+        <v>12.30261165288693</v>
       </c>
       <c r="H3" t="n">
-        <v>12.06385484443891</v>
+        <v>12.06385484443886</v>
       </c>
       <c r="I3" t="n">
-        <v>12.06385484443891</v>
+        <v>12.06385484443886</v>
       </c>
       <c r="J3" t="n">
-        <v>12.05358291302436</v>
+        <v>12.0535829130244</v>
       </c>
       <c r="K3" t="n">
-        <v>12.06385484443891</v>
+        <v>12.06385484443886</v>
       </c>
       <c r="L3" t="n">
-        <v>12.06385484443891</v>
+        <v>12.06385484443886</v>
       </c>
       <c r="M3" t="n">
-        <v>12.06137177868552</v>
+        <v>12.06137177868553</v>
       </c>
       <c r="N3" t="n">
-        <v>11.17130285387077</v>
+        <v>11.17130285387069</v>
       </c>
       <c r="O3" t="n">
-        <v>11.41658389083376</v>
+        <v>11.41658389083354</v>
       </c>
       <c r="P3" t="n">
-        <v>11.35645958184712</v>
+        <v>11.3564595818471</v>
       </c>
       <c r="Q3" t="n">
-        <v>10.68614085509211</v>
+        <v>10.68614085509203</v>
       </c>
       <c r="R3" t="n">
-        <v>12.06385484443891</v>
+        <v>12.06385484443886</v>
       </c>
       <c r="S3" t="n">
-        <v>12.06385484443891</v>
+        <v>12.06385484443886</v>
       </c>
       <c r="T3" t="n">
-        <v>12.06385484443891</v>
+        <v>12.06385484443886</v>
       </c>
       <c r="U3" t="n">
-        <v>11.5017816923048</v>
+        <v>11.50178169230483</v>
       </c>
       <c r="V3" t="n">
-        <v>11.72468358276883</v>
+        <v>11.72468358276882</v>
       </c>
       <c r="W3" t="n">
-        <v>12.06408113381252</v>
+        <v>12.06408113381231</v>
       </c>
       <c r="X3" t="n">
         <v>10.7916718338888</v>
       </c>
       <c r="Y3" t="n">
-        <v>13.20856888381979</v>
+        <v>13.20856888381965</v>
       </c>
       <c r="Z3" t="n">
-        <v>10.89103498176114</v>
+        <v>10.89103498176117</v>
       </c>
       <c r="AA3" t="n">
-        <v>12.06385484443891</v>
+        <v>12.06385484443886</v>
       </c>
       <c r="AB3" t="n">
-        <v>13.25350093813582</v>
+        <v>13.25350093813594</v>
       </c>
     </row>
     <row r="4">
@@ -5550,85 +5550,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>21.41544880836819</v>
+        <v>21.41544880836814</v>
       </c>
       <c r="C4" t="n">
-        <v>20.91212971459982</v>
+        <v>20.9121297145998</v>
       </c>
       <c r="D4" t="n">
-        <v>21.05527292685422</v>
+        <v>21.05527292685415</v>
       </c>
       <c r="E4" t="n">
         <v>20.84845334677315</v>
       </c>
       <c r="F4" t="n">
-        <v>21.11068130091283</v>
+        <v>21.11068130091281</v>
       </c>
       <c r="G4" t="n">
-        <v>21.29212050453372</v>
+        <v>21.29212050453367</v>
       </c>
       <c r="H4" t="n">
-        <v>21.42270611105111</v>
+        <v>21.42270611105108</v>
       </c>
       <c r="I4" t="n">
-        <v>21.61792142381784</v>
+        <v>21.61792142381777</v>
       </c>
       <c r="J4" t="n">
-        <v>20.46567285673601</v>
+        <v>20.46567285673596</v>
       </c>
       <c r="K4" t="n">
-        <v>21.30566471947776</v>
+        <v>21.30566471947763</v>
       </c>
       <c r="L4" t="n">
-        <v>21.14526971537941</v>
+        <v>21.14526971537935</v>
       </c>
       <c r="M4" t="n">
-        <v>21.18303706254743</v>
+        <v>21.18303706254745</v>
       </c>
       <c r="N4" t="n">
-        <v>21.23000628690644</v>
+        <v>21.23000628690637</v>
       </c>
       <c r="O4" t="n">
-        <v>21.75350095746375</v>
+        <v>21.75350095746369</v>
       </c>
       <c r="P4" t="n">
-        <v>21.48798309926388</v>
+        <v>21.48798309926378</v>
       </c>
       <c r="Q4" t="n">
-        <v>21.21760895110942</v>
+        <v>21.21760895110936</v>
       </c>
       <c r="R4" t="n">
-        <v>21.66781701966452</v>
+        <v>21.66781701966446</v>
       </c>
       <c r="S4" t="n">
-        <v>21.3032277303323</v>
+        <v>21.3032277303322</v>
       </c>
       <c r="T4" t="n">
-        <v>21.03047743969584</v>
+        <v>21.03047743969577</v>
       </c>
       <c r="U4" t="n">
-        <v>21.2991212449399</v>
+        <v>21.29912124493975</v>
       </c>
       <c r="V4" t="n">
-        <v>15.73379792786046</v>
+        <v>15.7337979278605</v>
       </c>
       <c r="W4" t="n">
-        <v>21.95444596514066</v>
+        <v>21.95444596514059</v>
       </c>
       <c r="X4" t="n">
-        <v>23.29947438641293</v>
+        <v>23.29947438641279</v>
       </c>
       <c r="Y4" t="n">
-        <v>21.85327222160894</v>
+        <v>21.85327222160884</v>
       </c>
       <c r="Z4" t="n">
-        <v>21.2007767217825</v>
+        <v>21.20077672178242</v>
       </c>
       <c r="AA4" t="n">
-        <v>21.65553808525457</v>
+        <v>21.65553808525449</v>
       </c>
       <c r="AB4" t="n">
-        <v>21.16190184433695</v>
+        <v>21.16190184433652</v>
       </c>
     </row>
     <row r="5">
@@ -5638,85 +5638,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>21.17971726210381</v>
+        <v>21.17971726210379</v>
       </c>
       <c r="C5" t="n">
-        <v>21.62500530320587</v>
+        <v>21.62500530320585</v>
       </c>
       <c r="D5" t="n">
-        <v>21.59940049851819</v>
+        <v>21.59940049851822</v>
       </c>
       <c r="E5" t="n">
-        <v>21.35184127358859</v>
+        <v>21.35184127358858</v>
       </c>
       <c r="F5" t="n">
-        <v>21.24233680674486</v>
+        <v>21.24233680674483</v>
       </c>
       <c r="G5" t="n">
-        <v>21.68642455157352</v>
+        <v>21.68642455157354</v>
       </c>
       <c r="H5" t="n">
-        <v>21.59940049851819</v>
+        <v>21.59940049851822</v>
       </c>
       <c r="I5" t="n">
-        <v>21.59940049851819</v>
+        <v>21.59940049851822</v>
       </c>
       <c r="J5" t="n">
-        <v>20.73720657216436</v>
+        <v>20.7372065721643</v>
       </c>
       <c r="K5" t="n">
-        <v>21.59940049851819</v>
+        <v>21.59940049851822</v>
       </c>
       <c r="L5" t="n">
-        <v>21.59940049851819</v>
+        <v>21.59940049851822</v>
       </c>
       <c r="M5" t="n">
-        <v>21.59691743276484</v>
+        <v>21.59691743276487</v>
       </c>
       <c r="N5" t="n">
-        <v>21.27407577883066</v>
+        <v>21.27407577883064</v>
       </c>
       <c r="O5" t="n">
-        <v>21.36347783656829</v>
+        <v>21.36347783656833</v>
       </c>
       <c r="P5" t="n">
-        <v>21.34156323195818</v>
+        <v>21.34156323195803</v>
       </c>
       <c r="Q5" t="n">
-        <v>21.09723992733576</v>
+        <v>21.0972399273357</v>
       </c>
       <c r="R5" t="n">
-        <v>21.59940049851819</v>
+        <v>21.59940049851822</v>
       </c>
       <c r="S5" t="n">
-        <v>21.59940049851819</v>
+        <v>21.59940049851822</v>
       </c>
       <c r="T5" t="n">
-        <v>21.59940049851819</v>
+        <v>21.59940049851822</v>
       </c>
       <c r="U5" t="n">
-        <v>21.39453143476154</v>
+        <v>21.39453143476141</v>
       </c>
       <c r="V5" t="n">
-        <v>15.77647235641093</v>
+        <v>15.77647235641101</v>
       </c>
       <c r="W5" t="n">
-        <v>21.5994829783376</v>
+        <v>21.59948297833757</v>
       </c>
       <c r="X5" t="n">
-        <v>21.13570472989989</v>
+        <v>21.13570472989974</v>
       </c>
       <c r="Y5" t="n">
-        <v>22.01663532396167</v>
+        <v>22.01663532396158</v>
       </c>
       <c r="Z5" t="n">
-        <v>21.17192143051832</v>
+        <v>21.17192143051831</v>
       </c>
       <c r="AA5" t="n">
-        <v>21.59940049851819</v>
+        <v>21.59940049851822</v>
       </c>
       <c r="AB5" t="n">
-        <v>22.02467441338441</v>
+        <v>22.02467441338414</v>
       </c>
     </row>
     <row r="6">
@@ -5726,85 +5726,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>10.0334057279074</v>
+        <v>10.03340572790723</v>
       </c>
       <c r="C6" t="n">
-        <v>9.530086634138918</v>
+        <v>9.530086634138913</v>
       </c>
       <c r="D6" t="n">
-        <v>9.673229846393408</v>
+        <v>9.673229846393244</v>
       </c>
       <c r="E6" t="n">
-        <v>9.466410266312252</v>
+        <v>9.466410266312241</v>
       </c>
       <c r="F6" t="n">
-        <v>9.728638220451924</v>
+        <v>9.728638220451922</v>
       </c>
       <c r="G6" t="n">
-        <v>9.873171767850534</v>
+        <v>9.873171767850661</v>
       </c>
       <c r="H6" t="n">
-        <v>10.04066303059031</v>
+        <v>10.04066303059016</v>
       </c>
       <c r="I6" t="n">
-        <v>10.23587834335704</v>
+        <v>10.23587834335686</v>
       </c>
       <c r="J6" t="n">
-        <v>9.899995326639612</v>
+        <v>9.89999532663955</v>
       </c>
       <c r="K6" t="n">
-        <v>9.923621639016956</v>
+        <v>9.923621639016716</v>
       </c>
       <c r="L6" t="n">
-        <v>9.763226634918613</v>
+        <v>9.763226634918437</v>
       </c>
       <c r="M6" t="n">
-        <v>9.80099398208654</v>
+        <v>9.80099398208656</v>
       </c>
       <c r="N6" t="n">
-        <v>9.847963206445645</v>
+        <v>9.847963206445472</v>
       </c>
       <c r="O6" t="n">
-        <v>10.33455222078059</v>
+        <v>10.33455222078053</v>
       </c>
       <c r="P6" t="n">
-        <v>10.06903436258073</v>
+        <v>10.06903436258062</v>
       </c>
       <c r="Q6" t="n">
-        <v>9.83556587064861</v>
+        <v>9.835565870648455</v>
       </c>
       <c r="R6" t="n">
-        <v>10.28577393920372</v>
+        <v>10.28577393920355</v>
       </c>
       <c r="S6" t="n">
-        <v>9.921184649871503</v>
+        <v>9.921184649871289</v>
       </c>
       <c r="T6" t="n">
-        <v>9.64843435923504</v>
+        <v>9.648434359234884</v>
       </c>
       <c r="U6" t="n">
-        <v>9.88017250825675</v>
+        <v>9.880172508256647</v>
       </c>
       <c r="V6" t="n">
-        <v>10.00061082419394</v>
+        <v>10.00061082419393</v>
       </c>
       <c r="W6" t="n">
-        <v>10.53549722845751</v>
+        <v>10.53549722845744</v>
       </c>
       <c r="X6" t="n">
-        <v>11.88052564972979</v>
+        <v>11.88052564972971</v>
       </c>
       <c r="Y6" t="n">
-        <v>10.47122914114814</v>
+        <v>10.47122914114793</v>
       </c>
       <c r="Z6" t="n">
-        <v>9.818733641321632</v>
+        <v>9.818733641321506</v>
       </c>
       <c r="AA6" t="n">
-        <v>10.27349500479377</v>
+        <v>10.27349500479358</v>
       </c>
       <c r="AB6" t="n">
-        <v>9.77985876387606</v>
+        <v>9.779858763875822</v>
       </c>
     </row>
     <row r="7">
@@ -5814,85 +5814,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>9.797674181642911</v>
+        <v>9.797674181642883</v>
       </c>
       <c r="C7" t="n">
-        <v>10.24296222274498</v>
+        <v>10.24296222274496</v>
       </c>
       <c r="D7" t="n">
-        <v>10.21735741805731</v>
+        <v>10.21735741805728</v>
       </c>
       <c r="E7" t="n">
-        <v>9.969798193127691</v>
+        <v>9.969798193127678</v>
       </c>
       <c r="F7" t="n">
-        <v>9.860293726283951</v>
+        <v>9.860293726283937</v>
       </c>
       <c r="G7" t="n">
-        <v>10.26747581489037</v>
+        <v>10.26747581489039</v>
       </c>
       <c r="H7" t="n">
-        <v>10.21735741805731</v>
+        <v>10.21735741805728</v>
       </c>
       <c r="I7" t="n">
-        <v>10.21735741805731</v>
+        <v>10.21735741805728</v>
       </c>
       <c r="J7" t="n">
-        <v>10.17152904206794</v>
+        <v>10.17152904206791</v>
       </c>
       <c r="K7" t="n">
-        <v>10.21735741805731</v>
+        <v>10.21735741805728</v>
       </c>
       <c r="L7" t="n">
-        <v>10.21735741805731</v>
+        <v>10.21735741805728</v>
       </c>
       <c r="M7" t="n">
-        <v>10.21487435230394</v>
+        <v>10.21487435230397</v>
       </c>
       <c r="N7" t="n">
-        <v>9.892032698369912</v>
+        <v>9.892032698369748</v>
       </c>
       <c r="O7" t="n">
-        <v>9.944529099885141</v>
+        <v>9.944529099885175</v>
       </c>
       <c r="P7" t="n">
-        <v>9.922614495275027</v>
+        <v>9.922614495274885</v>
       </c>
       <c r="Q7" t="n">
-        <v>9.715196846874859</v>
+        <v>9.715196846874784</v>
       </c>
       <c r="R7" t="n">
-        <v>10.21735741805731</v>
+        <v>10.21735741805728</v>
       </c>
       <c r="S7" t="n">
-        <v>10.21735741805731</v>
+        <v>10.21735741805728</v>
       </c>
       <c r="T7" t="n">
-        <v>10.21735741805731</v>
+        <v>10.21735741805728</v>
       </c>
       <c r="U7" t="n">
-        <v>9.975582698078375</v>
+        <v>9.975582698078279</v>
       </c>
       <c r="V7" t="n">
-        <v>10.04328525274446</v>
+        <v>10.04328525274445</v>
       </c>
       <c r="W7" t="n">
         <v>10.18053424165443</v>
       </c>
       <c r="X7" t="n">
-        <v>9.71675599321674</v>
+        <v>9.716755993216587</v>
       </c>
       <c r="Y7" t="n">
-        <v>10.63459224350083</v>
+        <v>10.63459224350066</v>
       </c>
       <c r="Z7" t="n">
-        <v>9.789878350057332</v>
+        <v>9.789878350057402</v>
       </c>
       <c r="AA7" t="n">
-        <v>10.21735741805731</v>
+        <v>10.21735741805728</v>
       </c>
       <c r="AB7" t="n">
-        <v>10.64263133292351</v>
+        <v>10.64263133292325</v>
       </c>
     </row>
   </sheetData>
@@ -6058,85 +6058,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>13.67399666162813</v>
+        <v>13.67399666162854</v>
       </c>
       <c r="C2" t="n">
-        <v>10.62741910500175</v>
+        <v>10.62741910500202</v>
       </c>
       <c r="D2" t="n">
-        <v>13.08297688977391</v>
+        <v>13.08297688977439</v>
       </c>
       <c r="E2" t="n">
-        <v>11.0542815039519</v>
+        <v>11.05428150395233</v>
       </c>
       <c r="F2" t="n">
-        <v>12.71457330386204</v>
+        <v>12.71457330386206</v>
       </c>
       <c r="G2" t="n">
-        <v>30.51211504951502</v>
+        <v>30.51211504951544</v>
       </c>
       <c r="H2" t="n">
-        <v>11.18628148911774</v>
+        <v>11.18628148911817</v>
       </c>
       <c r="I2" t="n">
-        <v>12.53700963360015</v>
+        <v>12.53700963360051</v>
       </c>
       <c r="J2" t="n">
-        <v>21.57294473410374</v>
+        <v>21.57294473410381</v>
       </c>
       <c r="K2" t="n">
-        <v>13.76813761981236</v>
+        <v>13.76813761981267</v>
       </c>
       <c r="L2" t="n">
-        <v>13.10698444764942</v>
+        <v>13.10698444764977</v>
       </c>
       <c r="M2" t="n">
-        <v>39.14617148029118</v>
+        <v>39.14617148029115</v>
       </c>
       <c r="N2" t="n">
-        <v>13.75598484818961</v>
+        <v>13.75598484819002</v>
       </c>
       <c r="O2" t="n">
-        <v>13.98812964865823</v>
+        <v>13.98812964865859</v>
       </c>
       <c r="P2" t="n">
-        <v>18.62355297564899</v>
+        <v>18.62355297564924</v>
       </c>
       <c r="Q2" t="n">
-        <v>13.6234751298319</v>
+        <v>13.62347512983229</v>
       </c>
       <c r="R2" t="n">
-        <v>11.67973391348701</v>
+        <v>11.67973391348669</v>
       </c>
       <c r="S2" t="n">
-        <v>15.38018428417962</v>
+        <v>15.38018428418002</v>
       </c>
       <c r="T2" t="n">
-        <v>12.06135519682925</v>
+        <v>12.06135519682968</v>
       </c>
       <c r="U2" t="n">
-        <v>16.00462410831313</v>
+        <v>16.00462410831355</v>
       </c>
       <c r="V2" t="n">
         <v>12.46853440844666</v>
       </c>
       <c r="W2" t="n">
-        <v>16.05815011969196</v>
+        <v>16.05815011969247</v>
       </c>
       <c r="X2" t="n">
-        <v>15.47409760728736</v>
+        <v>15.47409760728778</v>
       </c>
       <c r="Y2" t="n">
-        <v>16.98426806890734</v>
+        <v>16.98426806890775</v>
       </c>
       <c r="Z2" t="n">
-        <v>15.46864478649369</v>
+        <v>15.46864478649407</v>
       </c>
       <c r="AA2" t="n">
-        <v>13.94961247059103</v>
+        <v>13.94961247059142</v>
       </c>
       <c r="AB2" t="n">
-        <v>36.88792905745023</v>
+        <v>36.88792905745028</v>
       </c>
     </row>
     <row r="3">
@@ -6146,85 +6146,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>11.19616723642929</v>
+        <v>11.19616723643003</v>
       </c>
       <c r="C3" t="n">
-        <v>12.42412529711527</v>
+        <v>12.42412529711515</v>
       </c>
       <c r="D3" t="n">
-        <v>12.41909117533573</v>
+        <v>12.41909117533611</v>
       </c>
       <c r="E3" t="n">
-        <v>11.71614504527763</v>
+        <v>11.71614504527806</v>
       </c>
       <c r="F3" t="n">
         <v>11.3624924211786</v>
       </c>
       <c r="G3" t="n">
-        <v>12.67267242068251</v>
+        <v>12.67267242068261</v>
       </c>
       <c r="H3" t="n">
-        <v>12.41909117533573</v>
+        <v>12.41909117533611</v>
       </c>
       <c r="I3" t="n">
-        <v>12.41909117533573</v>
+        <v>12.41909117533611</v>
       </c>
       <c r="J3" t="n">
-        <v>12.39909213013366</v>
+        <v>12.39909213013371</v>
       </c>
       <c r="K3" t="n">
-        <v>12.41909117533573</v>
+        <v>12.41909117533611</v>
       </c>
       <c r="L3" t="n">
-        <v>12.41909117533573</v>
+        <v>12.41909117533611</v>
       </c>
       <c r="M3" t="n">
-        <v>12.46945126415427</v>
+        <v>12.46945126415426</v>
       </c>
       <c r="N3" t="n">
-        <v>11.47112053198525</v>
+        <v>11.47112053198563</v>
       </c>
       <c r="O3" t="n">
-        <v>11.73163109591118</v>
+        <v>11.7316310959115</v>
       </c>
       <c r="P3" t="n">
-        <v>11.66777366187063</v>
+        <v>11.66777366187114</v>
       </c>
       <c r="Q3" t="n">
-        <v>10.95583477053727</v>
+        <v>10.95583477053735</v>
       </c>
       <c r="R3" t="n">
-        <v>12.41909117533573</v>
+        <v>12.41909117533611</v>
       </c>
       <c r="S3" t="n">
-        <v>12.41909117533573</v>
+        <v>12.41909117533611</v>
       </c>
       <c r="T3" t="n">
-        <v>12.41909117533573</v>
+        <v>12.41909117533611</v>
       </c>
       <c r="U3" t="n">
-        <v>11.82189556797663</v>
+        <v>11.82189556797656</v>
       </c>
       <c r="V3" t="n">
-        <v>12.02983931282732</v>
+        <v>12.02983931282745</v>
       </c>
       <c r="W3" t="n">
-        <v>12.41933151500895</v>
+        <v>12.41933151500963</v>
       </c>
       <c r="X3" t="n">
-        <v>11.06791817957287</v>
+        <v>11.06791817957333</v>
       </c>
       <c r="Y3" t="n">
-        <v>13.63449868652815</v>
+        <v>13.63449868652831</v>
       </c>
       <c r="Z3" t="n">
-        <v>11.17345079640758</v>
+        <v>11.17345079640763</v>
       </c>
       <c r="AA3" t="n">
-        <v>12.41909117533573</v>
+        <v>12.41909117533611</v>
       </c>
       <c r="AB3" t="n">
-        <v>13.74547175750199</v>
+        <v>13.74547175750202</v>
       </c>
     </row>
     <row r="4">
@@ -6234,85 +6234,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>23.33880778214881</v>
+        <v>23.33880778215028</v>
       </c>
       <c r="C4" t="n">
-        <v>22.23156528098292</v>
+        <v>22.23156528098407</v>
       </c>
       <c r="D4" t="n">
-        <v>23.12338801541231</v>
+        <v>23.1233880154141</v>
       </c>
       <c r="E4" t="n">
-        <v>22.35104861767225</v>
+        <v>22.35104861767253</v>
       </c>
       <c r="F4" t="n">
-        <v>22.97373488832019</v>
+        <v>22.97373488831997</v>
       </c>
       <c r="G4" t="n">
-        <v>29.47610421136575</v>
+        <v>29.4761042113662</v>
       </c>
       <c r="H4" t="n">
-        <v>22.43206481399519</v>
+        <v>22.43206481399659</v>
       </c>
       <c r="I4" t="n">
-        <v>22.92438936160837</v>
+        <v>22.92438936161012</v>
       </c>
       <c r="J4" t="n">
-        <v>25.22120866336236</v>
+        <v>25.22120866336217</v>
       </c>
       <c r="K4" t="n">
-        <v>23.37312105594729</v>
+        <v>23.37312105594938</v>
       </c>
       <c r="L4" t="n">
-        <v>23.13213848834672</v>
+        <v>23.13213848834837</v>
       </c>
       <c r="M4" t="n">
-        <v>32.65512082197624</v>
+        <v>32.65512082197669</v>
       </c>
       <c r="N4" t="n">
-        <v>23.36869151339663</v>
+        <v>23.36869151339793</v>
       </c>
       <c r="O4" t="n">
-        <v>23.45330556718551</v>
+        <v>23.45330556718686</v>
       </c>
       <c r="P4" t="n">
-        <v>25.14286293798658</v>
+        <v>25.14286293798624</v>
       </c>
       <c r="Q4" t="n">
-        <v>23.32039327706449</v>
+        <v>23.32039327706432</v>
       </c>
       <c r="R4" t="n">
-        <v>22.61192242826689</v>
+        <v>22.61192242826823</v>
       </c>
       <c r="S4" t="n">
-        <v>23.96069313550269</v>
+        <v>23.96069313550353</v>
       </c>
       <c r="T4" t="n">
-        <v>22.75101890482178</v>
+        <v>22.75101890482328</v>
       </c>
       <c r="U4" t="n">
-        <v>24.18829411885564</v>
+        <v>24.18829411885757</v>
       </c>
       <c r="V4" t="n">
-        <v>16.29993138202249</v>
+        <v>16.29993138202241</v>
       </c>
       <c r="W4" t="n">
-        <v>24.20780372146971</v>
+        <v>24.20780372147135</v>
       </c>
       <c r="X4" t="n">
-        <v>23.99492343899064</v>
+        <v>23.9949234389906</v>
       </c>
       <c r="Y4" t="n">
-        <v>24.5453628389327</v>
+        <v>24.54536283893432</v>
       </c>
       <c r="Z4" t="n">
-        <v>23.99293594984004</v>
+        <v>23.99293594984158</v>
       </c>
       <c r="AA4" t="n">
-        <v>23.43926650807157</v>
+        <v>23.43926650807317</v>
       </c>
       <c r="AB4" t="n">
-        <v>31.83111185102509</v>
+        <v>31.83111185102475</v>
       </c>
     </row>
     <row r="5">
@@ -6322,85 +6322,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>22.43566805280638</v>
+        <v>22.43566805280788</v>
       </c>
       <c r="C5" t="n">
-        <v>22.88644359002013</v>
+        <v>22.88644359001996</v>
       </c>
       <c r="D5" t="n">
-        <v>22.88140946824072</v>
+        <v>22.88140946824066</v>
       </c>
       <c r="E5" t="n">
-        <v>22.59229010649128</v>
+        <v>22.59229010649201</v>
       </c>
       <c r="F5" t="n">
-        <v>22.4809172835167</v>
+        <v>22.48091728351705</v>
       </c>
       <c r="G5" t="n">
-        <v>22.97383685446814</v>
+        <v>22.97383685446832</v>
       </c>
       <c r="H5" t="n">
-        <v>22.88140946824072</v>
+        <v>22.88140946824066</v>
       </c>
       <c r="I5" t="n">
-        <v>22.88140946824072</v>
+        <v>22.88140946824066</v>
       </c>
       <c r="J5" t="n">
-        <v>21.87744711403073</v>
+        <v>21.87744711403209</v>
       </c>
       <c r="K5" t="n">
-        <v>22.88140946824072</v>
+        <v>22.88140946824066</v>
       </c>
       <c r="L5" t="n">
-        <v>22.88140946824072</v>
+        <v>22.88140946824066</v>
       </c>
       <c r="M5" t="n">
-        <v>22.93176955705867</v>
+        <v>22.93176955705882</v>
       </c>
       <c r="N5" t="n">
-        <v>22.53588530037151</v>
+        <v>22.5358853003728</v>
       </c>
       <c r="O5" t="n">
-        <v>22.63083834185386</v>
+        <v>22.63083834185393</v>
       </c>
       <c r="P5" t="n">
-        <v>22.60756305699871</v>
+        <v>22.60756305699811</v>
       </c>
       <c r="Q5" t="n">
-        <v>22.34806969111528</v>
+        <v>22.34806969111596</v>
       </c>
       <c r="R5" t="n">
-        <v>22.88140946824072</v>
+        <v>22.88140946824066</v>
       </c>
       <c r="S5" t="n">
-        <v>22.88140946824072</v>
+        <v>22.88140946824066</v>
       </c>
       <c r="T5" t="n">
-        <v>22.88140946824072</v>
+        <v>22.88140946824066</v>
       </c>
       <c r="U5" t="n">
-        <v>22.66373868198273</v>
+        <v>22.66373868198349</v>
       </c>
       <c r="V5" t="n">
-        <v>16.14003217108717</v>
+        <v>16.14003217108732</v>
       </c>
       <c r="W5" t="n">
-        <v>22.88149706922796</v>
+        <v>22.88149706922927</v>
       </c>
       <c r="X5" t="n">
-        <v>22.38892277756015</v>
+        <v>22.38892277756003</v>
       </c>
       <c r="Y5" t="n">
-        <v>23.32441123403468</v>
+        <v>23.32441123403436</v>
       </c>
       <c r="Z5" t="n">
-        <v>22.42738817716952</v>
+        <v>22.42738817716967</v>
       </c>
       <c r="AA5" t="n">
-        <v>22.88140946824072</v>
+        <v>22.88140946824066</v>
       </c>
       <c r="AB5" t="n">
-        <v>23.39595791764732</v>
+        <v>23.39595791764753</v>
       </c>
     </row>
     <row r="6">
@@ -6410,85 +6410,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>10.9149057338186</v>
+        <v>10.91490573381903</v>
       </c>
       <c r="C6" t="n">
-        <v>9.80766323265266</v>
+        <v>9.807663232652709</v>
       </c>
       <c r="D6" t="n">
-        <v>10.69948596708225</v>
+        <v>10.69948596708279</v>
       </c>
       <c r="E6" t="n">
-        <v>9.927146569341071</v>
+        <v>9.927146569341486</v>
       </c>
       <c r="F6" t="n">
-        <v>10.54983283998886</v>
+        <v>10.54983283998885</v>
       </c>
       <c r="G6" t="n">
-        <v>17.01344212812888</v>
+        <v>17.01344212812932</v>
       </c>
       <c r="H6" t="n">
-        <v>10.00816276566499</v>
+        <v>10.00816276566546</v>
       </c>
       <c r="I6" t="n">
-        <v>10.50048731327817</v>
+        <v>10.50048731327862</v>
       </c>
       <c r="J6" t="n">
-        <v>13.74392823968719</v>
+        <v>13.74392823968749</v>
       </c>
       <c r="K6" t="n">
-        <v>10.94921900761782</v>
+        <v>10.94921900761821</v>
       </c>
       <c r="L6" t="n">
-        <v>10.70823644001697</v>
+        <v>10.70823644001742</v>
       </c>
       <c r="M6" t="n">
-        <v>20.23121877364534</v>
+        <v>20.2312187736453</v>
       </c>
       <c r="N6" t="n">
-        <v>10.94478946506637</v>
+        <v>10.94478946506679</v>
       </c>
       <c r="O6" t="n">
-        <v>10.99064348394953</v>
+        <v>10.99064348395003</v>
       </c>
       <c r="P6" t="n">
-        <v>12.68020085474881</v>
+        <v>12.68020085474916</v>
       </c>
       <c r="Q6" t="n">
-        <v>10.89649122873266</v>
+        <v>10.89649122873312</v>
       </c>
       <c r="R6" t="n">
-        <v>10.18802037993668</v>
+        <v>10.18802037993725</v>
       </c>
       <c r="S6" t="n">
-        <v>11.53679108717205</v>
+        <v>11.53679108717249</v>
       </c>
       <c r="T6" t="n">
-        <v>10.32711685649159</v>
+        <v>10.32711685649203</v>
       </c>
       <c r="U6" t="n">
-        <v>11.72563203562025</v>
+        <v>11.72563203562065</v>
       </c>
       <c r="V6" t="n">
-        <v>10.404078711011</v>
+        <v>10.40407871101093</v>
       </c>
       <c r="W6" t="n">
-        <v>11.74514163823372</v>
+        <v>11.7451416382344</v>
       </c>
       <c r="X6" t="n">
-        <v>11.53226135575311</v>
+        <v>11.53226135575361</v>
       </c>
       <c r="Y6" t="n">
-        <v>12.1214607906025</v>
+        <v>12.12146079060292</v>
       </c>
       <c r="Z6" t="n">
-        <v>11.56903390150985</v>
+        <v>11.56903390151027</v>
       </c>
       <c r="AA6" t="n">
-        <v>11.01536445974136</v>
+        <v>11.01536445974176</v>
       </c>
       <c r="AB6" t="n">
-        <v>19.40720980269354</v>
+        <v>19.40720980269351</v>
       </c>
     </row>
     <row r="7">
@@ -6498,82 +6498,82 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>10.0117660044757</v>
+        <v>10.01176600447642</v>
       </c>
       <c r="C7" t="n">
-        <v>10.4625415416887</v>
+        <v>10.46254154168864</v>
       </c>
       <c r="D7" t="n">
-        <v>10.45750741990924</v>
+        <v>10.45750741990966</v>
       </c>
       <c r="E7" t="n">
-        <v>10.16838805816024</v>
+        <v>10.16838805816058</v>
       </c>
       <c r="F7" t="n">
-        <v>10.05701523518607</v>
+        <v>10.05701523518606</v>
       </c>
       <c r="G7" t="n">
-        <v>10.51117477123102</v>
+        <v>10.51117477123141</v>
       </c>
       <c r="H7" t="n">
-        <v>10.45750741990924</v>
+        <v>10.45750741990966</v>
       </c>
       <c r="I7" t="n">
-        <v>10.45750741990924</v>
+        <v>10.45750741990966</v>
       </c>
       <c r="J7" t="n">
-        <v>10.40016669035618</v>
+        <v>10.40016669035641</v>
       </c>
       <c r="K7" t="n">
-        <v>10.45750741990924</v>
+        <v>10.45750741990966</v>
       </c>
       <c r="L7" t="n">
-        <v>10.45750741990924</v>
+        <v>10.45750741990966</v>
       </c>
       <c r="M7" t="n">
-        <v>10.50786750872772</v>
+        <v>10.50786750872774</v>
       </c>
       <c r="N7" t="n">
-        <v>10.11198325204131</v>
+        <v>10.11198325204156</v>
       </c>
       <c r="O7" t="n">
-        <v>10.16817625861702</v>
+        <v>10.16817625861711</v>
       </c>
       <c r="P7" t="n">
-        <v>10.14490097376107</v>
+        <v>10.14490097376116</v>
       </c>
       <c r="Q7" t="n">
-        <v>9.924167642784409</v>
+        <v>9.924167642784761</v>
       </c>
       <c r="R7" t="n">
-        <v>10.45750741990924</v>
+        <v>10.45750741990966</v>
       </c>
       <c r="S7" t="n">
-        <v>10.45750741990924</v>
+        <v>10.45750741990966</v>
       </c>
       <c r="T7" t="n">
-        <v>10.45750741990924</v>
+        <v>10.45750741990966</v>
       </c>
       <c r="U7" t="n">
-        <v>10.20107659874594</v>
+        <v>10.20107659874635</v>
       </c>
       <c r="V7" t="n">
-        <v>10.24417950007572</v>
+        <v>10.24417950007559</v>
       </c>
       <c r="W7" t="n">
-        <v>10.41883498599215</v>
+        <v>10.41883498599258</v>
       </c>
       <c r="X7" t="n">
-        <v>9.926260694322259</v>
+        <v>9.92626069432289</v>
       </c>
       <c r="Y7" t="n">
-        <v>10.90050918570331</v>
+        <v>10.90050918570321</v>
       </c>
       <c r="Z7" t="n">
-        <v>10.0034861288377</v>
+        <v>10.0034861288383</v>
       </c>
       <c r="AA7" t="n">
-        <v>10.45750741990924</v>
+        <v>10.45750741990966</v>
       </c>
       <c r="AB7" t="n">
         <v>10.97205586931622</v>
@@ -6742,85 +6742,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>12.58001572454505</v>
+        <v>12.58001572454507</v>
       </c>
       <c r="C2" t="n">
         <v>10.68018784842316</v>
       </c>
       <c r="D2" t="n">
-        <v>10.88183857790716</v>
+        <v>10.88183857790718</v>
       </c>
       <c r="E2" t="n">
         <v>10.32227940411099</v>
       </c>
       <c r="F2" t="n">
-        <v>10.55038548245682</v>
+        <v>10.55038548245681</v>
       </c>
       <c r="G2" t="n">
-        <v>26.00904728963696</v>
+        <v>26.00904728963698</v>
       </c>
       <c r="H2" t="n">
         <v>11.25683205111155</v>
       </c>
       <c r="I2" t="n">
-        <v>11.41451665879695</v>
+        <v>11.41451665879697</v>
       </c>
       <c r="J2" t="n">
-        <v>16.37848659441162</v>
+        <v>16.37848659441151</v>
       </c>
       <c r="K2" t="n">
-        <v>12.12631494118604</v>
+        <v>12.12631494118606</v>
       </c>
       <c r="L2" t="n">
-        <v>11.79633394515067</v>
+        <v>11.79633394515068</v>
       </c>
       <c r="M2" t="n">
-        <v>13.59236684635475</v>
+        <v>13.59236684635474</v>
       </c>
       <c r="N2" t="n">
-        <v>12.07646417753314</v>
+        <v>12.07646417753313</v>
       </c>
       <c r="O2" t="n">
-        <v>12.15924468036173</v>
+        <v>12.15924468036175</v>
       </c>
       <c r="P2" t="n">
-        <v>14.83110654482362</v>
+        <v>14.83110654482363</v>
       </c>
       <c r="Q2" t="n">
-        <v>12.73102777403445</v>
+        <v>12.73102777403447</v>
       </c>
       <c r="R2" t="n">
-        <v>11.30785544088089</v>
+        <v>11.30785544088091</v>
       </c>
       <c r="S2" t="n">
-        <v>11.81083500878976</v>
+        <v>11.81083500878978</v>
       </c>
       <c r="T2" t="n">
-        <v>10.66331698269105</v>
+        <v>10.66331698269103</v>
       </c>
       <c r="U2" t="n">
-        <v>12.10347325198561</v>
+        <v>12.10347325198563</v>
       </c>
       <c r="V2" t="n">
         <v>11.77245607590648</v>
       </c>
       <c r="W2" t="n">
-        <v>14.27416984297389</v>
+        <v>14.27416984297392</v>
       </c>
       <c r="X2" t="n">
-        <v>15.47358571554081</v>
+        <v>15.47358571554083</v>
       </c>
       <c r="Y2" t="n">
-        <v>20.70553432991931</v>
+        <v>20.70553432991928</v>
       </c>
       <c r="Z2" t="n">
-        <v>12.02829894649827</v>
+        <v>12.02829894649828</v>
       </c>
       <c r="AA2" t="n">
-        <v>11.67125995857798</v>
+        <v>11.67125995857797</v>
       </c>
       <c r="AB2" t="n">
-        <v>26.10349737929639</v>
+        <v>26.10349737929641</v>
       </c>
     </row>
     <row r="3">
@@ -6830,13 +6830,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>11.08719939387323</v>
+        <v>11.08719939387325</v>
       </c>
       <c r="C3" t="n">
-        <v>12.29533913101763</v>
+        <v>12.29533913101764</v>
       </c>
       <c r="D3" t="n">
-        <v>12.27848960890817</v>
+        <v>12.27848960890819</v>
       </c>
       <c r="E3" t="n">
         <v>11.60527726004003</v>
@@ -6845,70 +6845,70 @@
         <v>11.25487822107964</v>
       </c>
       <c r="G3" t="n">
-        <v>12.52551139553628</v>
+        <v>12.52551139553631</v>
       </c>
       <c r="H3" t="n">
-        <v>12.27848960890817</v>
+        <v>12.27848960890819</v>
       </c>
       <c r="I3" t="n">
-        <v>12.27848960890817</v>
+        <v>12.27848960890819</v>
       </c>
       <c r="J3" t="n">
-        <v>12.2613281169265</v>
+        <v>12.26132811692651</v>
       </c>
       <c r="K3" t="n">
-        <v>12.27848960890817</v>
+        <v>12.27848960890819</v>
       </c>
       <c r="L3" t="n">
-        <v>12.27848960890817</v>
+        <v>12.27848960890819</v>
       </c>
       <c r="M3" t="n">
         <v>12.27084086856766</v>
       </c>
       <c r="N3" t="n">
-        <v>11.35504039376662</v>
+        <v>11.35504039376664</v>
       </c>
       <c r="O3" t="n">
-        <v>11.6088122563087</v>
+        <v>11.60881225630871</v>
       </c>
       <c r="P3" t="n">
-        <v>11.54660664080671</v>
+        <v>11.54660664080674</v>
       </c>
       <c r="Q3" t="n">
-        <v>10.8530836767241</v>
+        <v>10.85308367672412</v>
       </c>
       <c r="R3" t="n">
-        <v>12.27848960890817</v>
+        <v>12.27848960890819</v>
       </c>
       <c r="S3" t="n">
-        <v>12.27848960890817</v>
+        <v>12.27848960890819</v>
       </c>
       <c r="T3" t="n">
-        <v>12.27848960890817</v>
+        <v>12.27848960890819</v>
       </c>
       <c r="U3" t="n">
-        <v>11.69676039250302</v>
+        <v>11.69676039250303</v>
       </c>
       <c r="V3" t="n">
-        <v>11.91162279226741</v>
+        <v>11.9116227922674</v>
       </c>
       <c r="W3" t="n">
-        <v>12.27872373165592</v>
+        <v>12.27872373165594</v>
       </c>
       <c r="X3" t="n">
-        <v>10.96226779211446</v>
+        <v>10.96226779211448</v>
       </c>
       <c r="Y3" t="n">
-        <v>13.46248957844231</v>
+        <v>13.46248957844232</v>
       </c>
       <c r="Z3" t="n">
-        <v>11.06507056651235</v>
+        <v>11.06507056651238</v>
       </c>
       <c r="AA3" t="n">
-        <v>12.27848960890817</v>
+        <v>12.27848960890819</v>
       </c>
       <c r="AB3" t="n">
-        <v>13.5480134028814</v>
+        <v>13.54801340288142</v>
       </c>
     </row>
     <row r="4">
@@ -6918,13 +6918,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>22.56279280553384</v>
+        <v>22.56279280553388</v>
       </c>
       <c r="C4" t="n">
-        <v>21.88103592275032</v>
+        <v>21.88103592275031</v>
       </c>
       <c r="D4" t="n">
-        <v>21.94382717658718</v>
+        <v>21.9438271765872</v>
       </c>
       <c r="E4" t="n">
         <v>21.71516226819099</v>
@@ -6933,70 +6933,70 @@
         <v>21.81163423143758</v>
       </c>
       <c r="G4" t="n">
-        <v>27.45751711935971</v>
+        <v>27.45751711935969</v>
       </c>
       <c r="H4" t="n">
-        <v>22.08050789417448</v>
+        <v>22.08050789417451</v>
       </c>
       <c r="I4" t="n">
-        <v>22.13798208204968</v>
+        <v>22.13798208204971</v>
       </c>
       <c r="J4" t="n">
-        <v>22.98864284082456</v>
+        <v>22.98864284082459</v>
       </c>
       <c r="K4" t="n">
-        <v>22.39742419762306</v>
+        <v>22.39742419762309</v>
       </c>
       <c r="L4" t="n">
-        <v>22.27714999940067</v>
+        <v>22.2771499994007</v>
       </c>
       <c r="M4" t="n">
-        <v>22.926922037504</v>
+        <v>22.92692203750399</v>
       </c>
       <c r="N4" t="n">
-        <v>22.37925417964883</v>
+        <v>22.37925417964884</v>
       </c>
       <c r="O4" t="n">
-        <v>22.40942670087209</v>
+        <v>22.40942670087212</v>
       </c>
       <c r="P4" t="n">
-        <v>23.38328897588241</v>
+        <v>23.38328897588243</v>
       </c>
       <c r="Q4" t="n">
-        <v>22.61783492429973</v>
+        <v>22.61783492429976</v>
       </c>
       <c r="R4" t="n">
-        <v>22.09910532059853</v>
+        <v>22.09910532059855</v>
       </c>
       <c r="S4" t="n">
-        <v>22.28243546681703</v>
+        <v>22.28243546681705</v>
       </c>
       <c r="T4" t="n">
-        <v>21.864178621141</v>
+        <v>21.86417862114104</v>
       </c>
       <c r="U4" t="n">
-        <v>22.38909867013016</v>
+        <v>22.38909867013019</v>
       </c>
       <c r="V4" t="n">
-        <v>15.91932171277403</v>
+        <v>15.919321712774</v>
       </c>
       <c r="W4" t="n">
-        <v>23.18029208793912</v>
+        <v>23.18029208793914</v>
       </c>
       <c r="X4" t="n">
-        <v>23.6174650892375</v>
+        <v>23.61746508923752</v>
       </c>
       <c r="Y4" t="n">
-        <v>25.52444892253601</v>
+        <v>25.52444892253603</v>
       </c>
       <c r="Z4" t="n">
-        <v>22.36169851852131</v>
+        <v>22.36169851852133</v>
       </c>
       <c r="AA4" t="n">
-        <v>22.23156199998783</v>
+        <v>22.23156199998785</v>
       </c>
       <c r="AB4" t="n">
-        <v>27.50790810810946</v>
+        <v>27.50790810810947</v>
       </c>
     </row>
     <row r="5">
@@ -7018,10 +7018,10 @@
         <v>22.18279992095568</v>
       </c>
       <c r="F5" t="n">
-        <v>22.0684135620942</v>
+        <v>22.06841356209421</v>
       </c>
       <c r="G5" t="n">
-        <v>22.54292661763231</v>
+        <v>22.54292661763232</v>
       </c>
       <c r="H5" t="n">
         <v>22.45289007708264</v>
@@ -7030,7 +7030,7 @@
         <v>22.45289007708264</v>
       </c>
       <c r="J5" t="n">
-        <v>21.48798692189702</v>
+        <v>21.48798692189704</v>
       </c>
       <c r="K5" t="n">
         <v>22.45289007708264</v>
@@ -7039,19 +7039,19 @@
         <v>22.45289007708264</v>
       </c>
       <c r="M5" t="n">
-        <v>22.44524133674213</v>
+        <v>22.44524133674211</v>
       </c>
       <c r="N5" t="n">
         <v>22.1163036818517</v>
       </c>
       <c r="O5" t="n">
-        <v>22.20880054580863</v>
+        <v>22.20880054580864</v>
       </c>
       <c r="P5" t="n">
-        <v>22.18612732941336</v>
+        <v>22.1861273294134</v>
       </c>
       <c r="Q5" t="n">
-        <v>21.93334635276305</v>
+        <v>21.93334635276307</v>
       </c>
       <c r="R5" t="n">
         <v>22.45289007708264</v>
@@ -7063,28 +7063,28 @@
         <v>22.45289007708264</v>
       </c>
       <c r="U5" t="n">
-        <v>22.24085660871229</v>
+        <v>22.24085660871232</v>
       </c>
       <c r="V5" t="n">
-        <v>15.97004634670951</v>
+        <v>15.97004634670946</v>
       </c>
       <c r="W5" t="n">
-        <v>22.45297541207496</v>
+        <v>22.45297541207499</v>
       </c>
       <c r="X5" t="n">
-        <v>21.97314268071823</v>
+        <v>21.97314268071824</v>
       </c>
       <c r="Y5" t="n">
         <v>22.88444416274825</v>
       </c>
       <c r="Z5" t="n">
-        <v>22.01061308481515</v>
+        <v>22.01061308481514</v>
       </c>
       <c r="AA5" t="n">
         <v>22.45289007708264</v>
       </c>
       <c r="AB5" t="n">
-        <v>22.93158163264266</v>
+        <v>22.93158163264268</v>
       </c>
     </row>
     <row r="6">
@@ -7094,64 +7094,64 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>10.4778707461207</v>
+        <v>10.47787074612072</v>
       </c>
       <c r="C6" t="n">
-        <v>9.796113863337185</v>
+        <v>9.796113863337178</v>
       </c>
       <c r="D6" t="n">
-        <v>9.858905117174029</v>
+        <v>9.858905117174041</v>
       </c>
       <c r="E6" t="n">
-        <v>9.630240208777847</v>
+        <v>9.630240208777854</v>
       </c>
       <c r="F6" t="n">
-        <v>9.726712172024442</v>
+        <v>9.726712172024438</v>
       </c>
       <c r="G6" t="n">
-        <v>15.33451632673431</v>
+        <v>15.33451632673433</v>
       </c>
       <c r="H6" t="n">
-        <v>9.995585834761357</v>
+        <v>9.995585834761366</v>
       </c>
       <c r="I6" t="n">
-        <v>10.05306002263654</v>
+        <v>10.05306002263656</v>
       </c>
       <c r="J6" t="n">
-        <v>11.81477593689078</v>
+        <v>11.81477593689079</v>
       </c>
       <c r="K6" t="n">
-        <v>10.31250213820993</v>
+        <v>10.31250213820995</v>
       </c>
       <c r="L6" t="n">
-        <v>10.19222793998752</v>
+        <v>10.19222793998755</v>
       </c>
       <c r="M6" t="n">
-        <v>10.84199997809085</v>
+        <v>10.84199997809086</v>
       </c>
       <c r="N6" t="n">
-        <v>10.29433212023567</v>
+        <v>10.29433212023568</v>
       </c>
       <c r="O6" t="n">
-        <v>10.28642590824671</v>
+        <v>10.28642590824673</v>
       </c>
       <c r="P6" t="n">
-        <v>11.26028818325702</v>
+        <v>11.26028818325704</v>
       </c>
       <c r="Q6" t="n">
-        <v>10.53291286488659</v>
+        <v>10.5329128648866</v>
       </c>
       <c r="R6" t="n">
-        <v>10.01418326118539</v>
+        <v>10.0141832611854</v>
       </c>
       <c r="S6" t="n">
-        <v>10.19751340740388</v>
+        <v>10.19751340740391</v>
       </c>
       <c r="T6" t="n">
-        <v>9.779256561727866</v>
+        <v>9.779256561727902</v>
       </c>
       <c r="U6" t="n">
-        <v>10.26609787750477</v>
+        <v>10.2660978775048</v>
       </c>
       <c r="V6" t="n">
         <v>10.1214295598828</v>
@@ -7160,16 +7160,16 @@
         <v>11.05729129531374</v>
       </c>
       <c r="X6" t="n">
-        <v>11.49446429661212</v>
+        <v>11.49446429661213</v>
       </c>
       <c r="Y6" t="n">
         <v>13.43952686312289</v>
       </c>
       <c r="Z6" t="n">
-        <v>10.27677645910817</v>
+        <v>10.27677645910818</v>
       </c>
       <c r="AA6" t="n">
-        <v>10.14663994057469</v>
+        <v>10.1466399405747</v>
       </c>
       <c r="AB6" t="n">
         <v>15.42298604869633</v>
@@ -7188,10 +7188,10 @@
         <v>10.38481753977895</v>
       </c>
       <c r="D7" t="n">
-        <v>10.36796801766948</v>
+        <v>10.36796801766949</v>
       </c>
       <c r="E7" t="n">
-        <v>10.09787786154254</v>
+        <v>10.09787786154253</v>
       </c>
       <c r="F7" t="n">
         <v>9.983491502681053</v>
@@ -7200,19 +7200,19 @@
         <v>10.41992582500692</v>
       </c>
       <c r="H7" t="n">
-        <v>10.36796801766948</v>
+        <v>10.36796801766949</v>
       </c>
       <c r="I7" t="n">
-        <v>10.36796801766948</v>
+        <v>10.36796801766949</v>
       </c>
       <c r="J7" t="n">
-        <v>10.31412001796322</v>
+        <v>10.31412001796323</v>
       </c>
       <c r="K7" t="n">
-        <v>10.36796801766948</v>
+        <v>10.36796801766949</v>
       </c>
       <c r="L7" t="n">
-        <v>10.36796801766948</v>
+        <v>10.36796801766949</v>
       </c>
       <c r="M7" t="n">
         <v>10.36031927732898</v>
@@ -7221,46 +7221,46 @@
         <v>10.03138162243856</v>
       </c>
       <c r="O7" t="n">
-        <v>10.08579975318322</v>
+        <v>10.08579975318325</v>
       </c>
       <c r="P7" t="n">
-        <v>10.06312653678798</v>
+        <v>10.06312653678799</v>
       </c>
       <c r="Q7" t="n">
-        <v>9.848424293349913</v>
+        <v>9.848424293349924</v>
       </c>
       <c r="R7" t="n">
-        <v>10.36796801766948</v>
+        <v>10.36796801766949</v>
       </c>
       <c r="S7" t="n">
-        <v>10.36796801766948</v>
+        <v>10.36796801766949</v>
       </c>
       <c r="T7" t="n">
-        <v>10.36796801766948</v>
+        <v>10.36796801766949</v>
       </c>
       <c r="U7" t="n">
-        <v>10.1178558160869</v>
+        <v>10.11785581608692</v>
       </c>
       <c r="V7" t="n">
-        <v>10.17215419381826</v>
+        <v>10.17215419381827</v>
       </c>
       <c r="W7" t="n">
-        <v>10.32997461944959</v>
+        <v>10.3299746194496</v>
       </c>
       <c r="X7" t="n">
-        <v>9.850141888092837</v>
+        <v>9.85014188809285</v>
       </c>
       <c r="Y7" t="n">
         <v>10.7995221033351</v>
       </c>
       <c r="Z7" t="n">
-        <v>9.92569102540199</v>
+        <v>9.92569102540201</v>
       </c>
       <c r="AA7" t="n">
-        <v>10.36796801766948</v>
+        <v>10.36796801766949</v>
       </c>
       <c r="AB7" t="n">
-        <v>10.84665957322954</v>
+        <v>10.84665957322953</v>
       </c>
     </row>
   </sheetData>
